--- a/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA58C61-6AB2-A04B-A0FA-EFB450D13758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED6C9ED-EB5D-A643-95BF-2237FC5DEAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1280" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
@@ -377,7 +377,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Mansatory for Autotune Type - PERFORMANCE_BASED or BOTH</t>
+          <t>Mandatory for Autotune Type - PERFORMANCE_BASED or BOTH</t>
         </r>
       </text>
     </comment>
@@ -386,40 +386,6 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Suruchi</author>
-  </authors>
-  <commentList>
-    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{4D05ED1D-9D75-B94C-8564-8547C5BB6DB9}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Enter OCID of the snapshot policy to be attached to the FSS.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Microsoft Office User</author>
@@ -668,7 +634,7 @@
 </comments>
 </file>
 
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Suruchi</author>
@@ -730,7 +696,7 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Suruchi</author>
@@ -12529,182 +12495,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
-Columns: Region, Compartment Name, Availability Domain, MountTarget Name, MountTarget SubnetName, FSS name, Path are mandatory.
-Freeform and Defined Tags - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>If specified, Applies to FSS object only and not to other components like Mount Target.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Enter subnet name as : </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&lt;</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">vcn-name&gt;_&lt;subnet-name&gt;
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Source Snapshot:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Accepts OCID of the source snapshot  or the name of the key defined under variable  fss_source_ocids in variables_&lt;region&gt;.tf file</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Replication Information: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Format - TargetFSS(OCID or Name)::ReplicationInterval::ReplicationName. Multiple replication values are seperated by newline in the same cell(\n is not supported). Ensure Target FSS for replication must not have exports created.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Defined Tags" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
-                             Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
-                           </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Example: Operations.CostCenter=01;Users.Name=user01</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <b/>
         <u/>
@@ -12768,6 +12558,204 @@
   </si>
   <si>
     <t>onlyFSS</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
+Columns: Region, Compartment Name, Availability Domain, MountTarget Name, MountTarget SubnetName, FSS name, Path are mandatory.
+Freeform and Defined Tags - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>If specified, Applies to FSS object only and not to other components like Mount Target.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Enter subnet name as : </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">vcn-name&gt;_&lt;subnet-name&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Source Snapshot:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Accepts OCID of the source snapshot  or the name of the key defined under variable  fss_source_ocids in variables_&lt;region&gt;.tf file
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Snapshot Policy - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accepts OCID of the snapshot policy or the name in format: &lt;snaphot_policy_compartment_name&gt;@&lt;snaphost_policy_name&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Replication Information: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Format - TargetFSS(OCID or Name)::ReplicationInterval::ReplicationName. Multiple replication values are seperated by newline in the same cell(\n is not supported). Ensure Target FSS for replication must not have exports created.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Defined Tags" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
+                             Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
+                           </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Example: Operations.CostCenter=01;Users.Name=user01</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -24200,7 +24188,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
@@ -24227,9 +24215,9 @@
     <col min="22" max="22" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="164" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" ht="190" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="134" t="s">
-        <v>1480</v>
+        <v>1483</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
@@ -24243,7 +24231,7 @@
       <c r="K1" s="135"/>
       <c r="L1" s="136"/>
       <c r="M1" s="148" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="N1" s="149"/>
       <c r="O1" s="149"/>
@@ -24255,7 +24243,7 @@
       <c r="U1" s="149"/>
       <c r="V1" s="150"/>
     </row>
-    <row r="2" spans="1:22" s="1" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
@@ -24626,7 +24614,7 @@
         <v>90</v>
       </c>
       <c r="D11" s="54" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="E11" s="55" t="s">
         <v>395</v>
@@ -24665,7 +24653,7 @@
       <c r="G12" s="54"/>
       <c r="H12" s="54"/>
       <c r="I12" s="54" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="J12" s="54"/>
       <c r="K12" s="54"/>
@@ -24687,12 +24675,11 @@
     <mergeCell ref="M1:V1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" sqref="B2:C2 A1:A2 E2 D2:D1048576 F2:L1048576 M1:S1048576 U1:XFD1048576" xr:uid="{ECAF8C21-0469-6E46-97A7-0CA01BCF64B2}"/>
+    <dataValidation allowBlank="1" sqref="M1:S1048576 U1:XFD1048576 D3:D1048576 F3:L1048576 B2:L2 A1:A2" xr:uid="{ECAF8C21-0469-6E46-97A7-0CA01BCF64B2}"/>
     <dataValidation showInputMessage="1" showErrorMessage="1" sqref="T1:T1048576" xr:uid="{3C93AF59-8CE9-5647-95AE-530DD7DB9390}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED6C9ED-EB5D-A643-95BF-2237FC5DEAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E132C99A-1DFE-8149-95A7-4BE2CADED25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -742,7 +742,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2627" uniqueCount="1484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2627" uniqueCount="1483">
   <si>
     <t>Region</t>
   </si>
@@ -10637,9 +10637,6 @@
   </si>
   <si>
     <t>Quota Policy</t>
-  </si>
-  <si>
-    <t>ashburn</t>
   </si>
   <si>
     <t>OracleAnalyticsQuota</t>
@@ -19636,7 +19633,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="84" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
   </sheetData>
@@ -19668,7 +19665,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="250" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="134" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
@@ -23981,7 +23978,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="202" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="134" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
@@ -24033,16 +24030,16 @@
         <v>438</v>
       </c>
       <c r="K2" s="28" t="s">
+        <v>1397</v>
+      </c>
+      <c r="L2" s="28" t="s">
         <v>1398</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="M2" s="28" t="s">
         <v>1399</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="N2" s="28" t="s">
         <v>1400</v>
-      </c>
-      <c r="N2" s="28" t="s">
-        <v>1401</v>
       </c>
       <c r="O2" s="28" t="s">
         <v>779</v>
@@ -24108,19 +24105,19 @@
         <v>781</v>
       </c>
       <c r="J4" s="124" t="s">
+        <v>1401</v>
+      </c>
+      <c r="K4" s="124" t="s">
         <v>1402</v>
-      </c>
-      <c r="K4" s="124" t="s">
-        <v>1403</v>
       </c>
       <c r="L4" s="124">
         <v>100</v>
       </c>
       <c r="M4" s="124" t="s">
+        <v>1403</v>
+      </c>
+      <c r="N4" s="124" t="s">
         <v>1404</v>
-      </c>
-      <c r="N4" s="124" t="s">
-        <v>1405</v>
       </c>
       <c r="O4" s="88" t="b">
         <v>1</v>
@@ -24217,7 +24214,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="190" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="134" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
@@ -24231,7 +24228,7 @@
       <c r="K1" s="135"/>
       <c r="L1" s="136"/>
       <c r="M1" s="148" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="N1" s="149"/>
       <c r="O1" s="149"/>
@@ -24272,13 +24269,13 @@
         <v>115</v>
       </c>
       <c r="J2" s="28" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K2" s="28" t="s">
         <v>1406</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="L2" s="28" t="s">
         <v>1407</v>
-      </c>
-      <c r="L2" s="28" t="s">
-        <v>1408</v>
       </c>
       <c r="M2" s="28" t="s">
         <v>116</v>
@@ -24302,10 +24299,10 @@
         <v>122</v>
       </c>
       <c r="T2" s="28" t="s">
+        <v>1408</v>
+      </c>
+      <c r="U2" s="28" t="s">
         <v>1409</v>
-      </c>
-      <c r="U2" s="28" t="s">
-        <v>1410</v>
       </c>
       <c r="V2" s="28" t="s">
         <v>428</v>
@@ -24614,7 +24611,7 @@
         <v>90</v>
       </c>
       <c r="D11" s="54" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="E11" s="55" t="s">
         <v>395</v>
@@ -24653,7 +24650,7 @@
       <c r="G12" s="54"/>
       <c r="H12" s="54"/>
       <c r="I12" s="54" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="J12" s="54"/>
       <c r="K12" s="54"/>
@@ -27321,13 +27318,13 @@
         <v>804</v>
       </c>
       <c r="D4" s="55" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E4" s="55" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="55" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="G4" s="55" t="b">
         <v>1</v>
@@ -27797,10 +27794,10 @@
         <v>811</v>
       </c>
       <c r="G2" s="28" t="s">
+        <v>1412</v>
+      </c>
+      <c r="H2" s="28" t="s">
         <v>1413</v>
-      </c>
-      <c r="H2" s="28" t="s">
-        <v>1414</v>
       </c>
       <c r="I2" s="28" t="s">
         <v>160</v>
@@ -27864,7 +27861,7 @@
         <v>10000</v>
       </c>
       <c r="L4" s="55" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="32" x14ac:dyDescent="0.2">
@@ -27898,7 +27895,7 @@
         <v>10000</v>
       </c>
       <c r="L5" s="55" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
@@ -27915,10 +27912,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="55" t="s">
+        <v>1416</v>
+      </c>
+      <c r="H6" s="55" t="s">
         <v>1417</v>
-      </c>
-      <c r="H6" s="55" t="s">
-        <v>1418</v>
       </c>
       <c r="I6" s="55">
         <v>53</v>
@@ -27928,7 +27925,7 @@
         <v>20000</v>
       </c>
       <c r="L6" s="55" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
   </sheetData>
@@ -39038,49 +39035,49 @@
         <v>560</v>
       </c>
       <c r="C3" s="33" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>1420</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="E3" s="33" t="s">
         <v>1421</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="F3" s="33" t="s">
         <v>1422</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="G3" s="33" t="s">
         <v>1423</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="H3" s="33" t="s">
         <v>1424</v>
-      </c>
-      <c r="H3" s="33" t="s">
-        <v>1425</v>
       </c>
       <c r="I3" s="33" t="s">
         <v>56</v>
       </c>
       <c r="J3" s="33" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="K3" s="33">
         <v>16</v>
       </c>
       <c r="L3" t="s">
+        <v>1426</v>
+      </c>
+      <c r="M3" t="s">
         <v>1427</v>
-      </c>
-      <c r="M3" t="s">
-        <v>1428</v>
       </c>
       <c r="N3" s="33">
         <v>3</v>
       </c>
       <c r="O3" s="33" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="P3" s="33" t="b">
         <v>0</v>
       </c>
       <c r="Q3" s="33" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="R3" s="29"/>
     </row>
@@ -39092,18 +39089,18 @@
         <v>560</v>
       </c>
       <c r="C4" s="33" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>1431</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>1432</v>
       </c>
       <c r="E4" s="33"/>
       <c r="F4" s="33"/>
       <c r="G4" s="33" t="s">
+        <v>1423</v>
+      </c>
+      <c r="H4" s="33" t="s">
         <v>1424</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>1425</v>
       </c>
       <c r="I4" s="33" t="s">
         <v>56</v>
@@ -39120,7 +39117,7 @@
         <v>3</v>
       </c>
       <c r="O4" s="33" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="P4" s="33" t="b">
         <v>0</v>
@@ -39203,7 +39200,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="145" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B1" s="157"/>
       <c r="C1" s="157"/>
@@ -39269,43 +39266,43 @@
         <v>5</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="C3" s="33" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>1435</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="E3" s="33" t="s">
         <v>1436</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="F3" s="33" t="s">
         <v>1437</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="G3" s="33" t="s">
         <v>1438</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="H3" s="33" t="s">
         <v>1439</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="I3" s="33" t="s">
         <v>1440</v>
       </c>
-      <c r="I3" s="33" t="s">
+      <c r="J3" s="33" t="s">
         <v>1441</v>
       </c>
-      <c r="J3" s="33" t="s">
+      <c r="K3" s="33" t="s">
         <v>1442</v>
       </c>
-      <c r="K3" s="33" t="s">
+      <c r="L3" s="33" t="s">
         <v>1443</v>
       </c>
-      <c r="L3" s="33" t="s">
+      <c r="M3" s="33" t="s">
         <v>1444</v>
       </c>
-      <c r="M3" s="33" t="s">
+      <c r="N3" s="33" t="s">
         <v>1445</v>
-      </c>
-      <c r="N3" s="33" t="s">
-        <v>1446</v>
       </c>
       <c r="O3" s="125"/>
     </row>
@@ -39314,41 +39311,41 @@
         <v>5</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="C4" s="33" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>1435</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>1436</v>
       </c>
       <c r="E4" s="33"/>
       <c r="F4" s="33" t="s">
+        <v>1437</v>
+      </c>
+      <c r="G4" s="33" t="s">
         <v>1438</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="H4" s="33" t="s">
         <v>1439</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="I4" s="33" t="s">
         <v>1440</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="J4" s="33" t="s">
         <v>1441</v>
       </c>
-      <c r="J4" s="33" t="s">
+      <c r="K4" s="33" t="s">
         <v>1442</v>
       </c>
-      <c r="K4" s="33" t="s">
+      <c r="L4" s="33" t="s">
         <v>1443</v>
       </c>
-      <c r="L4" s="33" t="s">
+      <c r="M4" s="33" t="s">
         <v>1444</v>
       </c>
-      <c r="M4" s="33" t="s">
-        <v>1445</v>
-      </c>
       <c r="N4" s="33" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="O4" s="125"/>
     </row>
@@ -40768,7 +40765,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="234" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="131" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B1" s="131"/>
       <c r="C1" s="131"/>
@@ -40777,7 +40774,7 @@
       <c r="F1" s="131"/>
       <c r="G1" s="131"/>
       <c r="H1" s="141" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="I1" s="131"/>
       <c r="J1" s="131"/>
@@ -40792,46 +40789,46 @@
         <v>0</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C2" s="127" t="s">
         <v>1450</v>
       </c>
-      <c r="C2" s="127" t="s">
+      <c r="D2" s="17" t="s">
         <v>1451</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="E2" s="17" t="s">
         <v>1452</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="F2" s="17" t="s">
+        <v>1454</v>
+      </c>
+      <c r="G2" s="50" t="s">
+        <v>1455</v>
+      </c>
+      <c r="H2" s="96" t="s">
+        <v>1456</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>1457</v>
+      </c>
+      <c r="J2" s="128" t="s">
+        <v>1458</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>1459</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>1460</v>
+      </c>
+      <c r="M2" s="129" t="s">
+        <v>1461</v>
+      </c>
+      <c r="N2" s="17" t="s">
         <v>1453</v>
       </c>
-      <c r="F2" s="17" t="s">
-        <v>1455</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>1456</v>
-      </c>
-      <c r="H2" s="96" t="s">
-        <v>1457</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>1458</v>
-      </c>
-      <c r="J2" s="128" t="s">
-        <v>1459</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>1460</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>1461</v>
-      </c>
-      <c r="M2" s="129" t="s">
+      <c r="O2" s="17" t="s">
         <v>1462</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>1454</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>1463</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
@@ -40861,23 +40858,23 @@
         <v>565</v>
       </c>
       <c r="C4" s="33" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>1464</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>1465</v>
       </c>
       <c r="E4" s="33"/>
       <c r="F4" s="33" t="s">
         <v>565</v>
       </c>
       <c r="G4" s="33" t="s">
+        <v>1465</v>
+      </c>
+      <c r="H4" s="33" t="s">
         <v>1466</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="I4" s="33" t="s">
         <v>1467</v>
-      </c>
-      <c r="I4" s="33" t="s">
-        <v>1468</v>
       </c>
       <c r="J4" s="130">
         <v>256</v>
@@ -40898,19 +40895,19 @@
         <v>560</v>
       </c>
       <c r="G5" s="33" t="s">
+        <v>1468</v>
+      </c>
+      <c r="H5" s="33" t="s">
         <v>1469</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="I5" s="33" t="s">
         <v>1470</v>
-      </c>
-      <c r="I5" s="33" t="s">
-        <v>1471</v>
       </c>
       <c r="J5" s="130">
         <v>384</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="L5" s="33"/>
       <c r="M5" s="130"/>
@@ -40925,10 +40922,10 @@
         <v>565</v>
       </c>
       <c r="C6" s="33" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D6" s="33" t="s">
         <v>1473</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>1474</v>
       </c>
       <c r="E6" s="33" t="s">
         <v>5</v>
@@ -40937,13 +40934,13 @@
         <v>565</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="J6" s="130">
         <v>128</v>
@@ -40968,13 +40965,13 @@
         <v>560</v>
       </c>
       <c r="G7" s="33" t="s">
+        <v>1468</v>
+      </c>
+      <c r="H7" s="33" t="s">
         <v>1469</v>
       </c>
-      <c r="H7" s="33" t="s">
-        <v>1470</v>
-      </c>
       <c r="I7" s="33" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="J7" s="130">
         <v>3072</v>
@@ -40995,19 +40992,19 @@
         <v>562</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H8" s="33" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="I8" s="33" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="J8" s="130">
         <v>521</v>
       </c>
       <c r="K8" s="33" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="L8" s="33" t="b">
         <v>1</v>
@@ -54591,16 +54588,16 @@
     </row>
     <row r="3" spans="1:5" ht="112" x14ac:dyDescent="0.2">
       <c r="A3" s="65" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="65" t="s">
         <v>1365</v>
       </c>
-      <c r="B3" s="65" t="s">
+      <c r="C3" s="65" t="s">
         <v>1366</v>
       </c>
-      <c r="C3" s="65" t="s">
+      <c r="D3" s="33" t="s">
         <v>1367</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>1368</v>
       </c>
       <c r="E3" s="34"/>
     </row>
@@ -54639,7 +54636,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="41" customFormat="1" ht="207" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="131" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="B1" s="132"/>
       <c r="C1" s="132"/>
@@ -54666,34 +54663,34 @@
         <v>2</v>
       </c>
       <c r="D2" s="112" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E2" s="113" t="s">
         <v>1370</v>
       </c>
-      <c r="E2" s="113" t="s">
+      <c r="F2" s="113" t="s">
         <v>1371</v>
       </c>
-      <c r="F2" s="113" t="s">
+      <c r="G2" s="113" t="s">
         <v>1372</v>
       </c>
-      <c r="G2" s="113" t="s">
+      <c r="H2" s="114" t="s">
         <v>1373</v>
       </c>
-      <c r="H2" s="114" t="s">
+      <c r="I2" s="115" t="s">
         <v>1374</v>
       </c>
-      <c r="I2" s="115" t="s">
+      <c r="J2" s="115" t="s">
         <v>1375</v>
       </c>
-      <c r="J2" s="115" t="s">
+      <c r="K2" s="113" t="s">
         <v>1376</v>
       </c>
-      <c r="K2" s="113" t="s">
+      <c r="L2" s="113" t="s">
         <v>1377</v>
       </c>
-      <c r="L2" s="113" t="s">
+      <c r="M2" s="113" t="s">
         <v>1378</v>
-      </c>
-      <c r="M2" s="113" t="s">
-        <v>1379</v>
       </c>
       <c r="N2" s="116" t="s">
         <v>428</v>
@@ -54701,32 +54698,32 @@
     </row>
     <row r="3" spans="1:14" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="33" t="s">
-        <v>318</v>
+        <v>5</v>
       </c>
       <c r="B3" s="33" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C3" s="33" t="s">
         <v>1380</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="D3" s="33" t="s">
         <v>1381</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>1382</v>
       </c>
       <c r="E3" s="33" t="s">
         <v>404</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="G3" s="33">
         <v>10</v>
       </c>
       <c r="H3" s="117"/>
       <c r="I3" s="118" t="s">
+        <v>1383</v>
+      </c>
+      <c r="J3" s="118" t="s">
         <v>1384</v>
-      </c>
-      <c r="J3" s="118" t="s">
-        <v>1385</v>
       </c>
       <c r="K3" s="33"/>
       <c r="L3" s="33"/>
@@ -54735,22 +54732,22 @@
     </row>
     <row r="4" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="33" t="s">
-        <v>318</v>
+        <v>5</v>
       </c>
       <c r="B4" s="33" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C4" s="33" t="s">
         <v>1386</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="D4" s="33" t="s">
         <v>1387</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="E4" s="33" t="s">
         <v>1388</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="F4" s="33" t="s">
         <v>1389</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>1390</v>
       </c>
       <c r="G4" s="33">
         <v>100</v>
@@ -54761,7 +54758,7 @@
       <c r="I4" s="118"/>
       <c r="J4" s="118"/>
       <c r="K4" s="33" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="L4" s="119"/>
       <c r="M4" s="33"/>
@@ -54779,13 +54776,13 @@
       <c r="I5" s="118"/>
       <c r="J5" s="118"/>
       <c r="K5" s="33" t="s">
+        <v>1391</v>
+      </c>
+      <c r="L5" s="34" t="s">
         <v>1392</v>
       </c>
-      <c r="L5" s="34" t="s">
+      <c r="M5" s="33" t="s">
         <v>1393</v>
-      </c>
-      <c r="M5" s="33" t="s">
-        <v>1394</v>
       </c>
       <c r="N5" s="120"/>
     </row>
@@ -54801,10 +54798,10 @@
       <c r="I6" s="118"/>
       <c r="J6" s="118"/>
       <c r="K6" s="33" t="s">
+        <v>1394</v>
+      </c>
+      <c r="L6" s="34" t="s">
         <v>1395</v>
-      </c>
-      <c r="L6" s="34" t="s">
-        <v>1396</v>
       </c>
       <c r="M6" s="33"/>
       <c r="N6" s="120"/>

--- a/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E132C99A-1DFE-8149-95A7-4BE2CADED25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD60A90-C57D-7C42-B23E-6A852C3E3675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10653,265 +10653,6 @@
 </t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;).
-"Region" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Home Region only</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Scope" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Compartment or Tag</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Target" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Compartment Name or {tagNamespace}.{tagKey}.{tagValue}. Note- It should be a </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Cost Tracking Tag.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Schedule" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MONTH or  SINGLE_USE</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Amount" - T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>he amount of the budget expressed as a whole number in the currency of the customer’s rate card</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Start Day" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>The number of days offset from the first day of the month, at which the budget processing period starts. eg. 18. Mandatory for schedule type - MONTH</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Budget Start Date"/"Budget End Date" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>eg. 2024-05-20. Mandatory for schedule type - SINGLE_USE</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Alert Rules" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&lt;ACTUAL/FORECAST&gt;::&lt;Threshold value %/Threshold Amount&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-"Alert Recipients": </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> comma seperated email addresses
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Defined Tags"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
-                                Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
-                                </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>Example: Operations.CostCenter=01;Users.Name=user01</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
     <t>Scope</t>
   </si>
   <si>
@@ -12740,6 +12481,254 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Example: Operations.CostCenter=01;Users.Name=user01</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;).
+"Region" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Home Region only</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Scope" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Compartment or Tag</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Target" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Compartment Name or {tagNamespace}.{tagKey}.{tagValue}.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Schedule" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MONTH or  SINGLE_USE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Amount" - T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>he amount of the budget expressed as a whole number in the currency of the customer’s rate card</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Start Day" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The number of days offset from the first day of the month, at which the budget processing period starts. eg. 18. Mandatory for schedule type - MONTH</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Budget Start Date"/"Budget End Date" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>eg. 2024-05-20. Mandatory for schedule type - SINGLE_USE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Alert Rules" - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;ACTUAL/FORECAST&gt;::&lt;Threshold value %/Threshold Amount&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Alert Recipients": </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> comma seperated email addresses
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Defined Tags"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
+                                Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
+                                </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>Example: Operations.CostCenter=01;Users.Name=user01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -19633,7 +19622,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="84" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
   </sheetData>
@@ -19665,7 +19654,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="250" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="134" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
@@ -23978,7 +23967,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="202" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="134" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
@@ -24030,16 +24019,16 @@
         <v>438</v>
       </c>
       <c r="K2" s="28" t="s">
+        <v>1396</v>
+      </c>
+      <c r="L2" s="28" t="s">
         <v>1397</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="M2" s="28" t="s">
         <v>1398</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="N2" s="28" t="s">
         <v>1399</v>
-      </c>
-      <c r="N2" s="28" t="s">
-        <v>1400</v>
       </c>
       <c r="O2" s="28" t="s">
         <v>779</v>
@@ -24105,19 +24094,19 @@
         <v>781</v>
       </c>
       <c r="J4" s="124" t="s">
+        <v>1400</v>
+      </c>
+      <c r="K4" s="124" t="s">
         <v>1401</v>
-      </c>
-      <c r="K4" s="124" t="s">
-        <v>1402</v>
       </c>
       <c r="L4" s="124">
         <v>100</v>
       </c>
       <c r="M4" s="124" t="s">
+        <v>1402</v>
+      </c>
+      <c r="N4" s="124" t="s">
         <v>1403</v>
-      </c>
-      <c r="N4" s="124" t="s">
-        <v>1404</v>
       </c>
       <c r="O4" s="88" t="b">
         <v>1</v>
@@ -24214,7 +24203,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="190" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="134" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="B1" s="135"/>
       <c r="C1" s="135"/>
@@ -24228,7 +24217,7 @@
       <c r="K1" s="135"/>
       <c r="L1" s="136"/>
       <c r="M1" s="148" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="N1" s="149"/>
       <c r="O1" s="149"/>
@@ -24269,13 +24258,13 @@
         <v>115</v>
       </c>
       <c r="J2" s="28" t="s">
+        <v>1404</v>
+      </c>
+      <c r="K2" s="28" t="s">
         <v>1405</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="L2" s="28" t="s">
         <v>1406</v>
-      </c>
-      <c r="L2" s="28" t="s">
-        <v>1407</v>
       </c>
       <c r="M2" s="28" t="s">
         <v>116</v>
@@ -24299,10 +24288,10 @@
         <v>122</v>
       </c>
       <c r="T2" s="28" t="s">
+        <v>1407</v>
+      </c>
+      <c r="U2" s="28" t="s">
         <v>1408</v>
-      </c>
-      <c r="U2" s="28" t="s">
-        <v>1409</v>
       </c>
       <c r="V2" s="28" t="s">
         <v>428</v>
@@ -24611,7 +24600,7 @@
         <v>90</v>
       </c>
       <c r="D11" s="54" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="E11" s="55" t="s">
         <v>395</v>
@@ -24650,7 +24639,7 @@
       <c r="G12" s="54"/>
       <c r="H12" s="54"/>
       <c r="I12" s="54" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="J12" s="54"/>
       <c r="K12" s="54"/>
@@ -27318,13 +27307,13 @@
         <v>804</v>
       </c>
       <c r="D4" s="55" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="E4" s="55" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="55" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="G4" s="55" t="b">
         <v>1</v>
@@ -27794,10 +27783,10 @@
         <v>811</v>
       </c>
       <c r="G2" s="28" t="s">
+        <v>1411</v>
+      </c>
+      <c r="H2" s="28" t="s">
         <v>1412</v>
-      </c>
-      <c r="H2" s="28" t="s">
-        <v>1413</v>
       </c>
       <c r="I2" s="28" t="s">
         <v>160</v>
@@ -27861,7 +27850,7 @@
         <v>10000</v>
       </c>
       <c r="L4" s="55" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="32" x14ac:dyDescent="0.2">
@@ -27895,7 +27884,7 @@
         <v>10000</v>
       </c>
       <c r="L5" s="55" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
@@ -27912,10 +27901,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="55" t="s">
+        <v>1415</v>
+      </c>
+      <c r="H6" s="55" t="s">
         <v>1416</v>
-      </c>
-      <c r="H6" s="55" t="s">
-        <v>1417</v>
       </c>
       <c r="I6" s="55">
         <v>53</v>
@@ -27925,7 +27914,7 @@
         <v>20000</v>
       </c>
       <c r="L6" s="55" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
   </sheetData>
@@ -39035,49 +39024,49 @@
         <v>560</v>
       </c>
       <c r="C3" s="33" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>1419</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="E3" s="33" t="s">
         <v>1420</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="F3" s="33" t="s">
         <v>1421</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="G3" s="33" t="s">
         <v>1422</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="H3" s="33" t="s">
         <v>1423</v>
-      </c>
-      <c r="H3" s="33" t="s">
-        <v>1424</v>
       </c>
       <c r="I3" s="33" t="s">
         <v>56</v>
       </c>
       <c r="J3" s="33" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="K3" s="33">
         <v>16</v>
       </c>
       <c r="L3" t="s">
+        <v>1425</v>
+      </c>
+      <c r="M3" t="s">
         <v>1426</v>
-      </c>
-      <c r="M3" t="s">
-        <v>1427</v>
       </c>
       <c r="N3" s="33">
         <v>3</v>
       </c>
       <c r="O3" s="33" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="P3" s="33" t="b">
         <v>0</v>
       </c>
       <c r="Q3" s="33" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="R3" s="29"/>
     </row>
@@ -39089,18 +39078,18 @@
         <v>560</v>
       </c>
       <c r="C4" s="33" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>1430</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>1431</v>
       </c>
       <c r="E4" s="33"/>
       <c r="F4" s="33"/>
       <c r="G4" s="33" t="s">
+        <v>1422</v>
+      </c>
+      <c r="H4" s="33" t="s">
         <v>1423</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>1424</v>
       </c>
       <c r="I4" s="33" t="s">
         <v>56</v>
@@ -39117,7 +39106,7 @@
         <v>3</v>
       </c>
       <c r="O4" s="33" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="P4" s="33" t="b">
         <v>0</v>
@@ -39200,7 +39189,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="145" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="B1" s="157"/>
       <c r="C1" s="157"/>
@@ -39266,43 +39255,43 @@
         <v>5</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="C3" s="33" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D3" s="33" t="s">
         <v>1434</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="E3" s="33" t="s">
         <v>1435</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="F3" s="33" t="s">
         <v>1436</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="G3" s="33" t="s">
         <v>1437</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="H3" s="33" t="s">
         <v>1438</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="I3" s="33" t="s">
         <v>1439</v>
       </c>
-      <c r="I3" s="33" t="s">
+      <c r="J3" s="33" t="s">
         <v>1440</v>
       </c>
-      <c r="J3" s="33" t="s">
+      <c r="K3" s="33" t="s">
         <v>1441</v>
       </c>
-      <c r="K3" s="33" t="s">
+      <c r="L3" s="33" t="s">
         <v>1442</v>
       </c>
-      <c r="L3" s="33" t="s">
+      <c r="M3" s="33" t="s">
         <v>1443</v>
       </c>
-      <c r="M3" s="33" t="s">
+      <c r="N3" s="33" t="s">
         <v>1444</v>
-      </c>
-      <c r="N3" s="33" t="s">
-        <v>1445</v>
       </c>
       <c r="O3" s="125"/>
     </row>
@@ -39311,41 +39300,41 @@
         <v>5</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="C4" s="33" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>1434</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>1435</v>
       </c>
       <c r="E4" s="33"/>
       <c r="F4" s="33" t="s">
+        <v>1436</v>
+      </c>
+      <c r="G4" s="33" t="s">
         <v>1437</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="H4" s="33" t="s">
         <v>1438</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="I4" s="33" t="s">
         <v>1439</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="J4" s="33" t="s">
         <v>1440</v>
       </c>
-      <c r="J4" s="33" t="s">
+      <c r="K4" s="33" t="s">
         <v>1441</v>
       </c>
-      <c r="K4" s="33" t="s">
+      <c r="L4" s="33" t="s">
         <v>1442</v>
       </c>
-      <c r="L4" s="33" t="s">
+      <c r="M4" s="33" t="s">
         <v>1443</v>
       </c>
-      <c r="M4" s="33" t="s">
-        <v>1444</v>
-      </c>
       <c r="N4" s="33" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="O4" s="125"/>
     </row>
@@ -40765,7 +40754,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="234" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="131" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B1" s="131"/>
       <c r="C1" s="131"/>
@@ -40774,7 +40763,7 @@
       <c r="F1" s="131"/>
       <c r="G1" s="131"/>
       <c r="H1" s="141" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="I1" s="131"/>
       <c r="J1" s="131"/>
@@ -40789,46 +40778,46 @@
         <v>0</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C2" s="127" t="s">
         <v>1449</v>
       </c>
-      <c r="C2" s="127" t="s">
+      <c r="D2" s="17" t="s">
         <v>1450</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="E2" s="17" t="s">
         <v>1451</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="F2" s="17" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G2" s="50" t="s">
+        <v>1454</v>
+      </c>
+      <c r="H2" s="96" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>1456</v>
+      </c>
+      <c r="J2" s="128" t="s">
+        <v>1457</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>1458</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>1459</v>
+      </c>
+      <c r="M2" s="129" t="s">
+        <v>1460</v>
+      </c>
+      <c r="N2" s="17" t="s">
         <v>1452</v>
       </c>
-      <c r="F2" s="17" t="s">
-        <v>1454</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>1455</v>
-      </c>
-      <c r="H2" s="96" t="s">
-        <v>1456</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>1457</v>
-      </c>
-      <c r="J2" s="128" t="s">
-        <v>1458</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>1459</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>1460</v>
-      </c>
-      <c r="M2" s="129" t="s">
+      <c r="O2" s="17" t="s">
         <v>1461</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>1453</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>1462</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
@@ -40858,23 +40847,23 @@
         <v>565</v>
       </c>
       <c r="C4" s="33" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>1463</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>1464</v>
       </c>
       <c r="E4" s="33"/>
       <c r="F4" s="33" t="s">
         <v>565</v>
       </c>
       <c r="G4" s="33" t="s">
+        <v>1464</v>
+      </c>
+      <c r="H4" s="33" t="s">
         <v>1465</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="I4" s="33" t="s">
         <v>1466</v>
-      </c>
-      <c r="I4" s="33" t="s">
-        <v>1467</v>
       </c>
       <c r="J4" s="130">
         <v>256</v>
@@ -40895,19 +40884,19 @@
         <v>560</v>
       </c>
       <c r="G5" s="33" t="s">
+        <v>1467</v>
+      </c>
+      <c r="H5" s="33" t="s">
         <v>1468</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="I5" s="33" t="s">
         <v>1469</v>
-      </c>
-      <c r="I5" s="33" t="s">
-        <v>1470</v>
       </c>
       <c r="J5" s="130">
         <v>384</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="L5" s="33"/>
       <c r="M5" s="130"/>
@@ -40922,10 +40911,10 @@
         <v>565</v>
       </c>
       <c r="C6" s="33" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D6" s="33" t="s">
         <v>1472</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>1473</v>
       </c>
       <c r="E6" s="33" t="s">
         <v>5</v>
@@ -40934,13 +40923,13 @@
         <v>565</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="J6" s="130">
         <v>128</v>
@@ -40965,13 +40954,13 @@
         <v>560</v>
       </c>
       <c r="G7" s="33" t="s">
+        <v>1467</v>
+      </c>
+      <c r="H7" s="33" t="s">
         <v>1468</v>
       </c>
-      <c r="H7" s="33" t="s">
-        <v>1469</v>
-      </c>
       <c r="I7" s="33" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="J7" s="130">
         <v>3072</v>
@@ -40992,19 +40981,19 @@
         <v>562</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H8" s="33" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="I8" s="33" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="J8" s="130">
         <v>521</v>
       </c>
       <c r="K8" s="33" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="L8" s="33" t="b">
         <v>1</v>
@@ -54636,7 +54625,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="41" customFormat="1" ht="207" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="131" t="s">
-        <v>1368</v>
+        <v>1482</v>
       </c>
       <c r="B1" s="132"/>
       <c r="C1" s="132"/>
@@ -54663,34 +54652,34 @@
         <v>2</v>
       </c>
       <c r="D2" s="112" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E2" s="113" t="s">
         <v>1369</v>
       </c>
-      <c r="E2" s="113" t="s">
+      <c r="F2" s="113" t="s">
         <v>1370</v>
       </c>
-      <c r="F2" s="113" t="s">
+      <c r="G2" s="113" t="s">
         <v>1371</v>
       </c>
-      <c r="G2" s="113" t="s">
+      <c r="H2" s="114" t="s">
         <v>1372</v>
       </c>
-      <c r="H2" s="114" t="s">
+      <c r="I2" s="115" t="s">
         <v>1373</v>
       </c>
-      <c r="I2" s="115" t="s">
+      <c r="J2" s="115" t="s">
         <v>1374</v>
       </c>
-      <c r="J2" s="115" t="s">
+      <c r="K2" s="113" t="s">
         <v>1375</v>
       </c>
-      <c r="K2" s="113" t="s">
+      <c r="L2" s="113" t="s">
         <v>1376</v>
       </c>
-      <c r="L2" s="113" t="s">
+      <c r="M2" s="113" t="s">
         <v>1377</v>
-      </c>
-      <c r="M2" s="113" t="s">
-        <v>1378</v>
       </c>
       <c r="N2" s="116" t="s">
         <v>428</v>
@@ -54701,29 +54690,29 @@
         <v>5</v>
       </c>
       <c r="B3" s="33" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C3" s="33" t="s">
         <v>1379</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="D3" s="33" t="s">
         <v>1380</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>1381</v>
       </c>
       <c r="E3" s="33" t="s">
         <v>404</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="G3" s="33">
         <v>10</v>
       </c>
       <c r="H3" s="117"/>
       <c r="I3" s="118" t="s">
+        <v>1382</v>
+      </c>
+      <c r="J3" s="118" t="s">
         <v>1383</v>
-      </c>
-      <c r="J3" s="118" t="s">
-        <v>1384</v>
       </c>
       <c r="K3" s="33"/>
       <c r="L3" s="33"/>
@@ -54735,19 +54724,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="33" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C4" s="33" t="s">
         <v>1385</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="D4" s="33" t="s">
         <v>1386</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="E4" s="33" t="s">
         <v>1387</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="F4" s="33" t="s">
         <v>1388</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>1389</v>
       </c>
       <c r="G4" s="33">
         <v>100</v>
@@ -54758,7 +54747,7 @@
       <c r="I4" s="118"/>
       <c r="J4" s="118"/>
       <c r="K4" s="33" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="L4" s="119"/>
       <c r="M4" s="33"/>
@@ -54776,13 +54765,13 @@
       <c r="I5" s="118"/>
       <c r="J5" s="118"/>
       <c r="K5" s="33" t="s">
+        <v>1390</v>
+      </c>
+      <c r="L5" s="34" t="s">
         <v>1391</v>
       </c>
-      <c r="L5" s="34" t="s">
+      <c r="M5" s="33" t="s">
         <v>1392</v>
-      </c>
-      <c r="M5" s="33" t="s">
-        <v>1393</v>
       </c>
       <c r="N5" s="120"/>
     </row>
@@ -54798,10 +54787,10 @@
       <c r="I6" s="118"/>
       <c r="J6" s="118"/>
       <c r="K6" s="33" t="s">
+        <v>1393</v>
+      </c>
+      <c r="L6" s="34" t="s">
         <v>1394</v>
-      </c>
-      <c r="L6" s="34" t="s">
-        <v>1395</v>
       </c>
       <c r="M6" s="33"/>
       <c r="N6" s="120"/>

--- a/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop1/cd3_automation_toolkit/example/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blohumi/Documents/orahub/cd3-automation-toolkit/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354CBC06-C927-3C46-99A0-58EF2561DA03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{806086EE-71F9-B346-A661-61E3318C11B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1940" yWindow="820" windowWidth="29920" windowHeight="17420" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="820" windowWidth="28800" windowHeight="17420" tabRatio="1000" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
@@ -13243,9 +13243,6 @@
     </r>
   </si>
   <si>
-    <t>Oracle GUA IPv6 Enabled</t>
-  </si>
-  <si>
     <t>ULA IPv6 CIDR</t>
   </si>
   <si>
@@ -13898,6 +13895,9 @@
   </si>
   <si>
     <t>Allow group SecurityAdmins to manage security-attribute-namespace in tenancy in tenancy</t>
+  </si>
+  <si>
+    <t>Is Oracle GUA Allocation Enabled</t>
   </si>
 </sst>
 </file>
@@ -14898,6 +14898,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -14975,13 +14982,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -20827,25 +20827,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="250" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="138" t="s">
-        <v>1528</v>
-      </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="138" t="s">
+      <c r="A1" s="140" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="140" t="s">
         <v>1463</v>
       </c>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="140"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="142"/>
     </row>
     <row r="2" spans="1:15" s="40" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
@@ -20861,13 +20861,13 @@
         <v>736</v>
       </c>
       <c r="E2" s="16" t="s">
+        <v>1605</v>
+      </c>
+      <c r="F2" s="16" t="s">
         <v>1525</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>1526</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>1527</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>12</v>
@@ -21121,19 +21121,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="222" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1464</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="144" t="s">
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="146" t="s">
         <v>983</v>
       </c>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
     </row>
     <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -21303,10 +21303,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="40" customFormat="1" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>969</v>
       </c>
-      <c r="B1" s="143"/>
+      <c r="B1" s="145"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -21375,16 +21375,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="103.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>970</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
     </row>
     <row r="2" spans="1:8" s="40" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -21584,30 +21584,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="203.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>971</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="145" t="s">
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="147" t="s">
         <v>972</v>
       </c>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
-      <c r="M1" s="145"/>
-      <c r="N1" s="145"/>
-      <c r="O1" s="145"/>
-      <c r="P1" s="145"/>
-      <c r="Q1" s="145"/>
-      <c r="R1" s="145"/>
-      <c r="S1" s="145"/>
-      <c r="T1" s="145"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
+      <c r="R1" s="147"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="147"/>
     </row>
     <row r="2" spans="1:20" s="40" customFormat="1" ht="59.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -22362,18 +22362,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>973</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
     </row>
     <row r="2" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -22461,17 +22461,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>974</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -22561,25 +22561,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>975</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -22715,28 +22715,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="139" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>960</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="134"/>
-      <c r="T1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
+      <c r="R1" s="136"/>
+      <c r="S1" s="136"/>
+      <c r="T1" s="136"/>
     </row>
     <row r="2" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="47" t="s">
@@ -23714,17 +23714,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="175" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>961</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
+      <c r="B1" s="148"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="148"/>
+      <c r="G1" s="148"/>
+      <c r="H1" s="148"/>
+      <c r="I1" s="148"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
@@ -24111,13 +24111,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="40" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>968</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -24374,19 +24374,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="200" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="149" t="s">
         <v>962</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
     </row>
     <row r="2" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -24560,15 +24560,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>963</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
     </row>
     <row r="2" spans="1:7" s="40" customFormat="1" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -24745,32 +24745,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="250" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="151" t="s">
         <v>1466</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="151"/>
-      <c r="I1" s="138" t="s">
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="153"/>
+      <c r="I1" s="140" t="s">
         <v>1136</v>
       </c>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
-      <c r="Q1" s="139"/>
-      <c r="R1" s="139"/>
-      <c r="S1" s="139"/>
-      <c r="T1" s="139"/>
-      <c r="U1" s="139"/>
-      <c r="V1" s="140"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
+      <c r="V1" s="142"/>
     </row>
     <row r="2" spans="1:22" s="40" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -25223,26 +25223,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="202" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1462</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
-      <c r="Q1" s="139"/>
-      <c r="R1" s="140"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="142"/>
     </row>
     <row r="2" spans="1:18" s="40" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -25481,32 +25481,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="190" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1143</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="152" t="s">
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="142"/>
+      <c r="M1" s="154" t="s">
         <v>1132</v>
       </c>
-      <c r="N1" s="153"/>
-      <c r="O1" s="153"/>
-      <c r="P1" s="153"/>
-      <c r="Q1" s="153"/>
-      <c r="R1" s="153"/>
-      <c r="S1" s="153"/>
-      <c r="T1" s="153"/>
-      <c r="U1" s="153"/>
-      <c r="V1" s="154"/>
+      <c r="N1" s="155"/>
+      <c r="O1" s="155"/>
+      <c r="P1" s="155"/>
+      <c r="Q1" s="155"/>
+      <c r="R1" s="155"/>
+      <c r="S1" s="155"/>
+      <c r="T1" s="155"/>
+      <c r="U1" s="155"/>
+      <c r="V1" s="156"/>
     </row>
     <row r="2" spans="1:22" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
@@ -26021,45 +26021,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="106" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1144</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="149" t="s">
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="142"/>
+      <c r="P1" s="151" t="s">
         <v>1169</v>
       </c>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
-      <c r="V1" s="150"/>
-      <c r="W1" s="150"/>
-      <c r="X1" s="150"/>
-      <c r="Y1" s="150"/>
-      <c r="Z1" s="150"/>
-      <c r="AA1" s="150"/>
-      <c r="AB1" s="150"/>
-      <c r="AC1" s="150"/>
-      <c r="AD1" s="150"/>
-      <c r="AE1" s="150"/>
-      <c r="AF1" s="150"/>
-      <c r="AG1" s="150"/>
-      <c r="AH1" s="150"/>
-      <c r="AI1" s="150"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
+      <c r="V1" s="152"/>
+      <c r="W1" s="152"/>
+      <c r="X1" s="152"/>
+      <c r="Y1" s="152"/>
+      <c r="Z1" s="152"/>
+      <c r="AA1" s="152"/>
+      <c r="AB1" s="152"/>
+      <c r="AC1" s="152"/>
+      <c r="AD1" s="152"/>
+      <c r="AE1" s="152"/>
+      <c r="AF1" s="152"/>
+      <c r="AG1" s="152"/>
+      <c r="AH1" s="152"/>
+      <c r="AI1" s="152"/>
     </row>
     <row r="2" spans="1:35" s="1" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
@@ -26512,27 +26512,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="122.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1150</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
+      <c r="R1" s="136"/>
+      <c r="S1" s="136"/>
     </row>
     <row r="2" spans="1:19" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
@@ -26813,30 +26813,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="119.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1151</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
-      <c r="Q1" s="139"/>
-      <c r="R1" s="139"/>
-      <c r="S1" s="139"/>
-      <c r="T1" s="139"/>
-      <c r="U1" s="139"/>
-      <c r="V1" s="140"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
+      <c r="V1" s="142"/>
     </row>
     <row r="2" spans="1:22" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="34" t="s">
@@ -27166,25 +27166,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="124" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1152</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
     </row>
     <row r="2" spans="1:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
@@ -27427,29 +27427,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="167" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>427</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="141" t="s">
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="143" t="s">
         <v>438</v>
       </c>
-      <c r="K1" s="155"/>
-      <c r="L1" s="155"/>
-      <c r="M1" s="155"/>
-      <c r="N1" s="155"/>
-      <c r="O1" s="155"/>
-      <c r="P1" s="155"/>
-      <c r="Q1" s="155"/>
-      <c r="R1" s="155"/>
-      <c r="S1" s="156"/>
+      <c r="K1" s="157"/>
+      <c r="L1" s="157"/>
+      <c r="M1" s="157"/>
+      <c r="N1" s="157"/>
+      <c r="O1" s="157"/>
+      <c r="P1" s="157"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="158"/>
     </row>
     <row r="2" spans="1:19" ht="58.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
@@ -28149,15 +28149,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="40" customFormat="1" ht="173" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="135" t="s">
+      <c r="A1" s="137" t="s">
         <v>1199</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="137"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="139"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
@@ -28187,10 +28187,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="32" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C3" s="32" t="s">
         <v>1546</v>
-      </c>
-      <c r="C3" s="32" t="s">
-        <v>1547</v>
       </c>
       <c r="D3" s="32"/>
       <c r="E3" s="33"/>
@@ -28202,10 +28202,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="32" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>1548</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>1549</v>
       </c>
       <c r="D4" s="32"/>
       <c r="E4" s="33"/>
@@ -28217,10 +28217,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="32" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C5" s="32" t="s">
         <v>1550</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>1551</v>
       </c>
       <c r="D5" s="32"/>
       <c r="E5" s="33"/>
@@ -28232,10 +28232,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="32" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>1552</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>1553</v>
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="33"/>
@@ -28247,10 +28247,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="32" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C7" s="32" t="s">
         <v>1554</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>1555</v>
       </c>
       <c r="D7" s="32"/>
       <c r="E7" s="19"/>
@@ -28262,10 +28262,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="131" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C8" s="131" t="s">
         <v>1556</v>
-      </c>
-      <c r="C8" s="131" t="s">
-        <v>1557</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="32"/>
@@ -28277,10 +28277,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="32" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C9" s="32" t="s">
         <v>1558</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>1559</v>
       </c>
       <c r="D9" s="32"/>
       <c r="E9" s="32"/>
@@ -28292,10 +28292,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="32" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>1560</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>1561</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="32"/>
@@ -28307,10 +28307,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="32" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C11" s="32" t="s">
         <v>1562</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>1563</v>
       </c>
       <c r="D11" s="32"/>
       <c r="E11" s="32"/>
@@ -28322,10 +28322,10 @@
         <v>5</v>
       </c>
       <c r="B12" s="32" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C12" s="32" t="s">
         <v>1564</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>1565</v>
       </c>
       <c r="D12" s="32"/>
       <c r="E12" s="33"/>
@@ -28337,10 +28337,10 @@
         <v>5</v>
       </c>
       <c r="B13" s="32" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C13" s="32" t="s">
         <v>1566</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>1567</v>
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="33"/>
@@ -28363,15 +28363,15 @@
         <v>5</v>
       </c>
       <c r="B15" s="18" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C15" s="18" t="s">
         <v>1568</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>1569</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="8"/>
       <c r="F15" s="32" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="G15" s="33"/>
     </row>
@@ -28380,15 +28380,15 @@
         <v>5</v>
       </c>
       <c r="B16" s="32" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C16" s="32" t="s">
         <v>1571</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>1572</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
       <c r="F16" s="32" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="G16" s="33"/>
     </row>
@@ -28397,15 +28397,15 @@
         <v>5</v>
       </c>
       <c r="B17" s="32" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C17" s="32" t="s">
         <v>1574</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>1575</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33"/>
       <c r="F17" s="32" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="G17" s="33"/>
     </row>
@@ -28414,15 +28414,15 @@
         <v>5</v>
       </c>
       <c r="B18" s="32" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C18" s="32" t="s">
         <v>1577</v>
-      </c>
-      <c r="C18" s="32" t="s">
-        <v>1578</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="33"/>
       <c r="F18" s="32" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="G18" s="33"/>
     </row>
@@ -28459,14 +28459,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="40" customFormat="1" ht="44.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>428</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="143"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="145"/>
     </row>
     <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
@@ -28613,12 +28613,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="147" t="s">
         <v>1153</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="137"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="139"/>
     </row>
     <row r="2" spans="1:4" ht="79" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
@@ -28720,22 +28720,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>771</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="140"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="142"/>
     </row>
     <row r="2" spans="1:14" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
@@ -29279,20 +29279,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>771</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
     </row>
     <row r="2" spans="1:12" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
@@ -29507,28 +29507,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="216" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
-        <v>1529</v>
-      </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="134"/>
-      <c r="T1" s="134"/>
+      <c r="A1" s="136" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
+      <c r="R1" s="136"/>
+      <c r="S1" s="136"/>
+      <c r="T1" s="136"/>
     </row>
     <row r="2" spans="1:20" ht="53" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
@@ -29541,7 +29541,7 @@
         <v>791</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="E2" s="16" t="s">
         <v>1137</v>
@@ -29559,16 +29559,16 @@
         <v>313</v>
       </c>
       <c r="J2" s="16" t="s">
+        <v>1530</v>
+      </c>
+      <c r="K2" s="16" t="s">
         <v>1531</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="L2" s="16" t="s">
         <v>1532</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="M2" s="16" t="s">
         <v>1533</v>
-      </c>
-      <c r="M2" s="16" t="s">
-        <v>1534</v>
       </c>
       <c r="N2" s="16" t="s">
         <v>793</v>
@@ -29637,20 +29637,20 @@
         <v>328</v>
       </c>
       <c r="J4" s="53" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="K4" s="53"/>
       <c r="L4" s="53" t="b">
         <v>1</v>
       </c>
       <c r="M4" s="54" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="N4" s="53" t="s">
         <v>317</v>
       </c>
       <c r="O4" s="54" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="P4" s="53" t="s">
         <v>406</v>
@@ -29672,39 +29672,39 @@
         <v>553</v>
       </c>
       <c r="C5" s="54" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D5" s="54" t="s">
         <v>1538</v>
-      </c>
-      <c r="D5" s="54" t="s">
-        <v>1539</v>
       </c>
       <c r="E5" s="54" t="s">
         <v>1161</v>
       </c>
       <c r="F5" s="54"/>
       <c r="G5" s="54" t="s">
+        <v>1539</v>
+      </c>
+      <c r="H5" s="54"/>
+      <c r="I5" s="134" t="s">
         <v>1540</v>
       </c>
-      <c r="H5" s="54"/>
-      <c r="I5" s="164" t="s">
+      <c r="J5" s="54" t="s">
         <v>1541</v>
       </c>
-      <c r="J5" s="54" t="s">
+      <c r="K5" s="54" t="s">
         <v>1542</v>
-      </c>
-      <c r="K5" s="54" t="s">
-        <v>1543</v>
       </c>
       <c r="L5" s="54" t="b">
         <v>1</v>
       </c>
       <c r="M5" s="54" t="s">
+        <v>1543</v>
+      </c>
+      <c r="N5" s="54" t="s">
         <v>1544</v>
       </c>
-      <c r="N5" s="54" t="s">
-        <v>1545</v>
-      </c>
       <c r="O5" s="54" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="P5" s="54" t="s">
         <v>324</v>
@@ -29904,35 +29904,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="1" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1162</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
-      <c r="Q1" s="139"/>
-      <c r="R1" s="139"/>
-      <c r="S1" s="139"/>
-      <c r="T1" s="139"/>
-      <c r="U1" s="139"/>
-      <c r="V1" s="139"/>
-      <c r="W1" s="139"/>
-      <c r="X1" s="139"/>
-      <c r="Y1" s="139"/>
-      <c r="Z1" s="139"/>
-      <c r="AA1" s="140"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
+      <c r="V1" s="141"/>
+      <c r="W1" s="141"/>
+      <c r="X1" s="141"/>
+      <c r="Y1" s="141"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="142"/>
     </row>
     <row r="2" spans="1:27" s="48" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="49" t="s">
@@ -33299,16 +33299,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="119.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>965</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
     </row>
     <row r="2" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="65" t="s">
@@ -36217,29 +36217,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="1" customFormat="1" ht="195" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="151" t="s">
         <v>1164</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="152"/>
+      <c r="I1" s="152"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
       <c r="V1" s="71"/>
       <c r="W1" s="71"/>
       <c r="X1" s="71"/>
@@ -40685,26 +40685,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="159" t="s">
         <v>1461</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
-      <c r="R1" s="159"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
+      <c r="J1" s="160"/>
+      <c r="K1" s="160"/>
+      <c r="L1" s="160"/>
+      <c r="M1" s="160"/>
+      <c r="N1" s="160"/>
+      <c r="O1" s="160"/>
+      <c r="P1" s="160"/>
+      <c r="Q1" s="160"/>
+      <c r="R1" s="161"/>
       <c r="S1" s="13"/>
     </row>
     <row r="2" spans="1:19" s="48" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40957,22 +40957,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="151" t="s">
         <v>1167</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
+      <c r="J1" s="160"/>
+      <c r="K1" s="160"/>
+      <c r="L1" s="160"/>
+      <c r="M1" s="160"/>
+      <c r="N1" s="160"/>
     </row>
     <row r="2" spans="1:15" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="35" t="s">
@@ -41194,16 +41194,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="40" customFormat="1" ht="166" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1202</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="137"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="139"/>
     </row>
     <row r="2" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -42184,26 +42184,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="292" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="162" t="s">
         <v>966</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="161"/>
-      <c r="G1" s="161"/>
-      <c r="H1" s="161"/>
-      <c r="I1" s="161"/>
-      <c r="J1" s="161"/>
-      <c r="K1" s="161"/>
-      <c r="L1" s="161"/>
-      <c r="M1" s="161"/>
-      <c r="N1" s="161"/>
-      <c r="O1" s="161"/>
-      <c r="P1" s="161"/>
-      <c r="Q1" s="161"/>
-      <c r="R1" s="162"/>
+      <c r="B1" s="163"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="163"/>
+      <c r="G1" s="163"/>
+      <c r="H1" s="163"/>
+      <c r="I1" s="163"/>
+      <c r="J1" s="163"/>
+      <c r="K1" s="163"/>
+      <c r="L1" s="163"/>
+      <c r="M1" s="163"/>
+      <c r="N1" s="163"/>
+      <c r="O1" s="163"/>
+      <c r="P1" s="163"/>
+      <c r="Q1" s="163"/>
+      <c r="R1" s="164"/>
     </row>
     <row r="2" spans="1:18" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -42557,25 +42557,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="234" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1465</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="145" t="s">
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="147" t="s">
         <v>1103</v>
       </c>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
     </row>
     <row r="2" spans="1:15" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
@@ -43862,39 +43862,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="212" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="165" t="s">
         <v>1467</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="159"/>
-      <c r="I1" s="149" t="s">
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="151" t="s">
         <v>1468</v>
       </c>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
-      <c r="V1" s="150"/>
-      <c r="W1" s="150"/>
-      <c r="X1" s="150"/>
-      <c r="Y1" s="150"/>
-      <c r="Z1" s="150"/>
-      <c r="AA1" s="150"/>
-      <c r="AB1" s="150"/>
-      <c r="AC1" s="150"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
+      <c r="V1" s="152"/>
+      <c r="W1" s="152"/>
+      <c r="X1" s="152"/>
+      <c r="Y1" s="152"/>
+      <c r="Z1" s="152"/>
+      <c r="AA1" s="152"/>
+      <c r="AB1" s="152"/>
+      <c r="AC1" s="152"/>
     </row>
     <row r="2" spans="1:29" s="40" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="35" t="s">
@@ -50137,16 +50137,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:81" ht="185" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1508</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
       <c r="I1" s="133"/>
       <c r="J1" s="1"/>
     </row>
@@ -59541,14 +59541,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="40" customFormat="1" ht="134.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1004</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="137"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="139"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -59613,16 +59613,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="40" customFormat="1" ht="131" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1203</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
     </row>
     <row r="2" spans="1:9" s="40" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
@@ -59687,21 +59687,21 @@
         <v>5</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="C5" s="32" t="s">
         <v>397</v>
       </c>
       <c r="D5" s="32" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E5" s="32" t="s">
         <v>1581</v>
-      </c>
-      <c r="E5" s="32" t="s">
-        <v>1582</v>
       </c>
       <c r="F5" s="32"/>
       <c r="G5" s="32"/>
       <c r="H5" s="32" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="I5" s="33"/>
     </row>
@@ -59711,7 +59711,7 @@
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="E6" s="32" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -59724,7 +59724,7 @@
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="E7" s="32" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -60081,7 +60081,7 @@
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="E36" s="32" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F36" s="32"/>
       <c r="G36" s="32"/>
@@ -60473,7 +60473,7 @@
       <c r="C68" s="32"/>
       <c r="D68" s="32"/>
       <c r="E68" s="32" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="F68" s="32"/>
       <c r="G68" s="32"/>
@@ -60485,7 +60485,7 @@
       <c r="C69" s="32"/>
       <c r="D69" s="32"/>
       <c r="E69" s="32" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="F69" s="32"/>
       <c r="G69" s="32"/>
@@ -60497,7 +60497,7 @@
       <c r="C70" s="32"/>
       <c r="D70" s="32"/>
       <c r="E70" s="32" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="F70" s="32"/>
       <c r="G70" s="32"/>
@@ -60509,7 +60509,7 @@
       <c r="C71" s="32"/>
       <c r="D71" s="32"/>
       <c r="E71" s="32" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="F71" s="32"/>
       <c r="G71" s="32"/>
@@ -60521,7 +60521,7 @@
       <c r="C72" s="32"/>
       <c r="D72" s="32"/>
       <c r="E72" s="32" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="F72" s="32"/>
       <c r="G72" s="32"/>
@@ -60533,7 +60533,7 @@
       <c r="C73" s="32"/>
       <c r="D73" s="32"/>
       <c r="E73" s="32" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="F73" s="32"/>
       <c r="G73" s="32"/>
@@ -60545,7 +60545,7 @@
       <c r="C74" s="32"/>
       <c r="D74" s="32"/>
       <c r="E74" s="32" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="F74" s="32"/>
       <c r="G74" s="32"/>
@@ -60557,7 +60557,7 @@
       <c r="C75" s="32"/>
       <c r="D75" s="32"/>
       <c r="E75" s="32" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="F75" s="32"/>
       <c r="G75" s="32"/>
@@ -60569,7 +60569,7 @@
       <c r="C76" s="32"/>
       <c r="D76" s="32"/>
       <c r="E76" s="32" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="F76" s="32"/>
       <c r="G76" s="32"/>
@@ -60581,7 +60581,7 @@
       <c r="C77" s="32"/>
       <c r="D77" s="32"/>
       <c r="E77" s="32" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="F77" s="32"/>
       <c r="G77" s="32"/>
@@ -60600,7 +60600,7 @@
       <c r="D78" s="32" t="s">
         <v>1012</v>
       </c>
-      <c r="E78" s="165" t="s">
+      <c r="E78" s="135" t="s">
         <v>1265</v>
       </c>
       <c r="F78" s="32"/>
@@ -61261,7 +61261,7 @@
       <c r="C131" s="32"/>
       <c r="D131" s="32"/>
       <c r="E131" s="32" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="F131" s="32"/>
       <c r="G131" s="32"/>
@@ -61273,7 +61273,7 @@
       <c r="C132" s="32"/>
       <c r="D132" s="32"/>
       <c r="E132" s="32" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="F132" s="32"/>
       <c r="G132" s="32"/>
@@ -61937,7 +61937,7 @@
       <c r="C186" s="32"/>
       <c r="D186" s="32"/>
       <c r="E186" s="32" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="F186" s="32"/>
       <c r="G186" s="32"/>
@@ -61949,7 +61949,7 @@
       <c r="C187" s="32"/>
       <c r="D187" s="32"/>
       <c r="E187" s="32" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="F187" s="32"/>
       <c r="G187" s="32"/>
@@ -61961,7 +61961,7 @@
       <c r="C188" s="32"/>
       <c r="D188" s="32"/>
       <c r="E188" s="32" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F188" s="32"/>
       <c r="G188" s="32"/>
@@ -62493,7 +62493,7 @@
       <c r="C231" s="32"/>
       <c r="D231" s="32"/>
       <c r="E231" s="32" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="F231" s="32"/>
       <c r="G231" s="32"/>
@@ -62619,7 +62619,7 @@
       <c r="C242" s="33"/>
       <c r="D242" s="33"/>
       <c r="E242" s="32" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="F242" s="33"/>
       <c r="G242" s="33"/>
@@ -62631,7 +62631,7 @@
       <c r="C243" s="33"/>
       <c r="D243" s="33"/>
       <c r="E243" s="32" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="F243" s="33"/>
       <c r="G243" s="33"/>
@@ -62643,7 +62643,7 @@
       <c r="C244" s="33"/>
       <c r="D244" s="33"/>
       <c r="E244" s="32" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="F244" s="33"/>
       <c r="G244" s="33"/>
@@ -63276,19 +63276,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="174" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>669</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="141" t="s">
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="143" t="s">
         <v>953</v>
       </c>
-      <c r="H1" s="142"/>
-      <c r="I1" s="143"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="145"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="37" t="s">
@@ -63653,13 +63653,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="40" customFormat="1" ht="92" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1027</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
@@ -63743,22 +63743,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="40" customFormat="1" ht="207" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1135</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
-      <c r="N1" s="137"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
+      <c r="K1" s="138"/>
+      <c r="L1" s="138"/>
+      <c r="M1" s="138"/>
+      <c r="N1" s="139"/>
     </row>
     <row r="2" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">

--- a/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blohumi/Documents/orahub/cd3-automation-toolkit/cd3_automation_toolkit/example/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PyCharmProjects/orahub-develop1/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{806086EE-71F9-B346-A661-61E3318C11B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02844B1-D3BD-2842-B6E6-FD23A74C50B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="820" windowWidth="28800" windowHeight="17420" tabRatio="1000" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="17400" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>

--- a/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44D9C27-2B1C-1644-87E3-FAB4EB1FC086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26C138A-F573-3345-9E6B-EEEEC667984A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="27080" windowHeight="17400" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -883,7 +883,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2847" uniqueCount="1623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2848" uniqueCount="1624">
   <si>
     <t>Region</t>
   </si>
@@ -13815,6 +13815,9 @@
   </si>
   <si>
     <t>Network@PHXEBS-VCN::qa-subnet</t>
+  </si>
+  <si>
+    <t>Plugin OS Management Service Agent</t>
   </si>
 </sst>
 </file>
@@ -14817,6 +14820,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -14895,8 +14900,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -20741,25 +20744,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="250" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1522</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="138" t="s">
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="140" t="s">
         <v>1459</v>
       </c>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="140"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="142"/>
     </row>
     <row r="2" spans="1:15" s="40" customFormat="1" ht="45" customHeight="1">
       <c r="A2" s="6" t="s">
@@ -21035,19 +21038,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="222" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1460</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="144" t="s">
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="146" t="s">
         <v>982</v>
       </c>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
     </row>
     <row r="2" spans="1:9" ht="16">
       <c r="A2" s="26" t="s">
@@ -21217,10 +21220,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="40" customFormat="1" ht="92.25" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>968</v>
       </c>
-      <c r="B1" s="143"/>
+      <c r="B1" s="145"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="9" t="s">
@@ -21289,16 +21292,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="103.75" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>969</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
     </row>
     <row r="2" spans="1:8" s="40" customFormat="1" ht="43.5" customHeight="1">
       <c r="A2" s="26" t="s">
@@ -21498,30 +21501,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="203.25" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>970</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="145" t="s">
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="147" t="s">
         <v>971</v>
       </c>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
-      <c r="M1" s="145"/>
-      <c r="N1" s="145"/>
-      <c r="O1" s="145"/>
-      <c r="P1" s="145"/>
-      <c r="Q1" s="145"/>
-      <c r="R1" s="145"/>
-      <c r="S1" s="145"/>
-      <c r="T1" s="145"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
+      <c r="R1" s="147"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="147"/>
     </row>
     <row r="2" spans="1:21" s="40" customFormat="1" ht="59.5" customHeight="1">
       <c r="A2" s="26" t="s">
@@ -22295,18 +22298,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="63" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>972</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
     </row>
     <row r="2" spans="1:11" ht="29.25" customHeight="1">
       <c r="A2" s="26" t="s">
@@ -22394,17 +22397,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="63" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>973</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="9" t="s">
@@ -22494,25 +22497,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="60" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>974</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="9" t="s">
@@ -22648,28 +22651,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="139" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>959</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="134"/>
-      <c r="T1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
+      <c r="R1" s="136"/>
+      <c r="S1" s="136"/>
+      <c r="T1" s="136"/>
     </row>
     <row r="2" spans="1:20" ht="16">
       <c r="A2" s="47" t="s">
@@ -23647,17 +23650,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="175" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>960</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
+      <c r="B1" s="148"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="148"/>
+      <c r="G1" s="148"/>
+      <c r="H1" s="148"/>
+      <c r="I1" s="148"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="6" t="s">
@@ -24044,13 +24047,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="40" customFormat="1" ht="108" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>967</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="26" t="s">
@@ -24307,19 +24310,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="200" customHeight="1">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="149" t="s">
         <v>961</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
     </row>
     <row r="2" spans="1:11" ht="32">
       <c r="A2" s="26" t="s">
@@ -24493,15 +24496,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="89.25" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>962</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
     </row>
     <row r="2" spans="1:7" s="40" customFormat="1" ht="28.75" customHeight="1">
       <c r="A2" s="26" t="s">
@@ -24652,7 +24655,7 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:AJ8"/>
+  <dimension ref="A1:AK8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
@@ -24668,7 +24671,7 @@
     <col min="11" max="11" width="10" customWidth="1"/>
     <col min="12" max="12" width="11.33203125" customWidth="1"/>
     <col min="13" max="13" width="12.83203125" customWidth="1"/>
-    <col min="14" max="14" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15.6640625" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="12.1640625" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="16.1640625" hidden="1" customWidth="1"/>
@@ -24683,57 +24686,59 @@
     <col min="26" max="26" width="17.6640625" hidden="1" customWidth="1"/>
     <col min="27" max="27" width="16.6640625" hidden="1" customWidth="1"/>
     <col min="28" max="28" width="14.1640625" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="2.33203125" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.33203125" customWidth="1"/>
-    <col min="36" max="36" width="21.33203125" customWidth="1"/>
+    <col min="29" max="29" width="12" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="6.6640625" customWidth="1"/>
+    <col min="31" max="31" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.33203125" customWidth="1"/>
+    <col min="37" max="37" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="250" customHeight="1">
-      <c r="A1" s="149" t="s">
+    <row r="1" spans="1:37" ht="250" customHeight="1">
+      <c r="A1" s="151" t="s">
         <v>1462</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="151"/>
-      <c r="I1" s="134" t="s">
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="153"/>
+      <c r="I1" s="136" t="s">
         <v>1604</v>
       </c>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
-      <c r="N1" s="136"/>
-      <c r="O1" s="136"/>
-      <c r="P1" s="136"/>
-      <c r="Q1" s="136"/>
-      <c r="R1" s="136"/>
-      <c r="S1" s="136"/>
-      <c r="T1" s="136"/>
-      <c r="U1" s="136"/>
-      <c r="V1" s="136"/>
-      <c r="W1" s="136"/>
-      <c r="X1" s="136"/>
-      <c r="Y1" s="136"/>
-      <c r="Z1" s="136"/>
-      <c r="AA1" s="136"/>
-      <c r="AB1" s="136"/>
-      <c r="AC1" s="136"/>
-      <c r="AD1" s="136"/>
-      <c r="AE1" s="136"/>
-      <c r="AF1" s="136"/>
-      <c r="AG1" s="136"/>
-      <c r="AH1" s="136"/>
-      <c r="AI1" s="136"/>
-      <c r="AJ1" s="137"/>
-    </row>
-    <row r="2" spans="1:36" s="40" customFormat="1" ht="52.5" customHeight="1">
+      <c r="J1" s="138"/>
+      <c r="K1" s="138"/>
+      <c r="L1" s="138"/>
+      <c r="M1" s="138"/>
+      <c r="N1" s="138"/>
+      <c r="O1" s="138"/>
+      <c r="P1" s="138"/>
+      <c r="Q1" s="138"/>
+      <c r="R1" s="138"/>
+      <c r="S1" s="138"/>
+      <c r="T1" s="138"/>
+      <c r="U1" s="138"/>
+      <c r="V1" s="138"/>
+      <c r="W1" s="138"/>
+      <c r="X1" s="138"/>
+      <c r="Y1" s="138"/>
+      <c r="Z1" s="138"/>
+      <c r="AA1" s="138"/>
+      <c r="AB1" s="138"/>
+      <c r="AC1" s="138"/>
+      <c r="AD1" s="138"/>
+      <c r="AE1" s="138"/>
+      <c r="AF1" s="138"/>
+      <c r="AG1" s="138"/>
+      <c r="AH1" s="138"/>
+      <c r="AI1" s="138"/>
+      <c r="AJ1" s="138"/>
+      <c r="AK1" s="139"/>
+    </row>
+    <row r="2" spans="1:37" s="40" customFormat="1" ht="52.5" customHeight="1">
       <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
@@ -24819,31 +24824,34 @@
         <v>1617</v>
       </c>
       <c r="AC2" s="27" t="s">
+        <v>1623</v>
+      </c>
+      <c r="AD2" s="27" t="s">
         <v>1618</v>
       </c>
-      <c r="AD2" s="26" t="s">
+      <c r="AE2" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="AE2" s="26" t="s">
+      <c r="AF2" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="AF2" s="27" t="s">
+      <c r="AG2" s="27" t="s">
         <v>548</v>
       </c>
-      <c r="AG2" s="26" t="s">
+      <c r="AH2" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="AH2" s="27" t="s">
+      <c r="AI2" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="AI2" s="27" t="s">
+      <c r="AJ2" s="27" t="s">
         <v>900</v>
       </c>
-      <c r="AJ2" s="26" t="s">
+      <c r="AK2" s="26" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="34" customHeight="1">
+    <row r="3" spans="1:37" ht="34" customHeight="1">
       <c r="A3" s="33" t="s">
         <v>315</v>
       </c>
@@ -24871,7 +24879,7 @@
       <c r="I3" s="33" t="s">
         <v>431</v>
       </c>
-      <c r="J3" s="164" t="s">
+      <c r="J3" s="134" t="s">
         <v>1621</v>
       </c>
       <c r="K3" s="33">
@@ -24895,19 +24903,20 @@
       <c r="AA3" s="33"/>
       <c r="AB3" s="33"/>
       <c r="AC3" s="33"/>
-      <c r="AD3" s="33" t="s">
+      <c r="AD3" s="33"/>
+      <c r="AE3" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="AE3" s="33" t="s">
+      <c r="AF3" s="33" t="s">
         <v>647</v>
       </c>
-      <c r="AF3" s="33"/>
       <c r="AG3" s="33"/>
       <c r="AH3" s="33"/>
       <c r="AI3" s="33"/>
       <c r="AJ3" s="33"/>
-    </row>
-    <row r="4" spans="1:36" ht="28.75" customHeight="1">
+      <c r="AK3" s="33"/>
+    </row>
+    <row r="4" spans="1:37" ht="28.75" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>4</v>
       </c>
@@ -24932,15 +24941,15 @@
       <c r="T4" s="8"/>
       <c r="U4" s="8"/>
       <c r="V4" s="33"/>
-      <c r="AD4" s="8"/>
-      <c r="AE4" s="33"/>
+      <c r="AE4" s="8"/>
       <c r="AF4" s="33"/>
-      <c r="AG4" s="8"/>
+      <c r="AG4" s="33"/>
       <c r="AH4" s="8"/>
       <c r="AI4" s="8"/>
-      <c r="AJ4" s="33"/>
-    </row>
-    <row r="5" spans="1:36" ht="128">
+      <c r="AJ4" s="8"/>
+      <c r="AK4" s="33"/>
+    </row>
+    <row r="5" spans="1:37" ht="48">
       <c r="A5" s="53" t="s">
         <v>5</v>
       </c>
@@ -24992,27 +25001,28 @@
       <c r="AA5" s="53"/>
       <c r="AB5" s="53"/>
       <c r="AC5" s="53"/>
-      <c r="AD5" s="53" t="s">
+      <c r="AD5" s="53"/>
+      <c r="AE5" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="AE5" s="53" t="s">
+      <c r="AF5" s="53" t="s">
         <v>549</v>
       </c>
-      <c r="AF5" s="53" t="s">
+      <c r="AG5" s="53" t="s">
         <v>364</v>
       </c>
-      <c r="AG5" s="53"/>
-      <c r="AH5" s="53" t="s">
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="AI5" s="54" t="s">
+      <c r="AJ5" s="54" t="s">
         <v>993</v>
       </c>
-      <c r="AJ5" s="54" t="s">
+      <c r="AK5" s="54" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="96">
+    <row r="6" spans="1:37" ht="32">
       <c r="A6" s="53" t="s">
         <v>5</v>
       </c>
@@ -25038,18 +25048,18 @@
       <c r="I6" s="53" t="s">
         <v>433</v>
       </c>
-      <c r="J6" s="165" t="s">
+      <c r="J6" s="135" t="s">
         <v>104</v>
       </c>
-      <c r="K6" s="165">
+      <c r="K6" s="135">
         <v>16</v>
       </c>
-      <c r="L6" s="165">
+      <c r="L6" s="135">
         <v>55</v>
       </c>
-      <c r="M6" s="165"/>
-      <c r="N6" s="165"/>
-      <c r="O6" s="165"/>
+      <c r="M6" s="135"/>
+      <c r="N6" s="135"/>
+      <c r="O6" s="135"/>
       <c r="P6" s="53"/>
       <c r="Q6" s="53"/>
       <c r="R6" s="53"/>
@@ -25064,23 +25074,24 @@
       <c r="AA6" s="53"/>
       <c r="AB6" s="53"/>
       <c r="AC6" s="53"/>
-      <c r="AD6" s="53" t="s">
+      <c r="AD6" s="53"/>
+      <c r="AE6" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="AE6" s="53" t="s">
+      <c r="AF6" s="53" t="s">
         <v>389</v>
       </c>
-      <c r="AF6" s="53"/>
-      <c r="AG6" s="53" t="s">
+      <c r="AG6" s="53"/>
+      <c r="AH6" s="53" t="s">
         <v>387</v>
       </c>
-      <c r="AH6" s="53"/>
-      <c r="AI6" s="54" t="s">
+      <c r="AI6" s="53"/>
+      <c r="AJ6" s="54" t="s">
         <v>994</v>
       </c>
-      <c r="AJ6" s="53"/>
-    </row>
-    <row r="7" spans="1:36" ht="96">
+      <c r="AK6" s="53"/>
+    </row>
+    <row r="7" spans="1:37" ht="48">
       <c r="A7" s="53" t="s">
         <v>5</v>
       </c>
@@ -25106,14 +25117,14 @@
       <c r="I7" s="53" t="s">
         <v>432</v>
       </c>
-      <c r="J7" s="165" t="s">
+      <c r="J7" s="135" t="s">
         <v>104</v>
       </c>
-      <c r="K7" s="165"/>
-      <c r="L7" s="165"/>
-      <c r="M7" s="165"/>
-      <c r="N7" s="165"/>
-      <c r="O7" s="165"/>
+      <c r="K7" s="135"/>
+      <c r="L7" s="135"/>
+      <c r="M7" s="135"/>
+      <c r="N7" s="135"/>
+      <c r="O7" s="135"/>
       <c r="P7" s="53"/>
       <c r="Q7" s="53"/>
       <c r="R7" s="53"/>
@@ -25128,21 +25139,22 @@
       <c r="AA7" s="53"/>
       <c r="AB7" s="53"/>
       <c r="AC7" s="53"/>
-      <c r="AD7" s="53" t="s">
+      <c r="AD7" s="53"/>
+      <c r="AE7" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="AE7" s="53" t="s">
+      <c r="AF7" s="53" t="s">
         <v>389</v>
       </c>
-      <c r="AF7" s="53"/>
-      <c r="AG7" s="53" t="s">
+      <c r="AG7" s="53"/>
+      <c r="AH7" s="53" t="s">
         <v>388</v>
       </c>
-      <c r="AH7" s="53"/>
       <c r="AI7" s="53"/>
       <c r="AJ7" s="53"/>
-    </row>
-    <row r="8" spans="1:36" ht="96">
+      <c r="AK7" s="53"/>
+    </row>
+    <row r="8" spans="1:37" ht="48">
       <c r="A8" s="53" t="s">
         <v>5</v>
       </c>
@@ -25168,14 +25180,14 @@
       <c r="I8" s="53" t="s">
         <v>796</v>
       </c>
-      <c r="J8" s="165" t="s">
+      <c r="J8" s="135" t="s">
         <v>104</v>
       </c>
-      <c r="K8" s="165"/>
-      <c r="L8" s="165"/>
-      <c r="M8" s="165"/>
-      <c r="N8" s="165"/>
-      <c r="O8" s="165"/>
+      <c r="K8" s="135"/>
+      <c r="L8" s="135"/>
+      <c r="M8" s="135"/>
+      <c r="N8" s="135"/>
+      <c r="O8" s="135"/>
       <c r="P8" s="53"/>
       <c r="Q8" s="53"/>
       <c r="R8" s="53"/>
@@ -25190,27 +25202,28 @@
       <c r="AA8" s="53"/>
       <c r="AB8" s="53"/>
       <c r="AC8" s="53"/>
-      <c r="AD8" s="53" t="s">
+      <c r="AD8" s="53"/>
+      <c r="AE8" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="AE8" s="53" t="s">
+      <c r="AF8" s="53" t="s">
         <v>389</v>
       </c>
-      <c r="AF8" s="53"/>
-      <c r="AG8" s="53" t="s">
+      <c r="AG8" s="53"/>
+      <c r="AH8" s="53" t="s">
         <v>388</v>
       </c>
-      <c r="AH8" s="53"/>
       <c r="AI8" s="53"/>
       <c r="AJ8" s="53"/>
+      <c r="AK8" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="I1:AJ1"/>
+    <mergeCell ref="I1:AK1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="E1:XFD2 A1:C2 AD9:AJ1048576 H3:P1048576 D1:D1048576 AK3:XFD1048576 S3:AC1048576 AD3:AD8 AG3:AJ8" xr:uid="{F7DC7C30-2DF3-6E41-97D2-D6C5AC5CC012}"/>
+    <dataValidation allowBlank="1" sqref="E1:XFD2 A1:C2 AE9:AK1048576 H3:P1048576 D1:D1048576 AL3:XFD1048576 S3:AD1048576 AE3:AE8 AH3:AK8" xr:uid="{F7DC7C30-2DF3-6E41-97D2-D6C5AC5CC012}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -25249,26 +25262,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="202" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1458</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
-      <c r="Q1" s="139"/>
-      <c r="R1" s="140"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="142"/>
     </row>
     <row r="2" spans="1:18" s="40" customFormat="1" ht="48">
       <c r="A2" s="26" t="s">
@@ -25507,32 +25520,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="190" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1139</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="152" t="s">
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="142"/>
+      <c r="M1" s="154" t="s">
         <v>1131</v>
       </c>
-      <c r="N1" s="153"/>
-      <c r="O1" s="153"/>
-      <c r="P1" s="153"/>
-      <c r="Q1" s="153"/>
-      <c r="R1" s="153"/>
-      <c r="S1" s="153"/>
-      <c r="T1" s="153"/>
-      <c r="U1" s="153"/>
-      <c r="V1" s="154"/>
+      <c r="N1" s="155"/>
+      <c r="O1" s="155"/>
+      <c r="P1" s="155"/>
+      <c r="Q1" s="155"/>
+      <c r="R1" s="155"/>
+      <c r="S1" s="155"/>
+      <c r="T1" s="155"/>
+      <c r="U1" s="155"/>
+      <c r="V1" s="156"/>
     </row>
     <row r="2" spans="1:22" s="1" customFormat="1" ht="63" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -26047,45 +26060,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="106" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1140</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="149" t="s">
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="142"/>
+      <c r="P1" s="151" t="s">
         <v>1165</v>
       </c>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
-      <c r="V1" s="150"/>
-      <c r="W1" s="150"/>
-      <c r="X1" s="150"/>
-      <c r="Y1" s="150"/>
-      <c r="Z1" s="150"/>
-      <c r="AA1" s="150"/>
-      <c r="AB1" s="150"/>
-      <c r="AC1" s="150"/>
-      <c r="AD1" s="150"/>
-      <c r="AE1" s="150"/>
-      <c r="AF1" s="150"/>
-      <c r="AG1" s="150"/>
-      <c r="AH1" s="150"/>
-      <c r="AI1" s="150"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
+      <c r="V1" s="152"/>
+      <c r="W1" s="152"/>
+      <c r="X1" s="152"/>
+      <c r="Y1" s="152"/>
+      <c r="Z1" s="152"/>
+      <c r="AA1" s="152"/>
+      <c r="AB1" s="152"/>
+      <c r="AC1" s="152"/>
+      <c r="AD1" s="152"/>
+      <c r="AE1" s="152"/>
+      <c r="AF1" s="152"/>
+      <c r="AG1" s="152"/>
+      <c r="AH1" s="152"/>
+      <c r="AI1" s="152"/>
     </row>
     <row r="2" spans="1:35" s="1" customFormat="1" ht="64">
       <c r="A2" s="27" t="s">
@@ -26538,27 +26551,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="122.5" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1146</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
+      <c r="R1" s="136"/>
+      <c r="S1" s="136"/>
     </row>
     <row r="2" spans="1:19" ht="43" customHeight="1">
       <c r="A2" s="16" t="s">
@@ -26839,30 +26852,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="119.25" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1147</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
-      <c r="Q1" s="139"/>
-      <c r="R1" s="139"/>
-      <c r="S1" s="139"/>
-      <c r="T1" s="139"/>
-      <c r="U1" s="139"/>
-      <c r="V1" s="140"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
+      <c r="V1" s="142"/>
     </row>
     <row r="2" spans="1:22" ht="58.5" customHeight="1">
       <c r="A2" s="34" t="s">
@@ -27192,25 +27205,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="124" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1148</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
     </row>
     <row r="2" spans="1:17" ht="46.5" customHeight="1">
       <c r="A2" s="10" t="s">
@@ -27453,29 +27466,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="167" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>427</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="141" t="s">
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="143" t="s">
         <v>438</v>
       </c>
-      <c r="K1" s="155"/>
-      <c r="L1" s="155"/>
-      <c r="M1" s="155"/>
-      <c r="N1" s="155"/>
-      <c r="O1" s="155"/>
-      <c r="P1" s="155"/>
-      <c r="Q1" s="155"/>
-      <c r="R1" s="155"/>
-      <c r="S1" s="156"/>
+      <c r="K1" s="157"/>
+      <c r="L1" s="157"/>
+      <c r="M1" s="157"/>
+      <c r="N1" s="157"/>
+      <c r="O1" s="157"/>
+      <c r="P1" s="157"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="158"/>
     </row>
     <row r="2" spans="1:19" ht="58.75" customHeight="1">
       <c r="A2" s="10" t="s">
@@ -28175,15 +28188,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="40" customFormat="1" ht="173" customHeight="1">
-      <c r="A1" s="135" t="s">
+      <c r="A1" s="137" t="s">
         <v>1195</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="137"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="139"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="104" t="s">
@@ -28485,14 +28498,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="40" customFormat="1" ht="44.5" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>428</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="143"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="145"/>
     </row>
     <row r="2" spans="1:6" ht="14.5" customHeight="1">
       <c r="A2" s="16" t="s">
@@ -28639,12 +28652,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="64" customHeight="1">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="147" t="s">
         <v>1149</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="137"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="139"/>
     </row>
     <row r="2" spans="1:4" ht="79" customHeight="1">
       <c r="A2" s="16" t="s">
@@ -28746,22 +28759,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>770</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="140"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="142"/>
     </row>
     <row r="2" spans="1:14" ht="58" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -29305,20 +29318,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="22" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>770</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
     </row>
     <row r="2" spans="1:12" ht="72.75" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -29533,28 +29546,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="216" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1523</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="134"/>
-      <c r="T1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
+      <c r="R1" s="136"/>
+      <c r="S1" s="136"/>
+      <c r="T1" s="136"/>
     </row>
     <row r="2" spans="1:20" ht="53" customHeight="1">
       <c r="A2" s="16" t="s">
@@ -29934,35 +29947,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="1" customFormat="1" ht="135.75" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>1158</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
-      <c r="Q1" s="139"/>
-      <c r="R1" s="139"/>
-      <c r="S1" s="139"/>
-      <c r="T1" s="139"/>
-      <c r="U1" s="139"/>
-      <c r="V1" s="139"/>
-      <c r="W1" s="139"/>
-      <c r="X1" s="139"/>
-      <c r="Y1" s="139"/>
-      <c r="Z1" s="139"/>
-      <c r="AA1" s="140"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
+      <c r="V1" s="141"/>
+      <c r="W1" s="141"/>
+      <c r="X1" s="141"/>
+      <c r="Y1" s="141"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="142"/>
     </row>
     <row r="2" spans="1:27" s="48" customFormat="1" ht="48">
       <c r="A2" s="49" t="s">
@@ -33329,16 +33342,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="119.25" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>964</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
     </row>
     <row r="2" spans="1:8" ht="48">
       <c r="A2" s="65" t="s">
@@ -36247,29 +36260,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="1" customFormat="1" ht="195" customHeight="1">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="151" t="s">
         <v>1160</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="152"/>
+      <c r="I1" s="152"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
       <c r="V1" s="71"/>
       <c r="W1" s="71"/>
       <c r="X1" s="71"/>
@@ -40715,26 +40728,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="169.5" customHeight="1">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="159" t="s">
         <v>1457</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
-      <c r="R1" s="159"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
+      <c r="J1" s="160"/>
+      <c r="K1" s="160"/>
+      <c r="L1" s="160"/>
+      <c r="M1" s="160"/>
+      <c r="N1" s="160"/>
+      <c r="O1" s="160"/>
+      <c r="P1" s="160"/>
+      <c r="Q1" s="160"/>
+      <c r="R1" s="161"/>
       <c r="S1" s="13"/>
     </row>
     <row r="2" spans="1:19" s="48" customFormat="1" ht="72.75" customHeight="1">
@@ -40987,22 +41000,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="52" customHeight="1">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="151" t="s">
         <v>1163</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
+      <c r="J1" s="160"/>
+      <c r="K1" s="160"/>
+      <c r="L1" s="160"/>
+      <c r="M1" s="160"/>
+      <c r="N1" s="160"/>
     </row>
     <row r="2" spans="1:15" s="40" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="35" t="s">
@@ -41224,16 +41237,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="40" customFormat="1" ht="166" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1198</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="137"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="139"/>
     </row>
     <row r="2" spans="1:8" ht="14.5" customHeight="1">
       <c r="A2" s="26" t="s">
@@ -42214,26 +42227,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="292" customHeight="1">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="162" t="s">
         <v>965</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="161"/>
-      <c r="G1" s="161"/>
-      <c r="H1" s="161"/>
-      <c r="I1" s="161"/>
-      <c r="J1" s="161"/>
-      <c r="K1" s="161"/>
-      <c r="L1" s="161"/>
-      <c r="M1" s="161"/>
-      <c r="N1" s="161"/>
-      <c r="O1" s="161"/>
-      <c r="P1" s="161"/>
-      <c r="Q1" s="161"/>
-      <c r="R1" s="162"/>
+      <c r="B1" s="163"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="163"/>
+      <c r="G1" s="163"/>
+      <c r="H1" s="163"/>
+      <c r="I1" s="163"/>
+      <c r="J1" s="163"/>
+      <c r="K1" s="163"/>
+      <c r="L1" s="163"/>
+      <c r="M1" s="163"/>
+      <c r="N1" s="163"/>
+      <c r="O1" s="163"/>
+      <c r="P1" s="163"/>
+      <c r="Q1" s="163"/>
+      <c r="R1" s="164"/>
     </row>
     <row r="2" spans="1:18" ht="48">
       <c r="A2" s="26" t="s">
@@ -42587,25 +42600,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="234" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1461</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="145" t="s">
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="147" t="s">
         <v>1102</v>
       </c>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
-      <c r="M1" s="134"/>
-      <c r="N1" s="134"/>
-      <c r="O1" s="134"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
     </row>
     <row r="2" spans="1:15" ht="44" customHeight="1">
       <c r="A2" s="16" t="s">
@@ -43892,39 +43905,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="212" customHeight="1">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="165" t="s">
         <v>1463</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="159"/>
-      <c r="I1" s="149" t="s">
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="151" t="s">
         <v>1464</v>
       </c>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
-      <c r="V1" s="150"/>
-      <c r="W1" s="150"/>
-      <c r="X1" s="150"/>
-      <c r="Y1" s="150"/>
-      <c r="Z1" s="150"/>
-      <c r="AA1" s="150"/>
-      <c r="AB1" s="150"/>
-      <c r="AC1" s="150"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
+      <c r="V1" s="152"/>
+      <c r="W1" s="152"/>
+      <c r="X1" s="152"/>
+      <c r="Y1" s="152"/>
+      <c r="Z1" s="152"/>
+      <c r="AA1" s="152"/>
+      <c r="AB1" s="152"/>
+      <c r="AC1" s="152"/>
     </row>
     <row r="2" spans="1:29" s="40" customFormat="1" ht="48">
       <c r="A2" s="35" t="s">
@@ -50167,16 +50180,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:81" ht="185" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1504</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
       <c r="I1" s="130"/>
       <c r="J1" s="1"/>
     </row>
@@ -59571,14 +59584,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="40" customFormat="1" ht="134.25" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1003</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="137"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="139"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="26" t="s">
@@ -59643,16 +59656,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="40" customFormat="1" ht="131" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1199</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
     </row>
     <row r="2" spans="1:9" s="40" customFormat="1">
       <c r="A2" s="5" t="s">
@@ -63306,19 +63319,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="174" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="140" t="s">
         <v>669</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="141" t="s">
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="143" t="s">
         <v>952</v>
       </c>
-      <c r="H1" s="142"/>
-      <c r="I1" s="143"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="145"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="37" t="s">
@@ -63683,13 +63696,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="40" customFormat="1" ht="92" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1026</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="104" t="s">
@@ -63773,22 +63786,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="40" customFormat="1" ht="207" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>1134</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
-      <c r="N1" s="137"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
+      <c r="K1" s="138"/>
+      <c r="L1" s="138"/>
+      <c r="M1" s="138"/>
+      <c r="N1" s="139"/>
     </row>
     <row r="2" spans="1:14" ht="16">
       <c r="A2" s="104" t="s">

--- a/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26C138A-F573-3345-9E6B-EEEEC667984A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E37B5ED-1BE2-E145-A7A3-2574256BCC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="27080" windowHeight="17400" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -883,7 +883,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2848" uniqueCount="1624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2847" uniqueCount="1623">
   <si>
     <t>Region</t>
   </si>
@@ -13401,9 +13401,6 @@
   </si>
   <si>
     <t>Allow group AccessGovernanceAdmins to inspect all-resources in tenancy</t>
-  </si>
-  <si>
-    <t>Oracle-Tags.CreatedOn=2025-09-25T11:07:41.577Z;Oracle-Tags.CreatedBy=oracleidentitycloudservice/ulaganathan.namachivayam@oracle.com</t>
   </si>
   <si>
     <t>Allow group AccessGovernanceAdmins to read policies in tenancy</t>
@@ -20709,7 +20706,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1">
       <c r="A2" s="81" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
     </row>
   </sheetData>
@@ -20778,7 +20775,7 @@
         <v>736</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="F2" s="16" t="s">
         <v>1520</v>
@@ -21546,7 +21543,7 @@
         <v>11</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H2" s="27" t="s">
         <v>39</v>
@@ -21611,7 +21608,7 @@
         <v>49</v>
       </c>
       <c r="G3" s="32" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H3" s="33" t="s">
         <v>50</v>
@@ -24707,7 +24704,7 @@
       <c r="G1" s="152"/>
       <c r="H1" s="153"/>
       <c r="I1" s="136" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="J1" s="138"/>
       <c r="K1" s="138"/>
@@ -24782,52 +24779,52 @@
         <v>743</v>
       </c>
       <c r="O2" s="27" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="P2" s="27" t="s">
         <v>1002</v>
       </c>
       <c r="Q2" s="27" t="s">
+        <v>1605</v>
+      </c>
+      <c r="R2" s="27" t="s">
         <v>1606</v>
       </c>
-      <c r="R2" s="27" t="s">
+      <c r="S2" s="27" t="s">
         <v>1607</v>
       </c>
-      <c r="S2" s="27" t="s">
+      <c r="T2" s="27" t="s">
         <v>1608</v>
       </c>
-      <c r="T2" s="27" t="s">
+      <c r="U2" s="27" t="s">
         <v>1609</v>
       </c>
-      <c r="U2" s="27" t="s">
+      <c r="V2" s="27" t="s">
         <v>1610</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="W2" s="27" t="s">
         <v>1611</v>
       </c>
-      <c r="W2" s="27" t="s">
+      <c r="X2" s="27" t="s">
         <v>1612</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="Y2" s="27" t="s">
         <v>1613</v>
       </c>
-      <c r="Y2" s="27" t="s">
+      <c r="Z2" s="27" t="s">
         <v>1614</v>
       </c>
-      <c r="Z2" s="27" t="s">
+      <c r="AA2" s="27" t="s">
         <v>1615</v>
       </c>
-      <c r="AA2" s="27" t="s">
+      <c r="AB2" s="27" t="s">
         <v>1616</v>
       </c>
-      <c r="AB2" s="27" t="s">
+      <c r="AC2" s="27" t="s">
+        <v>1622</v>
+      </c>
+      <c r="AD2" s="27" t="s">
         <v>1617</v>
-      </c>
-      <c r="AC2" s="27" t="s">
-        <v>1623</v>
-      </c>
-      <c r="AD2" s="27" t="s">
-        <v>1618</v>
       </c>
       <c r="AE2" s="26" t="s">
         <v>94</v>
@@ -24868,19 +24865,19 @@
         <v>349</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="G3" s="33" t="b">
         <v>0</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="I3" s="33" t="s">
         <v>431</v>
       </c>
       <c r="J3" s="134" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="K3" s="33">
         <v>8</v>
@@ -25039,7 +25036,7 @@
         <v>349</v>
       </c>
       <c r="F6" s="54" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="G6" s="53" t="b">
         <v>0</v>
@@ -59655,7 +59652,7 @@
     <col min="8" max="8" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="40" customFormat="1" ht="131" customHeight="1">
+    <row r="1" spans="1:8" s="40" customFormat="1" ht="131" customHeight="1">
       <c r="A1" s="136" t="s">
         <v>1199</v>
       </c>
@@ -59667,7 +59664,7 @@
       <c r="G1" s="136"/>
       <c r="H1" s="136"/>
     </row>
-    <row r="2" spans="1:9" s="40" customFormat="1">
+    <row r="2" spans="1:8" s="40" customFormat="1">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -59693,7 +59690,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="69.75" customHeight="1">
+    <row r="3" spans="1:8" ht="69.75" customHeight="1">
       <c r="A3" s="32" t="s">
         <v>5</v>
       </c>
@@ -59713,7 +59710,7 @@
       <c r="G3" s="32"/>
       <c r="H3" s="32"/>
     </row>
-    <row r="4" spans="1:9" ht="69.75" customHeight="1">
+    <row r="4" spans="1:8" ht="69.75" customHeight="1">
       <c r="A4" s="32"/>
       <c r="B4" s="32"/>
       <c r="C4" s="32"/>
@@ -59725,7 +59722,7 @@
       <c r="G4" s="32"/>
       <c r="H4" s="32"/>
     </row>
-    <row r="5" spans="1:9" ht="80">
+    <row r="5" spans="1:8" ht="48">
       <c r="A5" s="32" t="s">
         <v>5</v>
       </c>
@@ -59743,38 +59740,33 @@
       </c>
       <c r="F5" s="32"/>
       <c r="G5" s="32"/>
-      <c r="H5" s="32" t="s">
-        <v>1577</v>
-      </c>
-      <c r="I5" s="33"/>
-    </row>
-    <row r="6" spans="1:9" ht="32">
+      <c r="H5" s="32"/>
+    </row>
+    <row r="6" spans="1:8" ht="32">
       <c r="A6" s="32"/>
       <c r="B6" s="32"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="E6" s="32" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="33"/>
-    </row>
-    <row r="7" spans="1:9" ht="32">
+    </row>
+    <row r="7" spans="1:8" ht="32">
       <c r="A7" s="32"/>
       <c r="B7" s="32"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="E7" s="32" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="33"/>
-    </row>
-    <row r="8" spans="1:9" ht="102.75" customHeight="1">
+    </row>
+    <row r="8" spans="1:8" ht="102.75" customHeight="1">
       <c r="A8" s="32" t="s">
         <v>5</v>
       </c>
@@ -59794,7 +59786,7 @@
       <c r="G8" s="32"/>
       <c r="H8" s="32"/>
     </row>
-    <row r="9" spans="1:9" ht="29.25" customHeight="1">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1">
       <c r="A9" s="32"/>
       <c r="B9" s="32"/>
       <c r="C9" s="32"/>
@@ -59806,7 +59798,7 @@
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:9" ht="29.25" customHeight="1">
+    <row r="10" spans="1:8" ht="29.25" customHeight="1">
       <c r="A10" s="32"/>
       <c r="B10" s="32"/>
       <c r="C10" s="32"/>
@@ -59818,7 +59810,7 @@
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
     </row>
-    <row r="11" spans="1:9" ht="29.25" customHeight="1">
+    <row r="11" spans="1:8" ht="29.25" customHeight="1">
       <c r="A11" s="32"/>
       <c r="B11" s="32"/>
       <c r="C11" s="32"/>
@@ -59830,7 +59822,7 @@
       <c r="G11" s="32"/>
       <c r="H11" s="32"/>
     </row>
-    <row r="12" spans="1:9" ht="29.25" customHeight="1">
+    <row r="12" spans="1:8" ht="29.25" customHeight="1">
       <c r="A12" s="32"/>
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
@@ -59842,7 +59834,7 @@
       <c r="G12" s="32"/>
       <c r="H12" s="32"/>
     </row>
-    <row r="13" spans="1:9" ht="29.25" customHeight="1">
+    <row r="13" spans="1:8" ht="29.25" customHeight="1">
       <c r="A13" s="32"/>
       <c r="B13" s="32"/>
       <c r="C13" s="32"/>
@@ -59854,7 +59846,7 @@
       <c r="G13" s="32"/>
       <c r="H13" s="32"/>
     </row>
-    <row r="14" spans="1:9" ht="29.25" customHeight="1">
+    <row r="14" spans="1:8" ht="29.25" customHeight="1">
       <c r="A14" s="32"/>
       <c r="B14" s="32"/>
       <c r="C14" s="32"/>
@@ -59866,7 +59858,7 @@
       <c r="G14" s="32"/>
       <c r="H14" s="32"/>
     </row>
-    <row r="15" spans="1:9" ht="29.25" customHeight="1">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1">
       <c r="A15" s="32"/>
       <c r="B15" s="32"/>
       <c r="C15" s="32"/>
@@ -59878,7 +59870,7 @@
       <c r="G15" s="32"/>
       <c r="H15" s="32"/>
     </row>
-    <row r="16" spans="1:9" ht="29.25" customHeight="1">
+    <row r="16" spans="1:8" ht="29.25" customHeight="1">
       <c r="A16" s="32"/>
       <c r="B16" s="32"/>
       <c r="C16" s="32"/>
@@ -60124,7 +60116,7 @@
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="E36" s="32" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="F36" s="32"/>
       <c r="G36" s="32"/>
@@ -60516,7 +60508,7 @@
       <c r="C68" s="32"/>
       <c r="D68" s="32"/>
       <c r="E68" s="32" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="F68" s="32"/>
       <c r="G68" s="32"/>
@@ -60528,7 +60520,7 @@
       <c r="C69" s="32"/>
       <c r="D69" s="32"/>
       <c r="E69" s="32" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="F69" s="32"/>
       <c r="G69" s="32"/>
@@ -60540,7 +60532,7 @@
       <c r="C70" s="32"/>
       <c r="D70" s="32"/>
       <c r="E70" s="32" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="F70" s="32"/>
       <c r="G70" s="32"/>
@@ -60552,7 +60544,7 @@
       <c r="C71" s="32"/>
       <c r="D71" s="32"/>
       <c r="E71" s="32" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="F71" s="32"/>
       <c r="G71" s="32"/>
@@ -60564,7 +60556,7 @@
       <c r="C72" s="32"/>
       <c r="D72" s="32"/>
       <c r="E72" s="32" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="F72" s="32"/>
       <c r="G72" s="32"/>
@@ -60576,7 +60568,7 @@
       <c r="C73" s="32"/>
       <c r="D73" s="32"/>
       <c r="E73" s="32" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F73" s="32"/>
       <c r="G73" s="32"/>
@@ -60588,7 +60580,7 @@
       <c r="C74" s="32"/>
       <c r="D74" s="32"/>
       <c r="E74" s="32" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="F74" s="32"/>
       <c r="G74" s="32"/>
@@ -60600,7 +60592,7 @@
       <c r="C75" s="32"/>
       <c r="D75" s="32"/>
       <c r="E75" s="32" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="F75" s="32"/>
       <c r="G75" s="32"/>
@@ -60612,7 +60604,7 @@
       <c r="C76" s="32"/>
       <c r="D76" s="32"/>
       <c r="E76" s="32" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="F76" s="32"/>
       <c r="G76" s="32"/>
@@ -60624,7 +60616,7 @@
       <c r="C77" s="32"/>
       <c r="D77" s="32"/>
       <c r="E77" s="32" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="F77" s="32"/>
       <c r="G77" s="32"/>
@@ -61304,7 +61296,7 @@
       <c r="C131" s="32"/>
       <c r="D131" s="32"/>
       <c r="E131" s="32" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="F131" s="32"/>
       <c r="G131" s="32"/>
@@ -61316,7 +61308,7 @@
       <c r="C132" s="32"/>
       <c r="D132" s="32"/>
       <c r="E132" s="32" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="F132" s="32"/>
       <c r="G132" s="32"/>
@@ -61980,7 +61972,7 @@
       <c r="C186" s="32"/>
       <c r="D186" s="32"/>
       <c r="E186" s="32" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="F186" s="32"/>
       <c r="G186" s="32"/>
@@ -61992,7 +61984,7 @@
       <c r="C187" s="32"/>
       <c r="D187" s="32"/>
       <c r="E187" s="32" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="F187" s="32"/>
       <c r="G187" s="32"/>
@@ -62004,7 +61996,7 @@
       <c r="C188" s="32"/>
       <c r="D188" s="32"/>
       <c r="E188" s="32" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="F188" s="32"/>
       <c r="G188" s="32"/>
@@ -62536,7 +62528,7 @@
       <c r="C231" s="32"/>
       <c r="D231" s="32"/>
       <c r="E231" s="32" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="F231" s="32"/>
       <c r="G231" s="32"/>
@@ -62662,7 +62654,7 @@
       <c r="C242" s="33"/>
       <c r="D242" s="33"/>
       <c r="E242" s="32" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="F242" s="33"/>
       <c r="G242" s="33"/>
@@ -62674,7 +62666,7 @@
       <c r="C243" s="33"/>
       <c r="D243" s="33"/>
       <c r="E243" s="32" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="F243" s="33"/>
       <c r="G243" s="33"/>
@@ -62686,7 +62678,7 @@
       <c r="C244" s="33"/>
       <c r="D244" s="33"/>
       <c r="E244" s="32" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="F244" s="33"/>
       <c r="G244" s="33"/>

--- a/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E37B5ED-1BE2-E145-A7A3-2574256BCC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7EAC7C-E5AB-7A40-8015-A8DE80563C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="27080" windowHeight="17400" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -883,7 +883,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2847" uniqueCount="1623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2847" uniqueCount="1622">
   <si>
     <t>Region</t>
   </si>
@@ -4274,21 +4274,6 @@
     <t>Cardiff</t>
   </si>
   <si>
-    <t>gov-ashburn</t>
-  </si>
-  <si>
-    <t>gov-cardiff</t>
-  </si>
-  <si>
-    <t>gov-chicago</t>
-  </si>
-  <si>
-    <t>gov-london</t>
-  </si>
-  <si>
-    <t>gov-phoenix</t>
-  </si>
-  <si>
     <t>Langley</t>
   </si>
   <si>
@@ -13815,6 +13800,18 @@
   </si>
   <si>
     <t>Plugin OS Management Service Agent</t>
+  </si>
+  <si>
+    <t>ashburn</t>
+  </si>
+  <si>
+    <t>chicago</t>
+  </si>
+  <si>
+    <t>london</t>
+  </si>
+  <si>
+    <t>cardiff</t>
   </si>
 </sst>
 </file>
@@ -20706,7 +20703,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1">
       <c r="A2" s="81" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
     </row>
   </sheetData>
@@ -20742,7 +20739,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="250" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1522</v>
+        <v>1517</v>
       </c>
       <c r="B1" s="141"/>
       <c r="C1" s="141"/>
@@ -20753,7 +20750,7 @@
       <c r="H1" s="141"/>
       <c r="I1" s="142"/>
       <c r="J1" s="140" t="s">
-        <v>1459</v>
+        <v>1454</v>
       </c>
       <c r="K1" s="141"/>
       <c r="L1" s="141"/>
@@ -20775,13 +20772,13 @@
         <v>736</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>1599</v>
+        <v>1594</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>1520</v>
+        <v>1515</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>1521</v>
+        <v>1516</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>12</v>
@@ -21036,7 +21033,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="222" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -21044,7 +21041,7 @@
       <c r="E1" s="136"/>
       <c r="F1" s="136"/>
       <c r="G1" s="146" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="H1" s="146"/>
       <c r="I1" s="146"/>
@@ -21063,7 +21060,7 @@
         <v>603</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>604</v>
@@ -21089,7 +21086,7 @@
         <v>722</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="E3" s="32"/>
       <c r="F3" s="32" t="s">
@@ -21127,13 +21124,13 @@
         <v>722</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="G5" s="33"/>
       <c r="H5" s="33"/>
@@ -21147,16 +21144,16 @@
         <v>350</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="G6" s="33"/>
       <c r="H6" s="33"/>
@@ -21218,7 +21215,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="40" customFormat="1" ht="92.25" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="B1" s="145"/>
     </row>
@@ -21290,7 +21287,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="103.75" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -21499,7 +21496,7 @@
   <sheetData>
     <row r="1" spans="1:21" ht="203.25" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="B1" s="141"/>
       <c r="C1" s="141"/>
@@ -21510,7 +21507,7 @@
       <c r="H1" s="141"/>
       <c r="I1" s="142"/>
       <c r="J1" s="147" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="K1" s="147"/>
       <c r="L1" s="147"/>
@@ -21537,13 +21534,13 @@
         <v>311</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="H2" s="27" t="s">
         <v>39</v>
@@ -21608,7 +21605,7 @@
         <v>49</v>
       </c>
       <c r="G3" s="32" t="s">
-        <v>1601</v>
+        <v>1596</v>
       </c>
       <c r="H3" s="33" t="s">
         <v>50</v>
@@ -21707,7 +21704,7 @@
         <v>721</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
       <c r="E5" s="33" t="s">
         <v>617</v>
@@ -21782,16 +21779,16 @@
         <v>350</v>
       </c>
       <c r="C7" s="53" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="D7" s="53" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="E7" s="53" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="F7" s="53" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="G7" s="133"/>
       <c r="H7" s="53" t="s">
@@ -21802,7 +21799,7 @@
       </c>
       <c r="J7" s="53"/>
       <c r="K7" s="53" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="L7" s="53"/>
       <c r="M7" s="54" t="s">
@@ -21837,16 +21834,16 @@
         <v>350</v>
       </c>
       <c r="C8" s="53" t="s">
+        <v>859</v>
+      </c>
+      <c r="D8" s="53" t="s">
+        <v>863</v>
+      </c>
+      <c r="E8" s="53" t="s">
+        <v>858</v>
+      </c>
+      <c r="F8" s="53" t="s">
         <v>864</v>
-      </c>
-      <c r="D8" s="53" t="s">
-        <v>868</v>
-      </c>
-      <c r="E8" s="53" t="s">
-        <v>863</v>
-      </c>
-      <c r="F8" s="53" t="s">
-        <v>869</v>
       </c>
       <c r="G8" s="133"/>
       <c r="H8" s="53" t="s">
@@ -21857,7 +21854,7 @@
       </c>
       <c r="J8" s="53"/>
       <c r="K8" s="53" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="L8" s="53"/>
       <c r="M8" s="53"/>
@@ -22296,7 +22293,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="63" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -22395,7 +22392,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="63" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -22495,7 +22492,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="60" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -22649,7 +22646,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="139" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -23648,7 +23645,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="175" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="B1" s="148"/>
       <c r="C1" s="148"/>
@@ -23667,22 +23664,22 @@
         <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>865</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>866</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>867</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>868</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>869</v>
+      </c>
+      <c r="H2" s="26" t="s">
         <v>870</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>871</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>872</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>873</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>874</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>875</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>421</v>
@@ -23709,19 +23706,19 @@
         <v>350</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="H4" s="32">
         <v>3600</v>
@@ -23736,19 +23733,19 @@
         <v>350</v>
       </c>
       <c r="C5" s="32" t="s">
+        <v>871</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>872</v>
+      </c>
+      <c r="E5" s="32" t="s">
         <v>876</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="F5" s="32" t="s">
         <v>877</v>
       </c>
-      <c r="E5" s="32" t="s">
-        <v>881</v>
-      </c>
-      <c r="F5" s="32" t="s">
-        <v>882</v>
-      </c>
       <c r="G5" s="32" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="H5" s="32">
         <v>300</v>
@@ -23763,19 +23760,19 @@
         <v>350</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="H6" s="32">
         <v>300</v>
@@ -24045,7 +24042,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="40" customFormat="1" ht="108" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -24077,7 +24074,7 @@
         <v>552</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>1191</v>
+        <v>1186</v>
       </c>
       <c r="D3" s="32" t="s">
         <v>397</v>
@@ -24092,7 +24089,7 @@
         <v>553</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>397</v>
@@ -24107,7 +24104,7 @@
         <v>350</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>397</v>
@@ -24122,7 +24119,7 @@
         <v>554</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="D6" s="32" t="s">
         <v>397</v>
@@ -24308,7 +24305,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="200" customHeight="1">
       <c r="A1" s="149" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="B1" s="150"/>
       <c r="C1" s="150"/>
@@ -24335,22 +24332,22 @@
         <v>311</v>
       </c>
       <c r="E2" s="26" t="s">
+        <v>883</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>884</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>885</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>886</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>887</v>
+      </c>
+      <c r="J2" s="26" t="s">
         <v>888</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>889</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>890</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>891</v>
-      </c>
-      <c r="I2" s="26" t="s">
-        <v>892</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>893</v>
       </c>
       <c r="K2" s="26" t="s">
         <v>421</v>
@@ -24385,20 +24382,20 @@
         <v>721</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="G4" s="33" t="s">
         <v>734</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="I4" s="28"/>
       <c r="J4" s="29" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="K4" s="29"/>
     </row>
@@ -24416,16 +24413,16 @@
         <v>721</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="G5" s="33" t="s">
         <v>734</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="I5" s="29"/>
       <c r="J5" s="29"/>
@@ -24494,7 +24491,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="89.25" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -24694,7 +24691,7 @@
   <sheetData>
     <row r="1" spans="1:37" ht="250" customHeight="1">
       <c r="A1" s="151" t="s">
-        <v>1462</v>
+        <v>1457</v>
       </c>
       <c r="B1" s="152"/>
       <c r="C1" s="152"/>
@@ -24704,7 +24701,7 @@
       <c r="G1" s="152"/>
       <c r="H1" s="153"/>
       <c r="I1" s="136" t="s">
-        <v>1603</v>
+        <v>1598</v>
       </c>
       <c r="J1" s="138"/>
       <c r="K1" s="138"/>
@@ -24752,7 +24749,7 @@
         <v>85</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="G2" s="26" t="s">
         <v>91</v>
@@ -24779,52 +24776,52 @@
         <v>743</v>
       </c>
       <c r="O2" s="27" t="s">
+        <v>1599</v>
+      </c>
+      <c r="P2" s="27" t="s">
+        <v>997</v>
+      </c>
+      <c r="Q2" s="27" t="s">
+        <v>1600</v>
+      </c>
+      <c r="R2" s="27" t="s">
+        <v>1601</v>
+      </c>
+      <c r="S2" s="27" t="s">
+        <v>1602</v>
+      </c>
+      <c r="T2" s="27" t="s">
+        <v>1603</v>
+      </c>
+      <c r="U2" s="27" t="s">
         <v>1604</v>
       </c>
-      <c r="P2" s="27" t="s">
-        <v>1002</v>
-      </c>
-      <c r="Q2" s="27" t="s">
+      <c r="V2" s="27" t="s">
         <v>1605</v>
       </c>
-      <c r="R2" s="27" t="s">
+      <c r="W2" s="27" t="s">
         <v>1606</v>
       </c>
-      <c r="S2" s="27" t="s">
+      <c r="X2" s="27" t="s">
         <v>1607</v>
       </c>
-      <c r="T2" s="27" t="s">
+      <c r="Y2" s="27" t="s">
         <v>1608</v>
       </c>
-      <c r="U2" s="27" t="s">
+      <c r="Z2" s="27" t="s">
         <v>1609</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="AA2" s="27" t="s">
         <v>1610</v>
       </c>
-      <c r="W2" s="27" t="s">
+      <c r="AB2" s="27" t="s">
         <v>1611</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="AC2" s="27" t="s">
+        <v>1617</v>
+      </c>
+      <c r="AD2" s="27" t="s">
         <v>1612</v>
-      </c>
-      <c r="Y2" s="27" t="s">
-        <v>1613</v>
-      </c>
-      <c r="Z2" s="27" t="s">
-        <v>1614</v>
-      </c>
-      <c r="AA2" s="27" t="s">
-        <v>1615</v>
-      </c>
-      <c r="AB2" s="27" t="s">
-        <v>1616</v>
-      </c>
-      <c r="AC2" s="27" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AD2" s="27" t="s">
-        <v>1617</v>
       </c>
       <c r="AE2" s="26" t="s">
         <v>94</v>
@@ -24842,7 +24839,7 @@
         <v>97</v>
       </c>
       <c r="AJ2" s="27" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="AK2" s="26" t="s">
         <v>421</v>
@@ -24865,19 +24862,19 @@
         <v>349</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>1618</v>
+        <v>1613</v>
       </c>
       <c r="G3" s="33" t="b">
         <v>0</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
       <c r="I3" s="33" t="s">
         <v>431</v>
       </c>
       <c r="J3" s="134" t="s">
-        <v>1620</v>
+        <v>1615</v>
       </c>
       <c r="K3" s="33">
         <v>8</v>
@@ -24963,7 +24960,7 @@
         <v>103</v>
       </c>
       <c r="F5" s="54" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="G5" s="53" t="b">
         <v>0</v>
@@ -24982,7 +24979,7 @@
       </c>
       <c r="N5" s="53"/>
       <c r="O5" s="53" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="P5" s="53"/>
       <c r="Q5" s="53"/>
@@ -25013,7 +25010,7 @@
         <v>90</v>
       </c>
       <c r="AJ5" s="54" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="AK5" s="54" t="s">
         <v>429</v>
@@ -25036,7 +25033,7 @@
         <v>349</v>
       </c>
       <c r="F6" s="54" t="s">
-        <v>1621</v>
+        <v>1616</v>
       </c>
       <c r="G6" s="53" t="b">
         <v>0</v>
@@ -25084,7 +25081,7 @@
       </c>
       <c r="AI6" s="53"/>
       <c r="AJ6" s="54" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="AK6" s="53"/>
     </row>
@@ -25105,7 +25102,7 @@
         <v>103</v>
       </c>
       <c r="F7" s="54" t="s">
-        <v>1137</v>
+        <v>1132</v>
       </c>
       <c r="G7" s="53" t="b">
         <v>0</v>
@@ -25168,7 +25165,7 @@
         <v>349</v>
       </c>
       <c r="F8" s="54" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
       <c r="G8" s="53" t="b">
         <v>0</v>
@@ -25260,7 +25257,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="202" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1458</v>
+        <v>1453</v>
       </c>
       <c r="B1" s="141"/>
       <c r="C1" s="141"/>
@@ -25291,7 +25288,7 @@
         <v>105</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="E2" s="26" t="s">
         <v>106</v>
@@ -25312,16 +25309,16 @@
         <v>430</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="M2" s="27" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="N2" s="27" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="O2" s="27" t="s">
         <v>744</v>
@@ -25387,19 +25384,19 @@
         <v>746</v>
       </c>
       <c r="J4" s="117" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="K4" s="117" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="L4" s="117">
         <v>100</v>
       </c>
       <c r="M4" s="117" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="N4" s="117" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="O4" s="84" t="b">
         <v>1</v>
@@ -25518,7 +25515,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="190" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1139</v>
+        <v>1134</v>
       </c>
       <c r="B1" s="141"/>
       <c r="C1" s="141"/>
@@ -25532,7 +25529,7 @@
       <c r="K1" s="141"/>
       <c r="L1" s="142"/>
       <c r="M1" s="154" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
       <c r="N1" s="155"/>
       <c r="O1" s="155"/>
@@ -25558,7 +25555,7 @@
         <v>110</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="F2" s="27" t="s">
         <v>111</v>
@@ -25573,13 +25570,13 @@
         <v>113</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="M2" s="27" t="s">
         <v>114</v>
@@ -25603,10 +25600,10 @@
         <v>120</v>
       </c>
       <c r="T2" s="27" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
       <c r="U2" s="27" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
       <c r="V2" s="27" t="s">
         <v>421</v>
@@ -25654,7 +25651,7 @@
         <v>121</v>
       </c>
       <c r="E4" s="54" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="F4" s="53"/>
       <c r="G4" s="53" t="s">
@@ -25758,7 +25755,7 @@
         <v>121</v>
       </c>
       <c r="E7" s="54" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="F7" s="53"/>
       <c r="G7" s="53"/>
@@ -25796,7 +25793,7 @@
         <v>129</v>
       </c>
       <c r="E8" s="54" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="F8" s="53"/>
       <c r="G8" s="53"/>
@@ -25838,7 +25835,7 @@
         <v>132</v>
       </c>
       <c r="E9" s="54" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="F9" s="53"/>
       <c r="G9" s="53"/>
@@ -25880,7 +25877,7 @@
         <v>134</v>
       </c>
       <c r="E10" s="54" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="F10" s="53"/>
       <c r="G10" s="53"/>
@@ -25915,10 +25912,10 @@
         <v>89</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="E11" s="54" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="F11" s="53"/>
       <c r="G11" s="53"/>
@@ -25954,7 +25951,7 @@
       <c r="G12" s="53"/>
       <c r="H12" s="53"/>
       <c r="I12" s="53" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="J12" s="53"/>
       <c r="K12" s="53"/>
@@ -26058,7 +26055,7 @@
   <sheetData>
     <row r="1" spans="1:35" ht="106" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1140</v>
+        <v>1135</v>
       </c>
       <c r="B1" s="141"/>
       <c r="C1" s="141"/>
@@ -26075,7 +26072,7 @@
       <c r="N1" s="141"/>
       <c r="O1" s="142"/>
       <c r="P1" s="151" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="Q1" s="152"/>
       <c r="R1" s="152"/>
@@ -26108,7 +26105,7 @@
         <v>797</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>798</v>
@@ -26120,10 +26117,10 @@
         <v>800</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>1142</v>
+        <v>1137</v>
       </c>
       <c r="J2" s="27" t="s">
         <v>801</v>
@@ -26138,7 +26135,7 @@
         <v>804</v>
       </c>
       <c r="N2" s="27" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="O2" s="27" t="s">
         <v>805</v>
@@ -26162,13 +26159,13 @@
         <v>807</v>
       </c>
       <c r="V2" s="27" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="W2" s="27" t="s">
         <v>83</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="Y2" s="27" t="s">
         <v>808</v>
@@ -26177,7 +26174,7 @@
         <v>809</v>
       </c>
       <c r="AA2" s="27" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
       <c r="AB2" s="27" t="s">
         <v>810</v>
@@ -26195,13 +26192,13 @@
         <v>812</v>
       </c>
       <c r="AG2" s="27" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="AH2" s="27" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="AI2" s="27" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1">
@@ -26254,10 +26251,10 @@
         <v>813</v>
       </c>
       <c r="D4" s="94" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="E4" s="94" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="F4" s="94" t="s">
         <v>815</v>
@@ -26266,10 +26263,10 @@
         <v>1</v>
       </c>
       <c r="H4" s="94" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
       <c r="I4" s="94" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
       <c r="J4" s="54" t="b">
         <v>0</v>
@@ -26284,10 +26281,10 @@
         <v>826</v>
       </c>
       <c r="N4" s="94" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
       <c r="O4" s="94" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="P4" s="94">
         <v>1</v>
@@ -26308,13 +26305,13 @@
         <v>828</v>
       </c>
       <c r="V4" s="94" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="W4" s="94" t="s">
         <v>98</v>
       </c>
       <c r="X4" s="94" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="Y4" s="94"/>
       <c r="Z4" s="94"/>
@@ -26349,10 +26346,10 @@
       <c r="L5" s="54"/>
       <c r="M5" s="54"/>
       <c r="N5" s="54" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="O5" s="94" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="P5" s="54">
         <v>2</v>
@@ -26371,13 +26368,13 @@
       </c>
       <c r="U5" s="54"/>
       <c r="V5" s="94" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="W5" s="54" t="s">
         <v>89</v>
       </c>
       <c r="X5" s="94" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="Y5" s="54"/>
       <c r="Z5" s="54"/>
@@ -26406,10 +26403,10 @@
         <v>823</v>
       </c>
       <c r="D6" s="54" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="E6" s="54" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="F6" s="54" t="s">
         <v>824</v>
@@ -26418,10 +26415,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="94" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
       <c r="I6" s="94" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
       <c r="J6" s="54" t="b">
         <v>0</v>
@@ -26430,10 +26427,10 @@
       <c r="L6" s="54"/>
       <c r="M6" s="54"/>
       <c r="N6" s="54" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
       <c r="O6" s="94" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="P6" s="54">
         <v>1</v>
@@ -26454,20 +26451,20 @@
         <v>828</v>
       </c>
       <c r="V6" s="94" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="W6" s="54" t="s">
         <v>98</v>
       </c>
       <c r="X6" s="94" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="Y6" s="54">
         <v>2</v>
       </c>
       <c r="Z6" s="54"/>
       <c r="AA6" s="94" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="AB6" s="96"/>
       <c r="AC6" s="54" t="s">
@@ -26479,7 +26476,7 @@
       <c r="AG6" s="53"/>
       <c r="AH6" s="53"/>
       <c r="AI6" s="54" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
     </row>
   </sheetData>
@@ -26549,7 +26546,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="122.5" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -26590,7 +26587,7 @@
         <v>612</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="H2" s="16" t="s">
         <v>137</v>
@@ -26668,7 +26665,7 @@
       <c r="E4" s="53"/>
       <c r="F4" s="53"/>
       <c r="G4" s="54" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="H4" s="53" t="b">
         <v>1</v>
@@ -26742,7 +26739,7 @@
       <c r="E6" s="53"/>
       <c r="F6" s="53"/>
       <c r="G6" s="54" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="H6" s="53" t="b">
         <v>0</v>
@@ -26850,7 +26847,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="119.25" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
       <c r="B1" s="141"/>
       <c r="C1" s="141"/>
@@ -26894,7 +26891,7 @@
         <v>154</v>
       </c>
       <c r="G2" s="34" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="H2" s="34" t="s">
         <v>155</v>
@@ -26984,7 +26981,7 @@
         <v>165</v>
       </c>
       <c r="G4" s="53" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="H4" s="53" t="s">
         <v>166</v>
@@ -27044,7 +27041,7 @@
         <v>171</v>
       </c>
       <c r="G5" s="53" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="H5" s="53" t="s">
         <v>166</v>
@@ -27092,7 +27089,7 @@
         <v>174</v>
       </c>
       <c r="G6" s="53" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="H6" s="53" t="s">
         <v>166</v>
@@ -27203,7 +27200,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="124" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1148</v>
+        <v>1143</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -28186,7 +28183,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="40" customFormat="1" ht="173" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="B1" s="138"/>
       <c r="C1" s="138"/>
@@ -28206,13 +28203,13 @@
         <v>2</v>
       </c>
       <c r="D2" s="106" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="E2" s="106" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
       <c r="F2" s="127" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="G2" s="106" t="s">
         <v>421</v>
@@ -28223,10 +28220,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>1540</v>
+        <v>1535</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="D3" s="32"/>
       <c r="E3" s="33"/>
@@ -28238,10 +28235,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>1542</v>
+        <v>1537</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>1543</v>
+        <v>1538</v>
       </c>
       <c r="D4" s="32"/>
       <c r="E4" s="33"/>
@@ -28253,10 +28250,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="D5" s="32"/>
       <c r="E5" s="33"/>
@@ -28268,10 +28265,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>1547</v>
+        <v>1542</v>
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="33"/>
@@ -28283,10 +28280,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>1548</v>
+        <v>1543</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>1549</v>
+        <v>1544</v>
       </c>
       <c r="D7" s="32"/>
       <c r="E7" s="19"/>
@@ -28298,10 +28295,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="128" t="s">
-        <v>1550</v>
+        <v>1545</v>
       </c>
       <c r="C8" s="128" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="32"/>
@@ -28313,10 +28310,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>1552</v>
+        <v>1547</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>1553</v>
+        <v>1548</v>
       </c>
       <c r="D9" s="32"/>
       <c r="E9" s="32"/>
@@ -28328,10 +28325,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>1554</v>
+        <v>1549</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="32"/>
@@ -28343,10 +28340,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>1556</v>
+        <v>1551</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>1557</v>
+        <v>1552</v>
       </c>
       <c r="D11" s="32"/>
       <c r="E11" s="32"/>
@@ -28358,10 +28355,10 @@
         <v>5</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>1558</v>
+        <v>1553</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>1559</v>
+        <v>1554</v>
       </c>
       <c r="D12" s="32"/>
       <c r="E12" s="33"/>
@@ -28373,10 +28370,10 @@
         <v>5</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>1560</v>
+        <v>1555</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>1561</v>
+        <v>1556</v>
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="33"/>
@@ -28399,15 +28396,15 @@
         <v>5</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>1562</v>
+        <v>1557</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="8"/>
       <c r="F15" s="32" t="s">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="G15" s="33"/>
     </row>
@@ -28416,15 +28413,15 @@
         <v>5</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
       <c r="F16" s="32" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="G16" s="33"/>
     </row>
@@ -28433,15 +28430,15 @@
         <v>5</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>1569</v>
+        <v>1564</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33"/>
       <c r="F17" s="32" t="s">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="G17" s="33"/>
     </row>
@@ -28450,15 +28447,15 @@
         <v>5</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>1571</v>
+        <v>1566</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>1572</v>
+        <v>1567</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="33"/>
       <c r="F18" s="32" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="G18" s="33"/>
     </row>
@@ -28650,7 +28647,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="64" customHeight="1">
       <c r="A1" s="147" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="B1" s="138"/>
       <c r="C1" s="138"/>
@@ -28664,10 +28661,10 @@
         <v>136</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>1150</v>
+        <v>1145</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="79" customHeight="1">
@@ -28686,10 +28683,10 @@
         <v>395</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="D4" s="54" t="s">
-        <v>1152</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="93.5" customHeight="1">
@@ -28700,10 +28697,10 @@
         <v>395</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>1154</v>
+        <v>1149</v>
       </c>
     </row>
   </sheetData>
@@ -28784,7 +28781,7 @@
         <v>769</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>768</v>
@@ -28846,13 +28843,13 @@
         <v>765</v>
       </c>
       <c r="D4" s="54" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="E4" s="54" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="54" t="s">
-        <v>1071</v>
+        <v>1066</v>
       </c>
       <c r="G4" s="54" t="b">
         <v>1</v>
@@ -28884,7 +28881,7 @@
         <v>761</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>1156</v>
+        <v>1151</v>
       </c>
       <c r="E5" s="54" t="b">
         <v>1</v>
@@ -29350,10 +29347,10 @@
         <v>772</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="I2" s="27" t="s">
         <v>157</v>
@@ -29365,7 +29362,7 @@
         <v>441</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="29.25" customHeight="1">
@@ -29417,7 +29414,7 @@
         <v>10000</v>
       </c>
       <c r="L4" s="54" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="32">
@@ -29451,7 +29448,7 @@
         <v>10000</v>
       </c>
       <c r="L5" s="54" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="16">
@@ -29468,10 +29465,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="54" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="H6" s="54" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="I6" s="54">
         <v>53</v>
@@ -29481,7 +29478,7 @@
         <v>20000</v>
       </c>
       <c r="L6" s="54" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
     </row>
   </sheetData>
@@ -29544,7 +29541,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="216" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -29577,10 +29574,10 @@
         <v>790</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="F2" s="16" t="s">
         <v>791</v>
@@ -29595,16 +29592,16 @@
         <v>313</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="K2" s="16" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="L2" s="16" t="s">
-        <v>1527</v>
+        <v>1522</v>
       </c>
       <c r="M2" s="16" t="s">
-        <v>1528</v>
+        <v>1523</v>
       </c>
       <c r="N2" s="16" t="s">
         <v>792</v>
@@ -29664,7 +29661,7 @@
       </c>
       <c r="D4" s="53"/>
       <c r="E4" s="54" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="F4" s="53"/>
       <c r="G4" s="53" t="s">
@@ -29677,20 +29674,20 @@
         <v>328</v>
       </c>
       <c r="J4" s="53" t="s">
-        <v>1529</v>
+        <v>1524</v>
       </c>
       <c r="K4" s="53"/>
       <c r="L4" s="53" t="b">
         <v>1</v>
       </c>
       <c r="M4" s="54" t="s">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="N4" s="53" t="s">
         <v>317</v>
       </c>
       <c r="O4" s="54" t="s">
-        <v>1531</v>
+        <v>1526</v>
       </c>
       <c r="P4" s="53" t="s">
         <v>406</v>
@@ -29712,39 +29709,39 @@
         <v>553</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>1532</v>
+        <v>1527</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>1533</v>
+        <v>1528</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="F5" s="54"/>
       <c r="G5" s="54" t="s">
-        <v>1534</v>
+        <v>1529</v>
       </c>
       <c r="H5" s="54"/>
       <c r="I5" s="131" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="J5" s="54" t="s">
-        <v>1536</v>
+        <v>1531</v>
       </c>
       <c r="K5" s="54" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
       <c r="L5" s="54" t="b">
         <v>1</v>
       </c>
       <c r="M5" s="54" t="s">
-        <v>1538</v>
+        <v>1533</v>
       </c>
       <c r="N5" s="54" t="s">
-        <v>1539</v>
+        <v>1534</v>
       </c>
       <c r="O5" s="54" t="s">
-        <v>1531</v>
+        <v>1526</v>
       </c>
       <c r="P5" s="54" t="s">
         <v>324</v>
@@ -29945,7 +29942,7 @@
   <sheetData>
     <row r="1" spans="1:27" s="1" customFormat="1" ht="135.75" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
       <c r="B1" s="141"/>
       <c r="C1" s="141"/>
@@ -29985,7 +29982,7 @@
         <v>83</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="E2" s="50" t="s">
         <v>675</v>
@@ -30099,7 +30096,7 @@
         <v>55</v>
       </c>
       <c r="D4" s="54" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="E4" s="89" t="s">
         <v>706</v>
@@ -30174,7 +30171,7 @@
         <v>89</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="E5" s="89" t="s">
         <v>708</v>
@@ -33340,7 +33337,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="119.25" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="B1" s="141"/>
       <c r="C1" s="141"/>
@@ -36258,7 +36255,7 @@
   <sheetData>
     <row r="1" spans="1:28" s="1" customFormat="1" ht="195" customHeight="1">
       <c r="A1" s="151" t="s">
-        <v>1160</v>
+        <v>1155</v>
       </c>
       <c r="B1" s="152"/>
       <c r="C1" s="152"/>
@@ -36302,10 +36299,10 @@
         <v>699</v>
       </c>
       <c r="E2" s="65" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="F2" s="65" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
       <c r="G2" s="65" t="s">
         <v>677</v>
@@ -36320,16 +36317,16 @@
         <v>700</v>
       </c>
       <c r="K2" s="65" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="L2" s="65" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="M2" s="65" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="N2" s="65" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="O2" s="65" t="s">
         <v>701</v>
@@ -36398,10 +36395,10 @@
         <v>718</v>
       </c>
       <c r="E4" s="54" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="F4" s="54" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="G4" s="53">
         <v>4</v>
@@ -36425,7 +36422,7 @@
         <v>96</v>
       </c>
       <c r="N4" s="90" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="O4" s="90" t="b">
         <v>1</v>
@@ -40726,7 +40723,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="169.5" customHeight="1">
       <c r="A1" s="159" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="B1" s="160"/>
       <c r="C1" s="160"/>
@@ -40755,46 +40752,46 @@
         <v>6</v>
       </c>
       <c r="C2" s="34" t="s">
+        <v>896</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E2" s="103" t="s">
+        <v>897</v>
+      </c>
+      <c r="F2" s="103" t="s">
+        <v>898</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>899</v>
+      </c>
+      <c r="H2" s="103" t="s">
+        <v>900</v>
+      </c>
+      <c r="I2" s="34" t="s">
         <v>901</v>
       </c>
-      <c r="D2" s="34" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E2" s="103" t="s">
+      <c r="J2" s="34" t="s">
         <v>902</v>
       </c>
-      <c r="F2" s="103" t="s">
+      <c r="K2" s="34" t="s">
         <v>903</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="L2" s="124" t="s">
+        <v>990</v>
+      </c>
+      <c r="M2" s="124" t="s">
+        <v>991</v>
+      </c>
+      <c r="N2" s="34" t="s">
         <v>904</v>
       </c>
-      <c r="H2" s="103" t="s">
+      <c r="O2" s="34" t="s">
         <v>905</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="P2" s="34" t="s">
         <v>906</v>
-      </c>
-      <c r="J2" s="34" t="s">
-        <v>907</v>
-      </c>
-      <c r="K2" s="34" t="s">
-        <v>908</v>
-      </c>
-      <c r="L2" s="124" t="s">
-        <v>995</v>
-      </c>
-      <c r="M2" s="124" t="s">
-        <v>996</v>
-      </c>
-      <c r="N2" s="34" t="s">
-        <v>909</v>
-      </c>
-      <c r="O2" s="34" t="s">
-        <v>910</v>
-      </c>
-      <c r="P2" s="34" t="s">
-        <v>911</v>
       </c>
       <c r="Q2" s="34" t="s">
         <v>94</v>
@@ -40811,49 +40808,49 @@
         <v>552</v>
       </c>
       <c r="C3" s="32" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H3" s="32" t="s">
         <v>1076</v>
-      </c>
-      <c r="D3" s="32" t="s">
-        <v>1077</v>
-      </c>
-      <c r="E3" s="32" t="s">
-        <v>1078</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>1079</v>
-      </c>
-      <c r="G3" s="32" t="s">
-        <v>1080</v>
-      </c>
-      <c r="H3" s="32" t="s">
-        <v>1081</v>
       </c>
       <c r="I3" s="32" t="s">
         <v>55</v>
       </c>
       <c r="J3" s="32" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
       <c r="K3" s="32">
         <v>16</v>
       </c>
       <c r="L3" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="M3" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="N3" s="32">
         <v>3</v>
       </c>
       <c r="O3" s="32" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="P3" s="32" t="b">
         <v>0</v>
       </c>
       <c r="Q3" s="32" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="R3" s="28"/>
     </row>
@@ -40865,18 +40862,18 @@
         <v>552</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="E4" s="32"/>
       <c r="F4" s="32"/>
       <c r="G4" s="32" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="I4" s="32" t="s">
         <v>55</v>
@@ -40893,7 +40890,7 @@
         <v>3</v>
       </c>
       <c r="O4" s="32" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
       <c r="P4" s="32" t="b">
         <v>0</v>
@@ -40998,7 +40995,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="52" customHeight="1">
       <c r="A1" s="151" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="B1" s="160"/>
       <c r="C1" s="160"/>
@@ -41019,43 +41016,43 @@
         <v>0</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="C2" s="103" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="D2" s="34" t="s">
+        <v>907</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>908</v>
+      </c>
+      <c r="F2" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>910</v>
+      </c>
+      <c r="H2" s="34" t="s">
+        <v>911</v>
+      </c>
+      <c r="I2" s="34" t="s">
         <v>912</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="J2" s="34" t="s">
         <v>913</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="K2" s="34" t="s">
         <v>914</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="L2" s="34" t="s">
         <v>915</v>
       </c>
-      <c r="H2" s="34" t="s">
+      <c r="M2" s="34" t="s">
         <v>916</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="N2" s="34" t="s">
         <v>917</v>
-      </c>
-      <c r="J2" s="34" t="s">
-        <v>918</v>
-      </c>
-      <c r="K2" s="34" t="s">
-        <v>919</v>
-      </c>
-      <c r="L2" s="34" t="s">
-        <v>920</v>
-      </c>
-      <c r="M2" s="34" t="s">
-        <v>921</v>
-      </c>
-      <c r="N2" s="34" t="s">
-        <v>922</v>
       </c>
       <c r="O2" s="48"/>
     </row>
@@ -41064,43 +41061,43 @@
         <v>5</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
       <c r="D3" s="32" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I3" s="32" t="s">
         <v>1090</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="J3" s="32" t="s">
         <v>1091</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="K3" s="32" t="s">
         <v>1092</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="L3" s="32" t="s">
         <v>1093</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="M3" s="32" t="s">
         <v>1094</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="N3" s="32" t="s">
         <v>1095</v>
-      </c>
-      <c r="J3" s="32" t="s">
-        <v>1096</v>
-      </c>
-      <c r="K3" s="32" t="s">
-        <v>1097</v>
-      </c>
-      <c r="L3" s="32" t="s">
-        <v>1098</v>
-      </c>
-      <c r="M3" s="32" t="s">
-        <v>1099</v>
-      </c>
-      <c r="N3" s="32" t="s">
-        <v>1100</v>
       </c>
       <c r="O3" s="118"/>
     </row>
@@ -41109,41 +41106,41 @@
         <v>5</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="E4" s="32"/>
       <c r="F4" s="32" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>1090</v>
+      </c>
+      <c r="J4" s="32" t="s">
+        <v>1091</v>
+      </c>
+      <c r="K4" s="32" t="s">
         <v>1092</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="L4" s="32" t="s">
         <v>1093</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="M4" s="32" t="s">
         <v>1094</v>
       </c>
-      <c r="I4" s="32" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J4" s="32" t="s">
+      <c r="N4" s="32" t="s">
         <v>1096</v>
-      </c>
-      <c r="K4" s="32" t="s">
-        <v>1097</v>
-      </c>
-      <c r="L4" s="32" t="s">
-        <v>1098</v>
-      </c>
-      <c r="M4" s="32" t="s">
-        <v>1099</v>
-      </c>
-      <c r="N4" s="32" t="s">
-        <v>1101</v>
       </c>
       <c r="O4" s="118"/>
     </row>
@@ -41235,7 +41232,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="40" customFormat="1" ht="166" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="B1" s="138"/>
       <c r="C1" s="138"/>
@@ -41250,22 +41247,22 @@
         <v>0</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
       <c r="D2" s="26" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="G2" s="125" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="H2" s="26" t="s">
         <v>421</v>
@@ -42225,7 +42222,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="292" customHeight="1">
       <c r="A1" s="162" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="B1" s="163"/>
       <c r="C1" s="163"/>
@@ -42253,49 +42250,49 @@
         <v>6</v>
       </c>
       <c r="C2" s="26" t="s">
+        <v>918</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>919</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>920</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>921</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>922</v>
+      </c>
+      <c r="H2" s="26" t="s">
         <v>923</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="I2" s="26" t="s">
         <v>924</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="J2" s="26" t="s">
         <v>925</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="K2" s="27" t="s">
         <v>926</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="L2" s="26" t="s">
         <v>927</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="M2" s="27" t="s">
         <v>928</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="N2" s="27" t="s">
         <v>929</v>
       </c>
-      <c r="J2" s="26" t="s">
+      <c r="O2" s="27" t="s">
         <v>930</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="P2" s="27" t="s">
         <v>931</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="Q2" s="27" t="s">
         <v>932</v>
-      </c>
-      <c r="M2" s="27" t="s">
-        <v>933</v>
-      </c>
-      <c r="N2" s="27" t="s">
-        <v>934</v>
-      </c>
-      <c r="O2" s="27" t="s">
-        <v>935</v>
-      </c>
-      <c r="P2" s="27" t="s">
-        <v>936</v>
-      </c>
-      <c r="Q2" s="27" t="s">
-        <v>937</v>
       </c>
       <c r="R2" s="26" t="s">
         <v>421</v>
@@ -42314,43 +42311,43 @@
         <v>552</v>
       </c>
       <c r="C4" s="33" t="s">
+        <v>933</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>934</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>935</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>935</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>936</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>937</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>983</v>
+      </c>
+      <c r="J4" s="28" t="s">
         <v>938</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="K4" s="28" t="s">
         <v>939</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="L4" s="28" t="s">
         <v>940</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>940</v>
-      </c>
-      <c r="G4" s="33" t="s">
-        <v>941</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>942</v>
-      </c>
-      <c r="I4" s="29" t="s">
-        <v>988</v>
-      </c>
-      <c r="J4" s="28" t="s">
-        <v>943</v>
-      </c>
-      <c r="K4" s="28" t="s">
-        <v>944</v>
-      </c>
-      <c r="L4" s="28" t="s">
-        <v>945</v>
       </c>
       <c r="M4" s="28" t="b">
         <v>1</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="O4" s="28" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="P4" s="28"/>
       <c r="Q4" s="28"/>
@@ -42363,40 +42360,40 @@
         <v>552</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="H5" s="33" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="I5" s="29" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="J5" s="28" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="K5" s="28" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="L5" s="28" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="M5" s="28" t="b">
         <v>1</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="O5" s="28"/>
       <c r="P5" s="28"/>
@@ -42410,22 +42407,22 @@
         <v>552</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="I6" s="29"/>
       <c r="J6" s="28"/>
@@ -42445,38 +42442,38 @@
         <v>552</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="I7" s="29" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="J7" s="28"/>
       <c r="K7" s="28" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="L7" s="28" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="M7" s="28" t="b">
         <v>1</v>
       </c>
       <c r="N7" s="29" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="O7" s="28"/>
       <c r="P7" s="28"/>
@@ -42598,7 +42595,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="234" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1461</v>
+        <v>1456</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -42607,7 +42604,7 @@
       <c r="F1" s="136"/>
       <c r="G1" s="136"/>
       <c r="H1" s="147" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="I1" s="136"/>
       <c r="J1" s="136"/>
@@ -42622,46 +42619,46 @@
         <v>0</v>
       </c>
       <c r="B2" s="16" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C2" s="120" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F2" s="16" t="s">
         <v>1103</v>
       </c>
-      <c r="C2" s="120" t="s">
+      <c r="G2" s="49" t="s">
         <v>1104</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="H2" s="92" t="s">
         <v>1105</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="I2" s="16" t="s">
         <v>1106</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="J2" s="121" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K2" s="16" t="s">
         <v>1108</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="L2" s="16" t="s">
         <v>1109</v>
       </c>
-      <c r="H2" s="92" t="s">
+      <c r="M2" s="122" t="s">
         <v>1110</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="N2" s="16" t="s">
+        <v>1102</v>
+      </c>
+      <c r="O2" s="16" t="s">
         <v>1111</v>
-      </c>
-      <c r="J2" s="121" t="s">
-        <v>1112</v>
-      </c>
-      <c r="K2" s="16" t="s">
-        <v>1113</v>
-      </c>
-      <c r="L2" s="16" t="s">
-        <v>1114</v>
-      </c>
-      <c r="M2" s="122" t="s">
-        <v>1115</v>
-      </c>
-      <c r="N2" s="16" t="s">
-        <v>1107</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="16">
@@ -42691,23 +42688,23 @@
         <v>554</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
       <c r="E4" s="32"/>
       <c r="F4" s="32" t="s">
         <v>554</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
       <c r="J4" s="123">
         <v>256</v>
@@ -42728,19 +42725,19 @@
         <v>552</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="I5" s="32" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
       <c r="J5" s="123">
         <v>384</v>
       </c>
       <c r="K5" s="32" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
       <c r="L5" s="32"/>
       <c r="M5" s="123"/>
@@ -42755,10 +42752,10 @@
         <v>554</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>5</v>
@@ -42767,13 +42764,13 @@
         <v>554</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
       <c r="J6" s="123">
         <v>128</v>
@@ -42798,13 +42795,13 @@
         <v>552</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="H7" s="32" t="s">
+        <v>1118</v>
+      </c>
+      <c r="I7" s="32" t="s">
         <v>1123</v>
-      </c>
-      <c r="I7" s="32" t="s">
-        <v>1128</v>
       </c>
       <c r="J7" s="123">
         <v>3072</v>
@@ -42825,19 +42822,19 @@
         <v>553</v>
       </c>
       <c r="G8" s="32" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
       <c r="H8" s="32" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
       <c r="J8" s="123">
         <v>521</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="L8" s="32" t="b">
         <v>1</v>
@@ -43903,7 +43900,7 @@
   <sheetData>
     <row r="1" spans="1:29" ht="212" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>1463</v>
+        <v>1458</v>
       </c>
       <c r="B1" s="160"/>
       <c r="C1" s="160"/>
@@ -43913,7 +43910,7 @@
       <c r="G1" s="160"/>
       <c r="H1" s="161"/>
       <c r="I1" s="151" t="s">
-        <v>1464</v>
+        <v>1459</v>
       </c>
       <c r="J1" s="152"/>
       <c r="K1" s="152"/>
@@ -43950,10 +43947,10 @@
         <v>2</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>1465</v>
+        <v>1460</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>1466</v>
+        <v>1461</v>
       </c>
       <c r="G2" s="34" t="s">
         <v>83</v>
@@ -43962,64 +43959,64 @@
         <v>85</v>
       </c>
       <c r="I2" s="34" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="J2" s="35" t="s">
         <v>84</v>
       </c>
       <c r="K2" s="35" t="s">
-        <v>1467</v>
+        <v>1462</v>
       </c>
       <c r="L2" s="35" t="s">
-        <v>1468</v>
+        <v>1463</v>
       </c>
       <c r="M2" s="34" t="s">
         <v>92</v>
       </c>
       <c r="N2" s="34" t="s">
+        <v>1464</v>
+      </c>
+      <c r="O2" s="34" t="s">
+        <v>1465</v>
+      </c>
+      <c r="P2" s="34" t="s">
+        <v>1466</v>
+      </c>
+      <c r="Q2" s="34" t="s">
+        <v>1467</v>
+      </c>
+      <c r="R2" s="34" t="s">
+        <v>1468</v>
+      </c>
+      <c r="S2" s="34" t="s">
         <v>1469</v>
       </c>
-      <c r="O2" s="34" t="s">
+      <c r="T2" s="34" t="s">
         <v>1470</v>
       </c>
-      <c r="P2" s="34" t="s">
+      <c r="U2" s="34" t="s">
         <v>1471</v>
       </c>
-      <c r="Q2" s="34" t="s">
+      <c r="V2" s="34" t="s">
         <v>1472</v>
       </c>
-      <c r="R2" s="34" t="s">
+      <c r="W2" s="34" t="s">
         <v>1473</v>
       </c>
-      <c r="S2" s="34" t="s">
+      <c r="X2" s="34" t="s">
         <v>1474</v>
       </c>
-      <c r="T2" s="34" t="s">
+      <c r="Y2" s="34" t="s">
         <v>1475</v>
       </c>
-      <c r="U2" s="34" t="s">
+      <c r="Z2" s="34" t="s">
         <v>1476</v>
-      </c>
-      <c r="V2" s="34" t="s">
-        <v>1477</v>
-      </c>
-      <c r="W2" s="34" t="s">
-        <v>1478</v>
-      </c>
-      <c r="X2" s="34" t="s">
-        <v>1479</v>
-      </c>
-      <c r="Y2" s="34" t="s">
-        <v>1480</v>
-      </c>
-      <c r="Z2" s="34" t="s">
-        <v>1481</v>
       </c>
       <c r="AA2" s="34" t="s">
         <v>75</v>
       </c>
       <c r="AB2" s="34" t="s">
-        <v>1482</v>
+        <v>1477</v>
       </c>
       <c r="AC2" s="35" t="s">
         <v>421</v>
@@ -44066,16 +44063,16 @@
         <v>553</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>1484</v>
+        <v>1479</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>1485</v>
+        <v>1480</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>1486</v>
+        <v>1481</v>
       </c>
       <c r="G4" s="18" t="s">
         <v>55</v>
@@ -44084,58 +44081,58 @@
         <v>349</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>1487</v>
+        <v>1482</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="33" t="s">
+        <v>1483</v>
+      </c>
+      <c r="N4" s="18" t="s">
+        <v>1484</v>
+      </c>
+      <c r="O4" s="18" t="s">
+        <v>1484</v>
+      </c>
+      <c r="P4" s="18" t="s">
+        <v>1485</v>
+      </c>
+      <c r="Q4" s="18" t="s">
+        <v>1486</v>
+      </c>
+      <c r="R4" s="18" t="s">
+        <v>1487</v>
+      </c>
+      <c r="S4" s="18" t="s">
         <v>1488</v>
       </c>
-      <c r="N4" s="18" t="s">
+      <c r="T4" s="18" t="s">
         <v>1489</v>
-      </c>
-      <c r="O4" s="18" t="s">
-        <v>1489</v>
-      </c>
-      <c r="P4" s="18" t="s">
-        <v>1490</v>
-      </c>
-      <c r="Q4" s="18" t="s">
-        <v>1491</v>
-      </c>
-      <c r="R4" s="18" t="s">
-        <v>1492</v>
-      </c>
-      <c r="S4" s="18" t="s">
-        <v>1493</v>
-      </c>
-      <c r="T4" s="18" t="s">
-        <v>1494</v>
       </c>
       <c r="U4" s="18" t="s">
         <v>192</v>
       </c>
       <c r="V4" s="18" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="W4" s="18" t="s">
-        <v>1486</v>
+        <v>1481</v>
       </c>
       <c r="X4" s="129" t="s">
-        <v>1496</v>
+        <v>1491</v>
       </c>
       <c r="Y4" s="18" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
       <c r="Z4" s="18" t="s">
-        <v>1498</v>
+        <v>1493</v>
       </c>
       <c r="AA4" s="18"/>
       <c r="AB4" s="8" t="s">
-        <v>1499</v>
+        <v>1494</v>
       </c>
       <c r="AC4" s="18"/>
     </row>
@@ -44147,16 +44144,16 @@
         <v>553</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>1500</v>
+        <v>1495</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>1501</v>
+        <v>1496</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>1502</v>
+        <v>1497</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>1486</v>
+        <v>1481</v>
       </c>
       <c r="G5" s="32" t="s">
         <v>89</v>
@@ -44165,56 +44162,56 @@
         <v>103</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>1487</v>
+        <v>1482</v>
       </c>
       <c r="K5" s="32"/>
       <c r="L5" s="32"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32" t="s">
+        <v>1484</v>
+      </c>
+      <c r="O5" s="32" t="s">
+        <v>1484</v>
+      </c>
+      <c r="P5" s="32" t="s">
+        <v>1485</v>
+      </c>
+      <c r="Q5" s="32" t="s">
+        <v>1486</v>
+      </c>
+      <c r="R5" s="32" t="s">
+        <v>1487</v>
+      </c>
+      <c r="S5" s="32" t="s">
+        <v>1488</v>
+      </c>
+      <c r="T5" s="32" t="s">
         <v>1489</v>
-      </c>
-      <c r="O5" s="32" t="s">
-        <v>1489</v>
-      </c>
-      <c r="P5" s="32" t="s">
-        <v>1490</v>
-      </c>
-      <c r="Q5" s="32" t="s">
-        <v>1491</v>
-      </c>
-      <c r="R5" s="32" t="s">
-        <v>1492</v>
-      </c>
-      <c r="S5" s="32" t="s">
-        <v>1493</v>
-      </c>
-      <c r="T5" s="32" t="s">
-        <v>1494</v>
       </c>
       <c r="U5" s="32" t="s">
         <v>192</v>
       </c>
       <c r="V5" s="32" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="W5" s="32" t="s">
-        <v>1486</v>
+        <v>1481</v>
       </c>
       <c r="X5" s="32" t="s">
-        <v>1496</v>
+        <v>1491</v>
       </c>
       <c r="Y5" s="32" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
       <c r="Z5" s="32" t="s">
-        <v>1498</v>
+        <v>1493</v>
       </c>
       <c r="AA5" s="32"/>
       <c r="AB5" s="33" t="s">
-        <v>1503</v>
+        <v>1498</v>
       </c>
       <c r="AC5" s="32"/>
     </row>
@@ -50178,7 +50175,7 @@
   <sheetData>
     <row r="1" spans="1:81" ht="185" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1504</v>
+        <v>1499</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -50204,13 +50201,13 @@
         <v>2</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>1505</v>
+        <v>1500</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>1506</v>
+        <v>1501</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>1507</v>
+        <v>1502</v>
       </c>
       <c r="H2" s="26" t="s">
         <v>421</v>
@@ -50233,23 +50230,23 @@
     </row>
     <row r="4" spans="1:81" ht="32" customHeight="1">
       <c r="A4" s="32" t="s">
-        <v>1508</v>
+        <v>1503</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>553</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="D4" s="32"/>
       <c r="E4" s="32" t="s">
-        <v>1487</v>
+        <v>1482</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>1509</v>
+        <v>1504</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>1510</v>
+        <v>1505</v>
       </c>
       <c r="H4" s="32"/>
     </row>
@@ -50260,32 +50257,32 @@
       <c r="D5" s="32"/>
       <c r="E5" s="32"/>
       <c r="F5" s="32" t="s">
-        <v>1511</v>
+        <v>1506</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>1512</v>
+        <v>1507</v>
       </c>
       <c r="H5" s="32"/>
     </row>
     <row r="6" spans="1:81" ht="32" customHeight="1">
       <c r="A6" s="32" t="s">
-        <v>1508</v>
+        <v>1503</v>
       </c>
       <c r="B6" s="32" t="s">
         <v>553</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>1500</v>
+        <v>1495</v>
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="32" t="s">
-        <v>1487</v>
+        <v>1482</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>1509</v>
+        <v>1504</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>1510</v>
+        <v>1505</v>
       </c>
       <c r="H6" s="32"/>
     </row>
@@ -50296,10 +50293,10 @@
       <c r="D7" s="32"/>
       <c r="E7" s="32"/>
       <c r="F7" s="32" t="s">
-        <v>1513</v>
+        <v>1508</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>1514</v>
+        <v>1509</v>
       </c>
       <c r="H7" s="32"/>
     </row>
@@ -50310,10 +50307,10 @@
       <c r="D8" s="32"/>
       <c r="E8" s="32"/>
       <c r="F8" s="32" t="s">
-        <v>1515</v>
+        <v>1510</v>
       </c>
       <c r="G8" s="32" t="s">
-        <v>1516</v>
+        <v>1511</v>
       </c>
       <c r="H8" s="32"/>
     </row>
@@ -51807,7 +51804,7 @@
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="33" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="F12" s="33"/>
       <c r="H12" s="33" t="s">
@@ -51824,7 +51821,7 @@
       </c>
       <c r="D13" s="33"/>
       <c r="E13" s="33" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="F13" s="33"/>
       <c r="H13" s="33" t="s">
@@ -52386,25 +52383,25 @@
         <v>616</v>
       </c>
       <c r="D1" s="64" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="E1" s="64" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
       <c r="F1" s="64" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="G1" s="64" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="H1" s="64" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="I1" s="64" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="J1" s="64" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="K1" s="64" t="s">
         <v>618</v>
@@ -52512,13 +52509,13 @@
         <v>829</v>
       </c>
       <c r="AT1" s="55" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="AU1" s="55" t="s">
         <v>617</v>
       </c>
       <c r="AV1" s="55" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
     </row>
     <row r="2" spans="1:48" s="57" customFormat="1" ht="16">
@@ -52564,7 +52561,7 @@
         <v>21</v>
       </c>
       <c r="L2" s="126" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="M2" s="58" t="s">
         <v>38</v>
@@ -52583,7 +52580,7 @@
         <v>23</v>
       </c>
       <c r="R2" s="58" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="S2" s="58" t="s">
         <v>569</v>
@@ -53082,7 +53079,7 @@
       <c r="J6" s="33"/>
       <c r="K6" s="58"/>
       <c r="L6" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="M6" s="58"/>
       <c r="N6" s="58"/>
@@ -53866,7 +53863,7 @@
       <c r="J16" s="33"/>
       <c r="K16" s="58"/>
       <c r="L16" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="M16" s="58"/>
       <c r="N16" s="58"/>
@@ -54389,7 +54386,7 @@
       <c r="J23" s="33"/>
       <c r="K23" s="58"/>
       <c r="L23" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="M23" s="58"/>
       <c r="N23" s="58"/>
@@ -54535,7 +54532,7 @@
       <c r="J25" s="33"/>
       <c r="K25" s="58"/>
       <c r="L25" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="M25" s="58"/>
       <c r="N25" s="58"/>
@@ -54681,7 +54678,7 @@
       <c r="J27" s="33"/>
       <c r="K27" s="58"/>
       <c r="L27" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="M27" s="58"/>
       <c r="N27" s="58"/>
@@ -54900,7 +54897,7 @@
       <c r="J30" s="33"/>
       <c r="K30" s="58"/>
       <c r="L30" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
       <c r="M30" s="58"/>
       <c r="N30" s="58"/>
@@ -55119,7 +55116,7 @@
       <c r="J33" s="33"/>
       <c r="K33" s="58"/>
       <c r="L33" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="M33" s="58"/>
       <c r="N33" s="58"/>
@@ -55249,7 +55246,7 @@
       <c r="J35" s="33"/>
       <c r="K35" s="58"/>
       <c r="L35" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="M35" s="58"/>
       <c r="N35" s="58"/>
@@ -55305,7 +55302,7 @@
       <c r="J36" s="33"/>
       <c r="K36" s="58"/>
       <c r="L36" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="M36" s="58"/>
       <c r="N36" s="58"/>
@@ -55378,7 +55375,7 @@
       <c r="J37" s="33"/>
       <c r="K37" s="58"/>
       <c r="L37" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="M37" s="58"/>
       <c r="N37" s="58"/>
@@ -55670,7 +55667,7 @@
       <c r="J41" s="33"/>
       <c r="K41" s="58"/>
       <c r="L41" s="63" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
       <c r="M41" s="58"/>
       <c r="N41" s="58"/>
@@ -55880,7 +55877,7 @@
       <c r="I45" s="33"/>
       <c r="J45" s="33"/>
       <c r="L45" s="57" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
       <c r="P45" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P45" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A45,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A45,4,4,1,"DHCP")))</f>
@@ -55926,7 +55923,7 @@
       <c r="I46" s="33"/>
       <c r="J46" s="33"/>
       <c r="L46" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="P46" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P46" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A46,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A46,4,4,1,"DHCP")))</f>
@@ -55972,7 +55969,7 @@
       <c r="I47" s="33"/>
       <c r="J47" s="33"/>
       <c r="L47" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="P47" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P47" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A47,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A47,4,4,1,"DHCP")))</f>
@@ -56018,7 +56015,7 @@
       <c r="I48" s="33"/>
       <c r="J48" s="33"/>
       <c r="L48" s="40" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
       <c r="P48" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P48" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A48,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A48,4,4,1,"DHCP")))</f>
@@ -56064,7 +56061,7 @@
       <c r="I49" s="33"/>
       <c r="J49" s="33"/>
       <c r="L49" t="s">
-        <v>841</v>
+        <v>1618</v>
       </c>
       <c r="P49" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P49" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A49,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A49,4,4,1,"DHCP")))</f>
@@ -56110,7 +56107,7 @@
       <c r="I50" s="33"/>
       <c r="J50" s="33"/>
       <c r="L50" t="s">
-        <v>843</v>
+        <v>1619</v>
       </c>
       <c r="P50" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P50" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A50,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A50,4,4,1,"DHCP")))</f>
@@ -56145,7 +56142,7 @@
       <c r="I51" s="33"/>
       <c r="J51" s="33"/>
       <c r="L51" t="s">
-        <v>845</v>
+        <v>1503</v>
       </c>
       <c r="AG51" s="63"/>
       <c r="AU51" s="101" t="str">
@@ -56165,7 +56162,7 @@
       <c r="I52" s="33"/>
       <c r="J52" s="33"/>
       <c r="L52" s="40" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="AU52" s="101" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -56185,7 +56182,7 @@
       <c r="I53" s="33"/>
       <c r="J53" s="33"/>
       <c r="L53" t="s">
-        <v>844</v>
+        <v>1620</v>
       </c>
       <c r="AU53" s="101" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -56205,7 +56202,7 @@
       <c r="I54" s="33"/>
       <c r="J54" s="33"/>
       <c r="L54" t="s">
-        <v>842</v>
+        <v>1621</v>
       </c>
       <c r="AU54" s="101" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -59079,10 +59076,10 @@
         <v>668</v>
       </c>
       <c r="C1" s="55" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="D1" s="55" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -59582,7 +59579,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="40" customFormat="1" ht="134.25" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="B1" s="138"/>
       <c r="C1" s="138"/>
@@ -59601,10 +59598,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>421</v>
@@ -59654,7 +59651,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="40" customFormat="1" ht="131" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -59704,7 +59701,7 @@
         <v>593</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="F3" s="32"/>
       <c r="G3" s="32"/>
@@ -59716,7 +59713,7 @@
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
       <c r="E4" s="32" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="F4" s="32"/>
       <c r="G4" s="32"/>
@@ -59727,16 +59724,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>1574</v>
+        <v>1569</v>
       </c>
       <c r="C5" s="32" t="s">
         <v>397</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>1575</v>
+        <v>1570</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>1576</v>
+        <v>1571</v>
       </c>
       <c r="F5" s="32"/>
       <c r="G5" s="32"/>
@@ -59748,7 +59745,7 @@
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="E6" s="32" t="s">
-        <v>1577</v>
+        <v>1572</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -59760,7 +59757,7 @@
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="E7" s="32" t="s">
-        <v>1578</v>
+        <v>1573</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -59780,7 +59777,7 @@
         <v>556</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -59792,7 +59789,7 @@
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="E9" s="32" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -59804,7 +59801,7 @@
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="E10" s="32" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -59816,7 +59813,7 @@
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="E11" s="32" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
@@ -59828,7 +59825,7 @@
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="E12" s="32" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -59840,7 +59837,7 @@
       <c r="C13" s="32"/>
       <c r="D13" s="32"/>
       <c r="E13" s="32" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -59852,7 +59849,7 @@
       <c r="C14" s="32"/>
       <c r="D14" s="32"/>
       <c r="E14" s="32" t="s">
-        <v>1208</v>
+        <v>1203</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -59864,7 +59861,7 @@
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
       <c r="E15" s="32" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -59876,7 +59873,7 @@
       <c r="C16" s="32"/>
       <c r="D16" s="32"/>
       <c r="E16" s="32" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -59888,7 +59885,7 @@
       <c r="C17" s="32"/>
       <c r="D17" s="32"/>
       <c r="E17" s="32" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
@@ -59900,7 +59897,7 @@
       <c r="C18" s="32"/>
       <c r="D18" s="32"/>
       <c r="E18" s="32" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -59912,7 +59909,7 @@
       <c r="C19" s="32"/>
       <c r="D19" s="32"/>
       <c r="E19" s="32" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -59924,7 +59921,7 @@
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
       <c r="E20" s="32" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
@@ -59936,7 +59933,7 @@
       <c r="C21" s="32"/>
       <c r="D21" s="32"/>
       <c r="E21" s="32" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="F21" s="32"/>
       <c r="G21" s="32"/>
@@ -59948,7 +59945,7 @@
       <c r="C22" s="32"/>
       <c r="D22" s="32"/>
       <c r="E22" s="32" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
@@ -59960,7 +59957,7 @@
       <c r="C23" s="32"/>
       <c r="D23" s="32"/>
       <c r="E23" s="32" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32"/>
@@ -59972,7 +59969,7 @@
       <c r="C24" s="32"/>
       <c r="D24" s="32"/>
       <c r="E24" s="32" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="32"/>
@@ -59984,7 +59981,7 @@
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
       <c r="E25" s="32" t="s">
-        <v>1219</v>
+        <v>1214</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
@@ -59996,7 +59993,7 @@
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
       <c r="E26" s="32" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
@@ -60008,7 +60005,7 @@
       <c r="C27" s="32"/>
       <c r="D27" s="32"/>
       <c r="E27" s="32" t="s">
-        <v>1221</v>
+        <v>1216</v>
       </c>
       <c r="F27" s="32"/>
       <c r="G27" s="32"/>
@@ -60020,7 +60017,7 @@
       <c r="C28" s="32"/>
       <c r="D28" s="32"/>
       <c r="E28" s="32" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="F28" s="32"/>
       <c r="G28" s="32"/>
@@ -60032,7 +60029,7 @@
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="E29" s="32" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="F29" s="32"/>
       <c r="G29" s="32"/>
@@ -60044,7 +60041,7 @@
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="E30" s="32" t="s">
-        <v>1224</v>
+        <v>1219</v>
       </c>
       <c r="F30" s="32"/>
       <c r="G30" s="32"/>
@@ -60056,7 +60053,7 @@
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="E31" s="32" t="s">
-        <v>1225</v>
+        <v>1220</v>
       </c>
       <c r="F31" s="32"/>
       <c r="G31" s="32"/>
@@ -60068,7 +60065,7 @@
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="E32" s="32" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="F32" s="32"/>
       <c r="G32" s="32"/>
@@ -60080,7 +60077,7 @@
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
       <c r="E33" s="32" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="F33" s="32"/>
       <c r="G33" s="32"/>
@@ -60092,7 +60089,7 @@
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
       <c r="E34" s="32" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="F34" s="32"/>
       <c r="G34" s="32"/>
@@ -60104,7 +60101,7 @@
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="E35" s="32" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="F35" s="32"/>
       <c r="G35" s="32"/>
@@ -60116,7 +60113,7 @@
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="E36" s="32" t="s">
-        <v>1579</v>
+        <v>1574</v>
       </c>
       <c r="F36" s="32"/>
       <c r="G36" s="32"/>
@@ -60128,7 +60125,7 @@
       <c r="C37" s="32"/>
       <c r="D37" s="32"/>
       <c r="E37" s="32" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="F37" s="32"/>
       <c r="G37" s="32"/>
@@ -60140,7 +60137,7 @@
       <c r="C38" s="32"/>
       <c r="D38" s="32"/>
       <c r="E38" s="32" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="F38" s="32"/>
       <c r="G38" s="32"/>
@@ -60152,7 +60149,7 @@
       <c r="C39" s="32"/>
       <c r="D39" s="32"/>
       <c r="E39" s="32" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="F39" s="32"/>
       <c r="G39" s="32"/>
@@ -60164,7 +60161,7 @@
       <c r="C40" s="32"/>
       <c r="D40" s="32"/>
       <c r="E40" s="32" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="F40" s="32"/>
       <c r="G40" s="32"/>
@@ -60176,7 +60173,7 @@
       <c r="C41" s="32"/>
       <c r="D41" s="32"/>
       <c r="E41" s="32" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="F41" s="32"/>
       <c r="G41" s="32"/>
@@ -60188,7 +60185,7 @@
       <c r="C42" s="32"/>
       <c r="D42" s="32"/>
       <c r="E42" s="32" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="F42" s="32"/>
       <c r="G42" s="32"/>
@@ -60200,7 +60197,7 @@
       <c r="C43" s="32"/>
       <c r="D43" s="32"/>
       <c r="E43" s="32" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="F43" s="32"/>
       <c r="G43" s="32"/>
@@ -60212,7 +60209,7 @@
       <c r="C44" s="32"/>
       <c r="D44" s="32"/>
       <c r="E44" s="32" t="s">
-        <v>1237</v>
+        <v>1232</v>
       </c>
       <c r="F44" s="32"/>
       <c r="G44" s="32"/>
@@ -60224,7 +60221,7 @@
       <c r="C45" s="32"/>
       <c r="D45" s="32"/>
       <c r="E45" s="32" t="s">
-        <v>1238</v>
+        <v>1233</v>
       </c>
       <c r="F45" s="32"/>
       <c r="G45" s="32"/>
@@ -60236,7 +60233,7 @@
       <c r="C46" s="32"/>
       <c r="D46" s="32"/>
       <c r="E46" s="32" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="F46" s="32"/>
       <c r="G46" s="32"/>
@@ -60248,7 +60245,7 @@
       <c r="C47" s="32"/>
       <c r="D47" s="32"/>
       <c r="E47" s="32" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
       <c r="F47" s="32"/>
       <c r="G47" s="32"/>
@@ -60260,7 +60257,7 @@
       <c r="C48" s="32"/>
       <c r="D48" s="32"/>
       <c r="E48" s="32" t="s">
-        <v>1241</v>
+        <v>1236</v>
       </c>
       <c r="F48" s="32"/>
       <c r="G48" s="32"/>
@@ -60272,7 +60269,7 @@
       <c r="C49" s="32"/>
       <c r="D49" s="32"/>
       <c r="E49" s="32" t="s">
-        <v>1242</v>
+        <v>1237</v>
       </c>
       <c r="F49" s="32"/>
       <c r="G49" s="32"/>
@@ -60284,7 +60281,7 @@
       <c r="C50" s="32"/>
       <c r="D50" s="32"/>
       <c r="E50" s="32" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="F50" s="32"/>
       <c r="G50" s="32"/>
@@ -60304,7 +60301,7 @@
         <v>558</v>
       </c>
       <c r="E51" s="32" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
       <c r="F51" s="32"/>
       <c r="G51" s="32"/>
@@ -60316,7 +60313,7 @@
       <c r="C52" s="32"/>
       <c r="D52" s="32"/>
       <c r="E52" s="32" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="F52" s="32"/>
       <c r="G52" s="32"/>
@@ -60328,7 +60325,7 @@
       <c r="C53" s="32"/>
       <c r="D53" s="32"/>
       <c r="E53" s="32" t="s">
-        <v>1246</v>
+        <v>1241</v>
       </c>
       <c r="F53" s="32"/>
       <c r="G53" s="32"/>
@@ -60340,7 +60337,7 @@
       <c r="C54" s="32"/>
       <c r="D54" s="32"/>
       <c r="E54" s="32" t="s">
-        <v>1247</v>
+        <v>1242</v>
       </c>
       <c r="F54" s="32"/>
       <c r="G54" s="32"/>
@@ -60352,7 +60349,7 @@
       <c r="C55" s="32"/>
       <c r="D55" s="32"/>
       <c r="E55" s="32" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="F55" s="32"/>
       <c r="G55" s="32"/>
@@ -60364,7 +60361,7 @@
       <c r="C56" s="32"/>
       <c r="D56" s="32"/>
       <c r="E56" s="32" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="F56" s="32"/>
       <c r="G56" s="32"/>
@@ -60376,7 +60373,7 @@
       <c r="C57" s="32"/>
       <c r="D57" s="32"/>
       <c r="E57" s="32" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
       <c r="F57" s="32"/>
       <c r="G57" s="32"/>
@@ -60388,7 +60385,7 @@
       <c r="C58" s="32"/>
       <c r="D58" s="32"/>
       <c r="E58" s="32" t="s">
-        <v>1251</v>
+        <v>1246</v>
       </c>
       <c r="F58" s="32"/>
       <c r="G58" s="32"/>
@@ -60400,7 +60397,7 @@
       <c r="C59" s="32"/>
       <c r="D59" s="32"/>
       <c r="E59" s="32" t="s">
-        <v>1252</v>
+        <v>1247</v>
       </c>
       <c r="F59" s="32"/>
       <c r="G59" s="32"/>
@@ -60412,7 +60409,7 @@
       <c r="C60" s="32"/>
       <c r="D60" s="32"/>
       <c r="E60" s="32" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
       <c r="F60" s="32"/>
       <c r="G60" s="32"/>
@@ -60424,7 +60421,7 @@
       <c r="C61" s="32"/>
       <c r="D61" s="32"/>
       <c r="E61" s="32" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="F61" s="32"/>
       <c r="G61" s="32"/>
@@ -60436,7 +60433,7 @@
       <c r="C62" s="32"/>
       <c r="D62" s="32"/>
       <c r="E62" s="32" t="s">
-        <v>1255</v>
+        <v>1250</v>
       </c>
       <c r="F62" s="32"/>
       <c r="G62" s="32"/>
@@ -60448,7 +60445,7 @@
       <c r="C63" s="32"/>
       <c r="D63" s="32"/>
       <c r="E63" s="32" t="s">
-        <v>1256</v>
+        <v>1251</v>
       </c>
       <c r="F63" s="32"/>
       <c r="G63" s="32"/>
@@ -60460,7 +60457,7 @@
       <c r="C64" s="32"/>
       <c r="D64" s="32"/>
       <c r="E64" s="32" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="F64" s="32"/>
       <c r="G64" s="32"/>
@@ -60472,7 +60469,7 @@
       <c r="C65" s="32"/>
       <c r="D65" s="32"/>
       <c r="E65" s="32" t="s">
-        <v>1258</v>
+        <v>1253</v>
       </c>
       <c r="F65" s="32"/>
       <c r="G65" s="32"/>
@@ -60484,7 +60481,7 @@
       <c r="C66" s="32"/>
       <c r="D66" s="32"/>
       <c r="E66" s="32" t="s">
-        <v>1259</v>
+        <v>1254</v>
       </c>
       <c r="F66" s="32"/>
       <c r="G66" s="32"/>
@@ -60496,7 +60493,7 @@
       <c r="C67" s="32"/>
       <c r="D67" s="32"/>
       <c r="E67" s="32" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="F67" s="32"/>
       <c r="G67" s="32"/>
@@ -60508,7 +60505,7 @@
       <c r="C68" s="32"/>
       <c r="D68" s="32"/>
       <c r="E68" s="32" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="F68" s="32"/>
       <c r="G68" s="32"/>
@@ -60520,7 +60517,7 @@
       <c r="C69" s="32"/>
       <c r="D69" s="32"/>
       <c r="E69" s="32" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="F69" s="32"/>
       <c r="G69" s="32"/>
@@ -60532,7 +60529,7 @@
       <c r="C70" s="32"/>
       <c r="D70" s="32"/>
       <c r="E70" s="32" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
       <c r="F70" s="32"/>
       <c r="G70" s="32"/>
@@ -60544,7 +60541,7 @@
       <c r="C71" s="32"/>
       <c r="D71" s="32"/>
       <c r="E71" s="32" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="F71" s="32"/>
       <c r="G71" s="32"/>
@@ -60556,7 +60553,7 @@
       <c r="C72" s="32"/>
       <c r="D72" s="32"/>
       <c r="E72" s="32" t="s">
-        <v>1584</v>
+        <v>1579</v>
       </c>
       <c r="F72" s="32"/>
       <c r="G72" s="32"/>
@@ -60568,7 +60565,7 @@
       <c r="C73" s="32"/>
       <c r="D73" s="32"/>
       <c r="E73" s="32" t="s">
-        <v>1585</v>
+        <v>1580</v>
       </c>
       <c r="F73" s="32"/>
       <c r="G73" s="32"/>
@@ -60580,7 +60577,7 @@
       <c r="C74" s="32"/>
       <c r="D74" s="32"/>
       <c r="E74" s="32" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="F74" s="32"/>
       <c r="G74" s="32"/>
@@ -60592,7 +60589,7 @@
       <c r="C75" s="32"/>
       <c r="D75" s="32"/>
       <c r="E75" s="32" t="s">
-        <v>1587</v>
+        <v>1582</v>
       </c>
       <c r="F75" s="32"/>
       <c r="G75" s="32"/>
@@ -60604,7 +60601,7 @@
       <c r="C76" s="32"/>
       <c r="D76" s="32"/>
       <c r="E76" s="32" t="s">
-        <v>1588</v>
+        <v>1583</v>
       </c>
       <c r="F76" s="32"/>
       <c r="G76" s="32"/>
@@ -60616,7 +60613,7 @@
       <c r="C77" s="32"/>
       <c r="D77" s="32"/>
       <c r="E77" s="32" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="F77" s="32"/>
       <c r="G77" s="32"/>
@@ -60627,16 +60624,16 @@
         <v>5</v>
       </c>
       <c r="B78" s="32" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="C78" s="32" t="s">
         <v>397</v>
       </c>
       <c r="D78" s="32" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="E78" s="132" t="s">
-        <v>1261</v>
+        <v>1256</v>
       </c>
       <c r="F78" s="32"/>
       <c r="G78" s="32"/>
@@ -60648,7 +60645,7 @@
       <c r="C79" s="32"/>
       <c r="D79" s="32"/>
       <c r="E79" s="32" t="s">
-        <v>1262</v>
+        <v>1257</v>
       </c>
       <c r="F79" s="32"/>
       <c r="G79" s="32"/>
@@ -60660,7 +60657,7 @@
       <c r="C80" s="32"/>
       <c r="D80" s="32"/>
       <c r="E80" s="32" t="s">
-        <v>1263</v>
+        <v>1258</v>
       </c>
       <c r="F80" s="32"/>
       <c r="G80" s="32"/>
@@ -60672,7 +60669,7 @@
       <c r="C81" s="32"/>
       <c r="D81" s="32"/>
       <c r="E81" s="32" t="s">
-        <v>1264</v>
+        <v>1259</v>
       </c>
       <c r="F81" s="32"/>
       <c r="G81" s="32"/>
@@ -60689,10 +60686,10 @@
         <v>397</v>
       </c>
       <c r="D82" s="32" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="E82" s="32" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="F82" s="32"/>
       <c r="G82" s="32"/>
@@ -60704,7 +60701,7 @@
       <c r="C83" s="32"/>
       <c r="D83" s="32"/>
       <c r="E83" s="32" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
       <c r="F83" s="32"/>
       <c r="G83" s="32"/>
@@ -60716,7 +60713,7 @@
       <c r="C84" s="32"/>
       <c r="D84" s="32"/>
       <c r="E84" s="32" t="s">
-        <v>1267</v>
+        <v>1262</v>
       </c>
       <c r="F84" s="32"/>
       <c r="G84" s="32"/>
@@ -60728,7 +60725,7 @@
       <c r="C85" s="32"/>
       <c r="D85" s="32"/>
       <c r="E85" s="32" t="s">
-        <v>1268</v>
+        <v>1263</v>
       </c>
       <c r="F85" s="32"/>
       <c r="G85" s="32"/>
@@ -60739,7 +60736,7 @@
         <v>5</v>
       </c>
       <c r="B86" s="32" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="C86" s="32" t="s">
         <v>397</v>
@@ -60748,7 +60745,7 @@
         <v>778</v>
       </c>
       <c r="E86" s="32" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
       <c r="F86" s="32"/>
       <c r="G86" s="32"/>
@@ -60760,7 +60757,7 @@
       <c r="C87" s="32"/>
       <c r="D87" s="32"/>
       <c r="E87" s="32" t="s">
-        <v>1270</v>
+        <v>1265</v>
       </c>
       <c r="F87" s="32"/>
       <c r="G87" s="32"/>
@@ -60772,7 +60769,7 @@
       <c r="C88" s="32"/>
       <c r="D88" s="32"/>
       <c r="E88" s="32" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="F88" s="32"/>
       <c r="G88" s="32"/>
@@ -60784,7 +60781,7 @@
       <c r="C89" s="32"/>
       <c r="D89" s="32"/>
       <c r="E89" s="32" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="F89" s="32"/>
       <c r="G89" s="32"/>
@@ -60796,7 +60793,7 @@
       <c r="C90" s="32"/>
       <c r="D90" s="32"/>
       <c r="E90" s="32" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="F90" s="32"/>
       <c r="G90" s="32"/>
@@ -60808,7 +60805,7 @@
       <c r="C91" s="32"/>
       <c r="D91" s="32"/>
       <c r="E91" s="32" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="F91" s="32"/>
       <c r="G91" s="32"/>
@@ -60820,7 +60817,7 @@
       <c r="C92" s="32"/>
       <c r="D92" s="32"/>
       <c r="E92" s="32" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="F92" s="32"/>
       <c r="G92" s="32"/>
@@ -60832,7 +60829,7 @@
       <c r="C93" s="32"/>
       <c r="D93" s="32"/>
       <c r="E93" s="32" t="s">
-        <v>1271</v>
+        <v>1266</v>
       </c>
       <c r="F93" s="32"/>
       <c r="G93" s="32"/>
@@ -60844,7 +60841,7 @@
       <c r="C94" s="32"/>
       <c r="D94" s="32"/>
       <c r="E94" s="32" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="F94" s="102"/>
       <c r="G94" s="32"/>
@@ -60864,7 +60861,7 @@
         <v>779</v>
       </c>
       <c r="E95" s="32" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="F95" s="32"/>
       <c r="G95" s="32"/>
@@ -60876,7 +60873,7 @@
       <c r="C96" s="32"/>
       <c r="D96" s="32"/>
       <c r="E96" s="32" t="s">
-        <v>1273</v>
+        <v>1268</v>
       </c>
       <c r="F96" s="32"/>
       <c r="G96" s="32"/>
@@ -60888,7 +60885,7 @@
       <c r="C97" s="32"/>
       <c r="D97" s="32"/>
       <c r="E97" s="32" t="s">
-        <v>1274</v>
+        <v>1269</v>
       </c>
       <c r="F97" s="32"/>
       <c r="G97" s="32"/>
@@ -60900,7 +60897,7 @@
       <c r="C98" s="32"/>
       <c r="D98" s="32"/>
       <c r="E98" s="29" t="s">
-        <v>1275</v>
+        <v>1270</v>
       </c>
       <c r="F98" s="32"/>
       <c r="G98" s="32"/>
@@ -60912,7 +60909,7 @@
       <c r="C99" s="32"/>
       <c r="D99" s="32"/>
       <c r="E99" s="29" t="s">
-        <v>1276</v>
+        <v>1271</v>
       </c>
       <c r="F99" s="32"/>
       <c r="G99" s="32"/>
@@ -60924,7 +60921,7 @@
       <c r="C100" s="32"/>
       <c r="D100" s="32"/>
       <c r="E100" s="29" t="s">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="F100" s="32"/>
       <c r="G100" s="32"/>
@@ -60936,7 +60933,7 @@
       <c r="C101" s="32"/>
       <c r="D101" s="32"/>
       <c r="E101" s="29" t="s">
-        <v>1278</v>
+        <v>1273</v>
       </c>
       <c r="F101" s="32"/>
       <c r="G101" s="32"/>
@@ -60948,7 +60945,7 @@
       <c r="C102" s="32"/>
       <c r="D102" s="32"/>
       <c r="E102" s="29" t="s">
-        <v>1279</v>
+        <v>1274</v>
       </c>
       <c r="F102" s="32"/>
       <c r="G102" s="32"/>
@@ -60960,7 +60957,7 @@
       <c r="C103" s="32"/>
       <c r="D103" s="32"/>
       <c r="E103" s="29" t="s">
-        <v>1280</v>
+        <v>1275</v>
       </c>
       <c r="F103" s="32"/>
       <c r="G103" s="32"/>
@@ -60972,7 +60969,7 @@
       <c r="C104" s="32"/>
       <c r="D104" s="32"/>
       <c r="E104" s="29" t="s">
-        <v>1281</v>
+        <v>1276</v>
       </c>
       <c r="F104" s="32"/>
       <c r="G104" s="32"/>
@@ -60984,7 +60981,7 @@
       <c r="C105" s="32"/>
       <c r="D105" s="32"/>
       <c r="E105" s="29" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="F105" s="32"/>
       <c r="G105" s="32"/>
@@ -60996,7 +60993,7 @@
       <c r="C106" s="32"/>
       <c r="D106" s="32"/>
       <c r="E106" s="29" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="F106" s="32"/>
       <c r="G106" s="32"/>
@@ -61008,7 +61005,7 @@
       <c r="C107" s="32"/>
       <c r="D107" s="32"/>
       <c r="E107" s="29" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="F107" s="32"/>
       <c r="G107" s="32"/>
@@ -61020,7 +61017,7 @@
       <c r="C108" s="32"/>
       <c r="D108" s="32"/>
       <c r="E108" s="29" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="F108" s="32"/>
       <c r="G108" s="32"/>
@@ -61032,7 +61029,7 @@
       <c r="C109" s="32"/>
       <c r="D109" s="32"/>
       <c r="E109" s="29" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
       <c r="F109" s="32"/>
       <c r="G109" s="32"/>
@@ -61044,7 +61041,7 @@
       <c r="C110" s="32"/>
       <c r="D110" s="32"/>
       <c r="E110" s="29" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="F110" s="32"/>
       <c r="G110" s="32"/>
@@ -61056,7 +61053,7 @@
       <c r="C111" s="32"/>
       <c r="D111" s="32"/>
       <c r="E111" s="29" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="F111" s="32"/>
       <c r="G111" s="32"/>
@@ -61068,7 +61065,7 @@
       <c r="C112" s="32"/>
       <c r="D112" s="32"/>
       <c r="E112" s="29" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="F112" s="32"/>
       <c r="G112" s="32"/>
@@ -61080,7 +61077,7 @@
       <c r="C113" s="32"/>
       <c r="D113" s="32"/>
       <c r="E113" s="29" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="F113" s="32"/>
       <c r="G113" s="32"/>
@@ -61092,7 +61089,7 @@
       <c r="C114" s="32"/>
       <c r="D114" s="32"/>
       <c r="E114" s="29" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
       <c r="F114" s="32"/>
       <c r="G114" s="32"/>
@@ -61104,7 +61101,7 @@
       <c r="C115" s="32"/>
       <c r="D115" s="32"/>
       <c r="E115" s="29" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
       <c r="F115" s="32"/>
       <c r="G115" s="32"/>
@@ -61116,7 +61113,7 @@
       <c r="C116" s="32"/>
       <c r="D116" s="32"/>
       <c r="E116" s="29" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="F116" s="32"/>
       <c r="G116" s="32"/>
@@ -61128,7 +61125,7 @@
       <c r="C117" s="32"/>
       <c r="D117" s="32"/>
       <c r="E117" s="29" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="F117" s="32"/>
       <c r="G117" s="32"/>
@@ -61140,7 +61137,7 @@
       <c r="C118" s="32"/>
       <c r="D118" s="32"/>
       <c r="E118" s="29" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
       <c r="F118" s="32"/>
       <c r="G118" s="32"/>
@@ -61152,7 +61149,7 @@
       <c r="C119" s="32"/>
       <c r="D119" s="32"/>
       <c r="E119" s="29" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="F119" s="32"/>
       <c r="G119" s="32"/>
@@ -61164,7 +61161,7 @@
       <c r="C120" s="32"/>
       <c r="D120" s="32"/>
       <c r="E120" s="29" t="s">
-        <v>1297</v>
+        <v>1292</v>
       </c>
       <c r="F120" s="32"/>
       <c r="G120" s="32"/>
@@ -61176,7 +61173,7 @@
       <c r="C121" s="32"/>
       <c r="D121" s="32"/>
       <c r="E121" s="29" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="F121" s="32"/>
       <c r="G121" s="32"/>
@@ -61188,7 +61185,7 @@
       <c r="C122" s="32"/>
       <c r="D122" s="32"/>
       <c r="E122" s="29" t="s">
-        <v>1299</v>
+        <v>1294</v>
       </c>
       <c r="F122" s="32"/>
       <c r="G122" s="32"/>
@@ -61200,7 +61197,7 @@
       <c r="C123" s="32"/>
       <c r="D123" s="32"/>
       <c r="E123" s="29" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="F123" s="32"/>
       <c r="G123" s="32"/>
@@ -61212,7 +61209,7 @@
       <c r="C124" s="32"/>
       <c r="D124" s="32"/>
       <c r="E124" s="29" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="F124" s="32"/>
       <c r="G124" s="32"/>
@@ -61224,7 +61221,7 @@
       <c r="C125" s="32"/>
       <c r="D125" s="32"/>
       <c r="E125" s="29" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="F125" s="32"/>
       <c r="G125" s="32"/>
@@ -61236,7 +61233,7 @@
       <c r="C126" s="32"/>
       <c r="D126" s="32"/>
       <c r="E126" s="29" t="s">
-        <v>1303</v>
+        <v>1298</v>
       </c>
       <c r="F126" s="32"/>
       <c r="G126" s="32"/>
@@ -61248,7 +61245,7 @@
       <c r="C127" s="32"/>
       <c r="D127" s="32"/>
       <c r="E127" s="29" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="F127" s="32"/>
       <c r="G127" s="32"/>
@@ -61260,7 +61257,7 @@
       <c r="C128" s="32"/>
       <c r="D128" s="32"/>
       <c r="E128" s="29" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
       <c r="F128" s="32"/>
       <c r="G128" s="32"/>
@@ -61272,7 +61269,7 @@
       <c r="C129" s="32"/>
       <c r="D129" s="32"/>
       <c r="E129" s="29" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="F129" s="32"/>
       <c r="G129" s="32"/>
@@ -61284,7 +61281,7 @@
       <c r="C130" s="32"/>
       <c r="D130" s="32"/>
       <c r="E130" s="29" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="F130" s="32"/>
       <c r="G130" s="32"/>
@@ -61296,7 +61293,7 @@
       <c r="C131" s="32"/>
       <c r="D131" s="32"/>
       <c r="E131" s="32" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
       <c r="F131" s="32"/>
       <c r="G131" s="32"/>
@@ -61308,7 +61305,7 @@
       <c r="C132" s="32"/>
       <c r="D132" s="32"/>
       <c r="E132" s="32" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="F132" s="32"/>
       <c r="G132" s="32"/>
@@ -61320,7 +61317,7 @@
       <c r="C133" s="32"/>
       <c r="D133" s="32"/>
       <c r="E133" s="32" t="s">
-        <v>1308</v>
+        <v>1303</v>
       </c>
       <c r="F133" s="32"/>
       <c r="G133" s="32"/>
@@ -61332,7 +61329,7 @@
       <c r="C134" s="32"/>
       <c r="D134" s="32"/>
       <c r="E134" s="32" t="s">
-        <v>1309</v>
+        <v>1304</v>
       </c>
       <c r="F134" s="32"/>
       <c r="G134" s="32"/>
@@ -61344,7 +61341,7 @@
       <c r="C135" s="32"/>
       <c r="D135" s="32"/>
       <c r="E135" s="32" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="F135" s="32"/>
       <c r="G135" s="32"/>
@@ -61356,7 +61353,7 @@
       <c r="C136" s="32"/>
       <c r="D136" s="32"/>
       <c r="E136" s="32" t="s">
-        <v>1311</v>
+        <v>1306</v>
       </c>
       <c r="F136" s="32"/>
       <c r="G136" s="32"/>
@@ -61376,7 +61373,7 @@
         <v>561</v>
       </c>
       <c r="E137" s="76" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="F137" s="32"/>
       <c r="G137" s="32"/>
@@ -61388,7 +61385,7 @@
       <c r="C138" s="32"/>
       <c r="D138" s="32"/>
       <c r="E138" s="76" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="F138" s="32"/>
       <c r="G138" s="32"/>
@@ -61400,7 +61397,7 @@
       <c r="C139" s="32"/>
       <c r="D139" s="32"/>
       <c r="E139" s="32" t="s">
-        <v>1314</v>
+        <v>1309</v>
       </c>
       <c r="F139" s="32"/>
       <c r="G139" s="32"/>
@@ -61412,7 +61409,7 @@
       <c r="C140" s="32"/>
       <c r="D140" s="32"/>
       <c r="E140" s="32" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="F140" s="32"/>
       <c r="G140" s="32"/>
@@ -61424,7 +61421,7 @@
       <c r="C141" s="32"/>
       <c r="D141" s="32"/>
       <c r="E141" s="32" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
       <c r="F141" s="32"/>
       <c r="G141" s="32"/>
@@ -61436,7 +61433,7 @@
       <c r="C142" s="32"/>
       <c r="D142" s="32"/>
       <c r="E142" s="32" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
       <c r="F142" s="32"/>
       <c r="G142" s="32"/>
@@ -61448,7 +61445,7 @@
       <c r="C143" s="32"/>
       <c r="D143" s="32"/>
       <c r="E143" s="32" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="F143" s="32"/>
       <c r="G143" s="32"/>
@@ -61460,7 +61457,7 @@
       <c r="C144" s="32"/>
       <c r="D144" s="32"/>
       <c r="E144" s="32" t="s">
-        <v>1319</v>
+        <v>1314</v>
       </c>
       <c r="F144" s="32"/>
       <c r="G144" s="32"/>
@@ -61472,7 +61469,7 @@
       <c r="C145" s="32"/>
       <c r="D145" s="32"/>
       <c r="E145" s="32" t="s">
-        <v>1320</v>
+        <v>1315</v>
       </c>
       <c r="F145" s="32"/>
       <c r="G145" s="32"/>
@@ -61484,7 +61481,7 @@
       <c r="C146" s="32"/>
       <c r="D146" s="32"/>
       <c r="E146" s="32" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="F146" s="32"/>
       <c r="G146" s="32"/>
@@ -61496,7 +61493,7 @@
       <c r="C147" s="32"/>
       <c r="D147" s="32"/>
       <c r="E147" s="32" t="s">
-        <v>1322</v>
+        <v>1317</v>
       </c>
       <c r="F147" s="32"/>
       <c r="G147" s="32"/>
@@ -61508,7 +61505,7 @@
       <c r="C148" s="32"/>
       <c r="D148" s="32"/>
       <c r="E148" s="32" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
       <c r="F148" s="32"/>
       <c r="G148" s="32"/>
@@ -61520,7 +61517,7 @@
       <c r="C149" s="32"/>
       <c r="D149" s="32"/>
       <c r="E149" s="32" t="s">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="F149" s="32"/>
       <c r="G149" s="32"/>
@@ -61532,7 +61529,7 @@
       <c r="C150" s="32"/>
       <c r="D150" s="32"/>
       <c r="E150" s="32" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="F150" s="32"/>
       <c r="G150" s="32"/>
@@ -61544,7 +61541,7 @@
       <c r="C151" s="32"/>
       <c r="D151" s="32"/>
       <c r="E151" s="32" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="F151" s="32"/>
       <c r="G151" s="32"/>
@@ -61556,7 +61553,7 @@
       <c r="C152" s="32"/>
       <c r="D152" s="32"/>
       <c r="E152" s="32" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="F152" s="32"/>
       <c r="G152" s="32"/>
@@ -61568,7 +61565,7 @@
       <c r="C153" s="32"/>
       <c r="D153" s="32"/>
       <c r="E153" s="32" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
       <c r="F153" s="32"/>
       <c r="G153" s="32"/>
@@ -61580,7 +61577,7 @@
       <c r="C154" s="32"/>
       <c r="D154" s="32"/>
       <c r="E154" s="32" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="F154" s="32"/>
       <c r="G154" s="32"/>
@@ -61592,7 +61589,7 @@
       <c r="C155" s="32"/>
       <c r="D155" s="32"/>
       <c r="E155" s="32" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
       <c r="F155" s="32"/>
       <c r="G155" s="32"/>
@@ -61604,7 +61601,7 @@
       <c r="C156" s="32"/>
       <c r="D156" s="32"/>
       <c r="E156" s="32" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="F156" s="32"/>
       <c r="G156" s="32"/>
@@ -61624,7 +61621,7 @@
         <v>563</v>
       </c>
       <c r="E157" s="32" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="F157" s="32"/>
       <c r="G157" s="32"/>
@@ -61636,7 +61633,7 @@
       <c r="C158" s="32"/>
       <c r="D158" s="32"/>
       <c r="E158" s="32" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="F158" s="32"/>
       <c r="G158" s="32"/>
@@ -61648,7 +61645,7 @@
       <c r="C159" s="32"/>
       <c r="D159" s="32"/>
       <c r="E159" s="32" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="F159" s="32"/>
       <c r="G159" s="32"/>
@@ -61660,7 +61657,7 @@
       <c r="C160" s="32"/>
       <c r="D160" s="32"/>
       <c r="E160" s="32" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="F160" s="32"/>
       <c r="G160" s="32"/>
@@ -61672,7 +61669,7 @@
       <c r="C161" s="32"/>
       <c r="D161" s="32"/>
       <c r="E161" s="32" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="F161" s="32"/>
       <c r="G161" s="32"/>
@@ -61684,7 +61681,7 @@
       <c r="C162" s="32"/>
       <c r="D162" s="32"/>
       <c r="E162" s="32" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="F162" s="32"/>
       <c r="G162" s="32"/>
@@ -61696,7 +61693,7 @@
       <c r="C163" s="32"/>
       <c r="D163" s="32"/>
       <c r="E163" s="32" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
       <c r="F163" s="32"/>
       <c r="G163" s="32"/>
@@ -61708,7 +61705,7 @@
       <c r="C164" s="32"/>
       <c r="D164" s="32"/>
       <c r="E164" s="32" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
       <c r="F164" s="32"/>
       <c r="G164" s="32"/>
@@ -61720,7 +61717,7 @@
       <c r="C165" s="32"/>
       <c r="D165" s="32"/>
       <c r="E165" s="32" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
       <c r="F165" s="32"/>
       <c r="G165" s="32"/>
@@ -61732,7 +61729,7 @@
       <c r="C166" s="32"/>
       <c r="D166" s="32"/>
       <c r="E166" s="32" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="F166" s="32"/>
       <c r="G166" s="32"/>
@@ -61744,7 +61741,7 @@
       <c r="C167" s="32"/>
       <c r="D167" s="32"/>
       <c r="E167" s="32" t="s">
-        <v>1342</v>
+        <v>1337</v>
       </c>
       <c r="F167" s="32"/>
       <c r="G167" s="32"/>
@@ -61756,7 +61753,7 @@
       <c r="C168" s="32"/>
       <c r="D168" s="32"/>
       <c r="E168" s="32" t="s">
-        <v>1343</v>
+        <v>1338</v>
       </c>
       <c r="F168" s="32"/>
       <c r="G168" s="32"/>
@@ -61768,7 +61765,7 @@
       <c r="C169" s="32"/>
       <c r="D169" s="32"/>
       <c r="E169" s="32" t="s">
-        <v>1344</v>
+        <v>1339</v>
       </c>
       <c r="F169" s="32"/>
       <c r="G169" s="32"/>
@@ -61780,7 +61777,7 @@
       <c r="C170" s="32"/>
       <c r="D170" s="32"/>
       <c r="E170" s="32" t="s">
-        <v>1345</v>
+        <v>1340</v>
       </c>
       <c r="F170" s="32"/>
       <c r="G170" s="32"/>
@@ -61792,7 +61789,7 @@
       <c r="C171" s="32"/>
       <c r="D171" s="32"/>
       <c r="E171" s="32" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
       <c r="F171" s="32"/>
       <c r="G171" s="32"/>
@@ -61804,7 +61801,7 @@
       <c r="C172" s="32"/>
       <c r="D172" s="32"/>
       <c r="E172" s="32" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="F172" s="32"/>
       <c r="G172" s="32"/>
@@ -61816,7 +61813,7 @@
       <c r="C173" s="32"/>
       <c r="D173" s="32"/>
       <c r="E173" s="32" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
       <c r="F173" s="32"/>
       <c r="G173" s="32"/>
@@ -61828,7 +61825,7 @@
       <c r="C174" s="32"/>
       <c r="D174" s="32"/>
       <c r="E174" s="32" t="s">
-        <v>1349</v>
+        <v>1344</v>
       </c>
       <c r="F174" s="32"/>
       <c r="G174" s="32"/>
@@ -61840,7 +61837,7 @@
       <c r="C175" s="32"/>
       <c r="D175" s="32"/>
       <c r="E175" s="32" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="F175" s="32"/>
       <c r="G175" s="32"/>
@@ -61852,7 +61849,7 @@
       <c r="C176" s="32"/>
       <c r="D176" s="32"/>
       <c r="E176" s="32" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="F176" s="32"/>
       <c r="G176" s="32"/>
@@ -61864,7 +61861,7 @@
       <c r="C177" s="32"/>
       <c r="D177" s="32"/>
       <c r="E177" s="32" t="s">
-        <v>1350</v>
+        <v>1345</v>
       </c>
       <c r="F177" s="32"/>
       <c r="G177" s="32"/>
@@ -61876,7 +61873,7 @@
       <c r="C178" s="32"/>
       <c r="D178" s="32"/>
       <c r="E178" s="32" t="s">
-        <v>1351</v>
+        <v>1346</v>
       </c>
       <c r="F178" s="32"/>
       <c r="G178" s="32"/>
@@ -61888,7 +61885,7 @@
       <c r="C179" s="32"/>
       <c r="D179" s="32"/>
       <c r="E179" s="32" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="F179" s="32"/>
       <c r="G179" s="32"/>
@@ -61900,7 +61897,7 @@
       <c r="C180" s="32"/>
       <c r="D180" s="32"/>
       <c r="E180" s="32" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
       <c r="F180" s="32"/>
       <c r="G180" s="32"/>
@@ -61912,7 +61909,7 @@
       <c r="C181" s="32"/>
       <c r="D181" s="32"/>
       <c r="E181" s="32" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
       <c r="F181" s="32"/>
       <c r="G181" s="32"/>
@@ -61924,7 +61921,7 @@
       <c r="C182" s="32"/>
       <c r="D182" s="32"/>
       <c r="E182" s="32" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="F182" s="32"/>
       <c r="G182" s="32"/>
@@ -61936,7 +61933,7 @@
       <c r="C183" s="32"/>
       <c r="D183" s="32"/>
       <c r="E183" s="32" t="s">
-        <v>1356</v>
+        <v>1351</v>
       </c>
       <c r="F183" s="32"/>
       <c r="G183" s="32"/>
@@ -61948,7 +61945,7 @@
       <c r="C184" s="32"/>
       <c r="D184" s="32"/>
       <c r="E184" s="32" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="F184" s="32"/>
       <c r="G184" s="32"/>
@@ -61960,7 +61957,7 @@
       <c r="C185" s="32"/>
       <c r="D185" s="32"/>
       <c r="E185" s="32" t="s">
-        <v>1358</v>
+        <v>1353</v>
       </c>
       <c r="F185" s="32"/>
       <c r="G185" s="32"/>
@@ -61972,7 +61969,7 @@
       <c r="C186" s="32"/>
       <c r="D186" s="32"/>
       <c r="E186" s="32" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
       <c r="F186" s="32"/>
       <c r="G186" s="32"/>
@@ -61984,7 +61981,7 @@
       <c r="C187" s="32"/>
       <c r="D187" s="32"/>
       <c r="E187" s="32" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
       <c r="F187" s="32"/>
       <c r="G187" s="32"/>
@@ -61996,7 +61993,7 @@
       <c r="C188" s="32"/>
       <c r="D188" s="32"/>
       <c r="E188" s="32" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
       <c r="F188" s="32"/>
       <c r="G188" s="32"/>
@@ -62016,7 +62013,7 @@
         <v>704</v>
       </c>
       <c r="E189" s="97" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="F189" s="32"/>
       <c r="G189" s="32"/>
@@ -62040,7 +62037,7 @@
       <c r="C191" s="32"/>
       <c r="D191" s="32"/>
       <c r="E191" s="32" t="s">
-        <v>1359</v>
+        <v>1354</v>
       </c>
       <c r="F191" s="32"/>
       <c r="G191" s="32"/>
@@ -62052,7 +62049,7 @@
       <c r="C192" s="32"/>
       <c r="D192" s="32"/>
       <c r="E192" s="32" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="F192" s="32"/>
       <c r="G192" s="32"/>
@@ -62072,7 +62069,7 @@
         <v>565</v>
       </c>
       <c r="E193" s="32" t="s">
-        <v>1361</v>
+        <v>1356</v>
       </c>
       <c r="F193" s="32"/>
       <c r="G193" s="32"/>
@@ -62084,7 +62081,7 @@
       <c r="C194" s="32"/>
       <c r="D194" s="32"/>
       <c r="E194" s="32" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="F194" s="32"/>
       <c r="G194" s="32"/>
@@ -62096,7 +62093,7 @@
       <c r="C195" s="32"/>
       <c r="D195" s="32"/>
       <c r="E195" s="32" t="s">
-        <v>1363</v>
+        <v>1358</v>
       </c>
       <c r="F195" s="32"/>
       <c r="G195" s="32"/>
@@ -62108,7 +62105,7 @@
       <c r="C196" s="32"/>
       <c r="D196" s="32"/>
       <c r="E196" s="32" t="s">
-        <v>1364</v>
+        <v>1359</v>
       </c>
       <c r="F196" s="32"/>
       <c r="G196" s="32"/>
@@ -62120,7 +62117,7 @@
       <c r="C197" s="32"/>
       <c r="D197" s="32"/>
       <c r="E197" s="32" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
       <c r="F197" s="32"/>
       <c r="G197" s="32"/>
@@ -62132,7 +62129,7 @@
       <c r="C198" s="32"/>
       <c r="D198" s="32"/>
       <c r="E198" s="32" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="F198" s="32"/>
       <c r="G198" s="32"/>
@@ -62144,7 +62141,7 @@
       <c r="C199" s="32"/>
       <c r="D199" s="32"/>
       <c r="E199" s="32" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="F199" s="32"/>
       <c r="G199" s="32"/>
@@ -62156,7 +62153,7 @@
       <c r="C200" s="32"/>
       <c r="D200" s="32"/>
       <c r="E200" s="32" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
       <c r="F200" s="32"/>
       <c r="G200" s="32"/>
@@ -62168,7 +62165,7 @@
       <c r="C201" s="32"/>
       <c r="D201" s="32"/>
       <c r="E201" s="32" t="s">
-        <v>1369</v>
+        <v>1364</v>
       </c>
       <c r="F201" s="32"/>
       <c r="G201" s="32"/>
@@ -62180,7 +62177,7 @@
       <c r="C202" s="32"/>
       <c r="D202" s="32"/>
       <c r="E202" s="32" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
       <c r="F202" s="32"/>
       <c r="G202" s="32"/>
@@ -62192,7 +62189,7 @@
       <c r="C203" s="32"/>
       <c r="D203" s="32"/>
       <c r="E203" s="32" t="s">
-        <v>1371</v>
+        <v>1366</v>
       </c>
       <c r="F203" s="32"/>
       <c r="G203" s="32"/>
@@ -62204,7 +62201,7 @@
       <c r="C204" s="32"/>
       <c r="D204" s="32"/>
       <c r="E204" s="32" t="s">
-        <v>1372</v>
+        <v>1367</v>
       </c>
       <c r="F204" s="32"/>
       <c r="G204" s="32"/>
@@ -62216,7 +62213,7 @@
       <c r="C205" s="32"/>
       <c r="D205" s="32"/>
       <c r="E205" s="32" t="s">
-        <v>1373</v>
+        <v>1368</v>
       </c>
       <c r="F205" s="32"/>
       <c r="G205" s="32"/>
@@ -62228,7 +62225,7 @@
       <c r="C206" s="32"/>
       <c r="D206" s="32"/>
       <c r="E206" s="32" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="F206" s="32"/>
       <c r="G206" s="32"/>
@@ -62240,7 +62237,7 @@
       <c r="C207" s="32"/>
       <c r="D207" s="32"/>
       <c r="E207" s="32" t="s">
-        <v>1375</v>
+        <v>1370</v>
       </c>
       <c r="F207" s="32"/>
       <c r="G207" s="32"/>
@@ -62252,7 +62249,7 @@
       <c r="C208" s="32"/>
       <c r="D208" s="32"/>
       <c r="E208" s="32" t="s">
-        <v>1376</v>
+        <v>1371</v>
       </c>
       <c r="F208" s="32"/>
       <c r="G208" s="32"/>
@@ -62264,7 +62261,7 @@
       <c r="C209" s="32"/>
       <c r="D209" s="32"/>
       <c r="E209" s="32" t="s">
-        <v>1377</v>
+        <v>1372</v>
       </c>
       <c r="F209" s="32"/>
       <c r="G209" s="32"/>
@@ -62276,7 +62273,7 @@
       <c r="C210" s="32"/>
       <c r="D210" s="32"/>
       <c r="E210" s="32" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="F210" s="32"/>
       <c r="G210" s="32"/>
@@ -62288,7 +62285,7 @@
       <c r="C211" s="32"/>
       <c r="D211" s="32"/>
       <c r="E211" s="32" t="s">
-        <v>1379</v>
+        <v>1374</v>
       </c>
       <c r="F211" s="32"/>
       <c r="G211" s="32"/>
@@ -62300,7 +62297,7 @@
       <c r="C212" s="32"/>
       <c r="D212" s="32"/>
       <c r="E212" s="32" t="s">
-        <v>1380</v>
+        <v>1375</v>
       </c>
       <c r="F212" s="32"/>
       <c r="G212" s="32"/>
@@ -62312,7 +62309,7 @@
       <c r="C213" s="32"/>
       <c r="D213" s="32"/>
       <c r="E213" s="32" t="s">
-        <v>1381</v>
+        <v>1376</v>
       </c>
       <c r="F213" s="32"/>
       <c r="G213" s="32"/>
@@ -62324,7 +62321,7 @@
       <c r="C214" s="32"/>
       <c r="D214" s="32"/>
       <c r="E214" s="32" t="s">
-        <v>1382</v>
+        <v>1377</v>
       </c>
       <c r="F214" s="32"/>
       <c r="G214" s="32"/>
@@ -62336,7 +62333,7 @@
       <c r="C215" s="32"/>
       <c r="D215" s="32"/>
       <c r="E215" s="32" t="s">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="F215" s="32"/>
       <c r="G215" s="32"/>
@@ -62348,7 +62345,7 @@
       <c r="C216" s="32"/>
       <c r="D216" s="32"/>
       <c r="E216" s="32" t="s">
-        <v>1384</v>
+        <v>1379</v>
       </c>
       <c r="F216" s="32"/>
       <c r="G216" s="32"/>
@@ -62360,7 +62357,7 @@
       <c r="C217" s="32"/>
       <c r="D217" s="32"/>
       <c r="E217" s="32" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="F217" s="32"/>
       <c r="G217" s="32"/>
@@ -62372,7 +62369,7 @@
       <c r="C218" s="32"/>
       <c r="D218" s="32"/>
       <c r="E218" s="32" t="s">
-        <v>1386</v>
+        <v>1381</v>
       </c>
       <c r="F218" s="32"/>
       <c r="G218" s="32"/>
@@ -62384,7 +62381,7 @@
       <c r="C219" s="32"/>
       <c r="D219" s="32"/>
       <c r="E219" s="32" t="s">
-        <v>1387</v>
+        <v>1382</v>
       </c>
       <c r="F219" s="32"/>
       <c r="G219" s="32"/>
@@ -62396,7 +62393,7 @@
       <c r="C220" s="32"/>
       <c r="D220" s="32"/>
       <c r="E220" s="32" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F220" s="32"/>
       <c r="G220" s="32"/>
@@ -62408,7 +62405,7 @@
       <c r="C221" s="32"/>
       <c r="D221" s="32"/>
       <c r="E221" s="32" t="s">
-        <v>1389</v>
+        <v>1384</v>
       </c>
       <c r="F221" s="32"/>
       <c r="G221" s="32"/>
@@ -62420,7 +62417,7 @@
       <c r="C222" s="32"/>
       <c r="D222" s="32"/>
       <c r="E222" s="32" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F222" s="32"/>
       <c r="G222" s="32"/>
@@ -62432,7 +62429,7 @@
       <c r="C223" s="32"/>
       <c r="D223" s="32"/>
       <c r="E223" s="32" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="F223" s="32"/>
       <c r="G223" s="32"/>
@@ -62444,7 +62441,7 @@
       <c r="C224" s="32"/>
       <c r="D224" s="32"/>
       <c r="E224" s="32" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="F224" s="32"/>
       <c r="G224" s="32"/>
@@ -62456,7 +62453,7 @@
       <c r="C225" s="32"/>
       <c r="D225" s="32"/>
       <c r="E225" s="32" t="s">
-        <v>1393</v>
+        <v>1388</v>
       </c>
       <c r="F225" s="32"/>
       <c r="G225" s="32"/>
@@ -62468,7 +62465,7 @@
       <c r="C226" s="32"/>
       <c r="D226" s="32"/>
       <c r="E226" s="32" t="s">
-        <v>1394</v>
+        <v>1389</v>
       </c>
       <c r="F226" s="32"/>
       <c r="G226" s="32"/>
@@ -62480,7 +62477,7 @@
       <c r="C227" s="32"/>
       <c r="D227" s="32"/>
       <c r="E227" s="32" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="F227" s="32"/>
       <c r="G227" s="32"/>
@@ -62492,7 +62489,7 @@
       <c r="C228" s="32"/>
       <c r="D228" s="32"/>
       <c r="E228" s="32" t="s">
-        <v>1396</v>
+        <v>1391</v>
       </c>
       <c r="F228" s="32"/>
       <c r="G228" s="32"/>
@@ -62504,7 +62501,7 @@
       <c r="C229" s="32"/>
       <c r="D229" s="32"/>
       <c r="E229" s="32" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="F229" s="32"/>
       <c r="G229" s="32"/>
@@ -62516,7 +62513,7 @@
       <c r="C230" s="32"/>
       <c r="D230" s="32"/>
       <c r="E230" s="32" t="s">
-        <v>1398</v>
+        <v>1393</v>
       </c>
       <c r="F230" s="32"/>
       <c r="G230" s="32"/>
@@ -62528,7 +62525,7 @@
       <c r="C231" s="32"/>
       <c r="D231" s="32"/>
       <c r="E231" s="32" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="F231" s="32"/>
       <c r="G231" s="32"/>
@@ -62540,7 +62537,7 @@
       <c r="C232" s="32"/>
       <c r="D232" s="32"/>
       <c r="E232" s="32" t="s">
-        <v>1399</v>
+        <v>1394</v>
       </c>
       <c r="F232" s="32"/>
       <c r="G232" s="32"/>
@@ -62552,7 +62549,7 @@
       <c r="C233" s="32"/>
       <c r="D233" s="32"/>
       <c r="E233" s="32" t="s">
-        <v>1400</v>
+        <v>1395</v>
       </c>
       <c r="F233" s="32"/>
       <c r="G233" s="32"/>
@@ -62564,7 +62561,7 @@
       <c r="C234" s="32"/>
       <c r="D234" s="32"/>
       <c r="E234" s="32" t="s">
-        <v>1401</v>
+        <v>1396</v>
       </c>
       <c r="F234" s="32"/>
       <c r="G234" s="32"/>
@@ -62576,7 +62573,7 @@
       <c r="C235" s="32"/>
       <c r="D235" s="32"/>
       <c r="E235" s="32" t="s">
-        <v>1402</v>
+        <v>1397</v>
       </c>
       <c r="F235" s="32"/>
       <c r="G235" s="32"/>
@@ -62588,7 +62585,7 @@
       <c r="C236" s="32"/>
       <c r="D236" s="32"/>
       <c r="E236" s="32" t="s">
-        <v>1403</v>
+        <v>1398</v>
       </c>
       <c r="F236" s="32"/>
       <c r="G236" s="32"/>
@@ -62600,7 +62597,7 @@
       <c r="C237" s="32"/>
       <c r="D237" s="32"/>
       <c r="E237" s="32" t="s">
-        <v>1404</v>
+        <v>1399</v>
       </c>
       <c r="F237" s="32"/>
       <c r="G237" s="32"/>
@@ -62612,7 +62609,7 @@
       <c r="C238" s="32"/>
       <c r="D238" s="32"/>
       <c r="E238" s="32" t="s">
-        <v>1405</v>
+        <v>1400</v>
       </c>
       <c r="F238" s="32"/>
       <c r="G238" s="32"/>
@@ -62624,7 +62621,7 @@
       <c r="C239" s="32"/>
       <c r="D239" s="32"/>
       <c r="E239" s="32" t="s">
-        <v>1406</v>
+        <v>1401</v>
       </c>
       <c r="F239" s="32"/>
       <c r="G239" s="32"/>
@@ -62636,7 +62633,7 @@
       <c r="C240" s="32"/>
       <c r="D240" s="32"/>
       <c r="E240" s="32" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="F240" s="32"/>
       <c r="G240" s="32"/>
@@ -62644,7 +62641,7 @@
     </row>
     <row r="241" spans="1:9" s="33" customFormat="1" ht="16">
       <c r="E241" s="32" t="s">
-        <v>1408</v>
+        <v>1403</v>
       </c>
       <c r="I241" s="75"/>
     </row>
@@ -62654,7 +62651,7 @@
       <c r="C242" s="33"/>
       <c r="D242" s="33"/>
       <c r="E242" s="32" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
       <c r="F242" s="33"/>
       <c r="G242" s="33"/>
@@ -62666,7 +62663,7 @@
       <c r="C243" s="33"/>
       <c r="D243" s="33"/>
       <c r="E243" s="32" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
       <c r="F243" s="33"/>
       <c r="G243" s="33"/>
@@ -62678,7 +62675,7 @@
       <c r="C244" s="33"/>
       <c r="D244" s="33"/>
       <c r="E244" s="32" t="s">
-        <v>1598</v>
+        <v>1593</v>
       </c>
       <c r="F244" s="33"/>
       <c r="G244" s="33"/>
@@ -62698,7 +62695,7 @@
         <v>782</v>
       </c>
       <c r="E245" s="32" t="s">
-        <v>1409</v>
+        <v>1404</v>
       </c>
       <c r="F245" s="33"/>
       <c r="G245" s="33"/>
@@ -62710,7 +62707,7 @@
       <c r="C246" s="33"/>
       <c r="D246" s="33"/>
       <c r="E246" s="32" t="s">
-        <v>1410</v>
+        <v>1405</v>
       </c>
       <c r="F246" s="33"/>
       <c r="G246" s="33"/>
@@ -62722,7 +62719,7 @@
       <c r="C247" s="33"/>
       <c r="D247" s="33"/>
       <c r="E247" s="32" t="s">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="F247" s="33"/>
       <c r="G247" s="33"/>
@@ -62734,7 +62731,7 @@
       <c r="C248" s="33"/>
       <c r="D248" s="33"/>
       <c r="E248" s="32" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="F248" s="33"/>
       <c r="G248" s="33"/>
@@ -62746,7 +62743,7 @@
       <c r="C249" s="33"/>
       <c r="D249" s="33"/>
       <c r="E249" s="32" t="s">
-        <v>1413</v>
+        <v>1408</v>
       </c>
       <c r="F249" s="33"/>
       <c r="G249" s="33"/>
@@ -62758,7 +62755,7 @@
       <c r="C250" s="33"/>
       <c r="D250" s="33"/>
       <c r="E250" s="32" t="s">
-        <v>1414</v>
+        <v>1409</v>
       </c>
       <c r="F250" s="33"/>
       <c r="G250" s="33"/>
@@ -62770,7 +62767,7 @@
       <c r="C251" s="33"/>
       <c r="D251" s="33"/>
       <c r="E251" s="32" t="s">
-        <v>1415</v>
+        <v>1410</v>
       </c>
       <c r="F251" s="33"/>
       <c r="G251" s="33"/>
@@ -62782,7 +62779,7 @@
       <c r="C252" s="33"/>
       <c r="D252" s="33"/>
       <c r="E252" s="32" t="s">
-        <v>1416</v>
+        <v>1411</v>
       </c>
       <c r="F252" s="33"/>
       <c r="G252" s="33"/>
@@ -62794,7 +62791,7 @@
       <c r="C253" s="33"/>
       <c r="D253" s="33"/>
       <c r="E253" s="32" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="F253" s="33"/>
       <c r="G253" s="33"/>
@@ -62806,7 +62803,7 @@
       <c r="C254" s="33"/>
       <c r="D254" s="33"/>
       <c r="E254" s="32" t="s">
-        <v>1418</v>
+        <v>1413</v>
       </c>
       <c r="F254" s="33"/>
       <c r="G254" s="33"/>
@@ -62818,7 +62815,7 @@
       <c r="C255" s="33"/>
       <c r="D255" s="33"/>
       <c r="E255" s="32" t="s">
-        <v>1419</v>
+        <v>1414</v>
       </c>
       <c r="F255" s="33"/>
       <c r="G255" s="33"/>
@@ -62830,7 +62827,7 @@
       <c r="C256" s="33"/>
       <c r="D256" s="33"/>
       <c r="E256" s="32" t="s">
-        <v>1420</v>
+        <v>1415</v>
       </c>
       <c r="F256" s="33"/>
       <c r="G256" s="33"/>
@@ -62842,7 +62839,7 @@
       <c r="C257" s="33"/>
       <c r="D257" s="33"/>
       <c r="E257" s="32" t="s">
-        <v>1421</v>
+        <v>1416</v>
       </c>
       <c r="F257" s="33"/>
       <c r="G257" s="33"/>
@@ -62854,7 +62851,7 @@
       <c r="C258" s="33"/>
       <c r="D258" s="33"/>
       <c r="E258" s="32" t="s">
-        <v>1422</v>
+        <v>1417</v>
       </c>
       <c r="F258" s="33"/>
       <c r="G258" s="33"/>
@@ -62866,7 +62863,7 @@
       <c r="C259" s="33"/>
       <c r="D259" s="33"/>
       <c r="E259" s="32" t="s">
-        <v>1423</v>
+        <v>1418</v>
       </c>
       <c r="F259" s="33"/>
       <c r="G259" s="33"/>
@@ -62878,7 +62875,7 @@
       <c r="C260" s="33"/>
       <c r="D260" s="33"/>
       <c r="E260" s="32" t="s">
-        <v>1424</v>
+        <v>1419</v>
       </c>
       <c r="F260" s="33"/>
       <c r="G260" s="33"/>
@@ -62890,7 +62887,7 @@
       <c r="C261" s="33"/>
       <c r="D261" s="33"/>
       <c r="E261" s="32" t="s">
-        <v>1425</v>
+        <v>1420</v>
       </c>
       <c r="F261" s="33"/>
       <c r="G261" s="33"/>
@@ -62902,7 +62899,7 @@
       <c r="C262" s="33"/>
       <c r="D262" s="33"/>
       <c r="E262" s="32" t="s">
-        <v>1426</v>
+        <v>1421</v>
       </c>
       <c r="F262" s="33"/>
       <c r="G262" s="33"/>
@@ -62914,7 +62911,7 @@
       <c r="C263" s="33"/>
       <c r="D263" s="33"/>
       <c r="E263" s="32" t="s">
-        <v>1427</v>
+        <v>1422</v>
       </c>
       <c r="F263" s="33"/>
       <c r="G263" s="33"/>
@@ -62926,7 +62923,7 @@
       <c r="C264" s="33"/>
       <c r="D264" s="33"/>
       <c r="E264" s="32" t="s">
-        <v>1428</v>
+        <v>1423</v>
       </c>
       <c r="F264" s="33"/>
       <c r="G264" s="33"/>
@@ -62938,7 +62935,7 @@
       <c r="C265" s="33"/>
       <c r="D265" s="33"/>
       <c r="E265" s="32" t="s">
-        <v>1429</v>
+        <v>1424</v>
       </c>
       <c r="F265" s="33"/>
       <c r="G265" s="33"/>
@@ -62950,7 +62947,7 @@
       <c r="C266" s="33"/>
       <c r="D266" s="33"/>
       <c r="E266" s="32" t="s">
-        <v>1430</v>
+        <v>1425</v>
       </c>
       <c r="F266" s="33"/>
       <c r="G266" s="33"/>
@@ -62962,7 +62959,7 @@
       <c r="C267" s="33"/>
       <c r="D267" s="33"/>
       <c r="E267" s="32" t="s">
-        <v>1431</v>
+        <v>1426</v>
       </c>
       <c r="F267" s="33"/>
       <c r="G267" s="33"/>
@@ -62974,7 +62971,7 @@
       <c r="C268" s="33"/>
       <c r="D268" s="33"/>
       <c r="E268" s="32" t="s">
-        <v>1432</v>
+        <v>1427</v>
       </c>
       <c r="F268" s="33"/>
       <c r="G268" s="33"/>
@@ -62986,7 +62983,7 @@
       <c r="C269" s="33"/>
       <c r="D269" s="33"/>
       <c r="E269" s="32" t="s">
-        <v>1433</v>
+        <v>1428</v>
       </c>
       <c r="F269" s="33"/>
       <c r="G269" s="33"/>
@@ -62998,7 +62995,7 @@
       <c r="C270" s="33"/>
       <c r="D270" s="33"/>
       <c r="E270" s="32" t="s">
-        <v>1434</v>
+        <v>1429</v>
       </c>
       <c r="F270" s="33"/>
       <c r="G270" s="33"/>
@@ -63010,7 +63007,7 @@
       <c r="C271" s="33"/>
       <c r="D271" s="33"/>
       <c r="E271" s="32" t="s">
-        <v>1435</v>
+        <v>1430</v>
       </c>
       <c r="F271" s="33"/>
       <c r="G271" s="33"/>
@@ -63022,7 +63019,7 @@
       <c r="C272" s="33"/>
       <c r="D272" s="33"/>
       <c r="E272" s="32" t="s">
-        <v>1436</v>
+        <v>1431</v>
       </c>
       <c r="F272" s="33"/>
       <c r="G272" s="33"/>
@@ -63033,16 +63030,16 @@
         <v>5</v>
       </c>
       <c r="B273" s="32" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="C273" s="33" t="s">
         <v>397</v>
       </c>
       <c r="D273" s="32" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="E273" s="32" t="s">
-        <v>1437</v>
+        <v>1432</v>
       </c>
       <c r="F273" s="33"/>
       <c r="G273" s="33"/>
@@ -63054,7 +63051,7 @@
       <c r="C274" s="33"/>
       <c r="D274" s="32"/>
       <c r="E274" s="32" t="s">
-        <v>1438</v>
+        <v>1433</v>
       </c>
       <c r="F274" s="33"/>
       <c r="G274" s="33"/>
@@ -63066,7 +63063,7 @@
       <c r="C275" s="33"/>
       <c r="D275" s="32"/>
       <c r="E275" s="32" t="s">
-        <v>1439</v>
+        <v>1434</v>
       </c>
       <c r="F275" s="33"/>
       <c r="G275" s="33"/>
@@ -63078,7 +63075,7 @@
       <c r="C276" s="33"/>
       <c r="D276" s="32"/>
       <c r="E276" s="32" t="s">
-        <v>1440</v>
+        <v>1435</v>
       </c>
       <c r="F276" s="33"/>
       <c r="G276" s="33"/>
@@ -63110,7 +63107,7 @@
         <v>784</v>
       </c>
       <c r="E278" s="32" t="s">
-        <v>1441</v>
+        <v>1436</v>
       </c>
       <c r="F278" s="32"/>
       <c r="G278" s="32"/>
@@ -63122,7 +63119,7 @@
       <c r="C279" s="32"/>
       <c r="D279" s="32"/>
       <c r="E279" s="32" t="s">
-        <v>1442</v>
+        <v>1437</v>
       </c>
       <c r="F279" s="32"/>
       <c r="G279" s="32"/>
@@ -63134,7 +63131,7 @@
       <c r="C280" s="32"/>
       <c r="D280" s="32"/>
       <c r="E280" s="32" t="s">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="F280" s="32"/>
       <c r="G280" s="32"/>
@@ -63154,7 +63151,7 @@
         <v>786</v>
       </c>
       <c r="E281" s="32" t="s">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="F281" s="32"/>
       <c r="G281" s="32"/>
@@ -63166,7 +63163,7 @@
       <c r="C282" s="32"/>
       <c r="D282" s="32"/>
       <c r="E282" s="32" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
       <c r="F282" s="32"/>
       <c r="G282" s="32"/>
@@ -63178,7 +63175,7 @@
       <c r="C283" s="32"/>
       <c r="D283" s="32"/>
       <c r="E283" s="32" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="F283" s="32"/>
       <c r="G283" s="32"/>
@@ -63320,7 +63317,7 @@
       <c r="E1" s="141"/>
       <c r="F1" s="142"/>
       <c r="G1" s="143" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="H1" s="144"/>
       <c r="I1" s="145"/>
@@ -63384,7 +63381,7 @@
         <v>298</v>
       </c>
       <c r="F4" s="53" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="G4" s="53" t="b">
         <v>0</v>
@@ -63413,7 +63410,7 @@
         <v>300</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="G5" s="53" t="b">
         <v>0</v>
@@ -63434,13 +63431,13 @@
         <v>301</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="E6" s="53" t="s">
         <v>302</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="G6" s="53" t="b">
         <v>0</v>
@@ -63465,7 +63462,7 @@
         <v>303</v>
       </c>
       <c r="F7" s="53" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="G7" s="53" t="b">
         <v>0</v>
@@ -63490,7 +63487,7 @@
         <v>304</v>
       </c>
       <c r="F8" s="53" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="G8" s="53" t="b">
         <v>0</v>
@@ -63509,7 +63506,7 @@
         <v>305</v>
       </c>
       <c r="D9" s="53" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="E9" s="53" t="s">
         <v>306</v>
@@ -63536,13 +63533,13 @@
         <v>305</v>
       </c>
       <c r="D10" s="53" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="E10" s="53" t="s">
         <v>308</v>
       </c>
       <c r="F10" s="53" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="G10" s="53" t="b">
         <v>0</v>
@@ -63561,13 +63558,13 @@
         <v>305</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="E11" s="53" t="s">
         <v>309</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="G11" s="53" t="b">
         <v>0</v>
@@ -63586,13 +63583,13 @@
         <v>305</v>
       </c>
       <c r="D12" s="53" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="E12" s="53" t="s">
         <v>310</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
       <c r="G12" s="53" t="b">
         <v>0</v>
@@ -63689,7 +63686,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="40" customFormat="1" ht="92" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -63707,7 +63704,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="105" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>421</v>
@@ -63718,13 +63715,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="C3" s="63" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="E3" s="33"/>
     </row>
@@ -63779,7 +63776,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="40" customFormat="1" ht="207" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1134</v>
+        <v>1129</v>
       </c>
       <c r="B1" s="138"/>
       <c r="C1" s="138"/>
@@ -63806,34 +63803,34 @@
         <v>2</v>
       </c>
       <c r="D2" s="105" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E2" s="106" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F2" s="106" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G2" s="106" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H2" s="107" t="s">
+        <v>1030</v>
+      </c>
+      <c r="I2" s="108" t="s">
         <v>1031</v>
       </c>
-      <c r="E2" s="106" t="s">
+      <c r="J2" s="108" t="s">
         <v>1032</v>
       </c>
-      <c r="F2" s="106" t="s">
+      <c r="K2" s="106" t="s">
         <v>1033</v>
       </c>
-      <c r="G2" s="106" t="s">
+      <c r="L2" s="106" t="s">
         <v>1034</v>
       </c>
-      <c r="H2" s="107" t="s">
+      <c r="M2" s="106" t="s">
         <v>1035</v>
-      </c>
-      <c r="I2" s="108" t="s">
-        <v>1036</v>
-      </c>
-      <c r="J2" s="108" t="s">
-        <v>1037</v>
-      </c>
-      <c r="K2" s="106" t="s">
-        <v>1038</v>
-      </c>
-      <c r="L2" s="106" t="s">
-        <v>1039</v>
-      </c>
-      <c r="M2" s="106" t="s">
-        <v>1040</v>
       </c>
       <c r="N2" s="109" t="s">
         <v>421</v>
@@ -63844,29 +63841,29 @@
         <v>5</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="E3" s="32" t="s">
         <v>397</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="G3" s="32">
         <v>10</v>
       </c>
       <c r="H3" s="110"/>
       <c r="I3" s="111" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="J3" s="111" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="K3" s="32"/>
       <c r="L3" s="32"/>
@@ -63878,19 +63875,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="G4" s="32">
         <v>100</v>
@@ -63901,7 +63898,7 @@
       <c r="I4" s="111"/>
       <c r="J4" s="111"/>
       <c r="K4" s="32" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="L4" s="112"/>
       <c r="M4" s="32"/>
@@ -63919,13 +63916,13 @@
       <c r="I5" s="111"/>
       <c r="J5" s="111"/>
       <c r="K5" s="32" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="L5" s="33" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="M5" s="32" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="N5" s="113"/>
     </row>
@@ -63941,10 +63938,10 @@
       <c r="I6" s="111"/>
       <c r="J6" s="111"/>
       <c r="K6" s="32" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="M6" s="32"/>
       <c r="N6" s="113"/>

--- a/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7EAC7C-E5AB-7A40-8015-A8DE80563C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB6CFEA-6122-C244-828C-605A7E145C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="27080" windowHeight="17400" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -883,7 +883,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2847" uniqueCount="1622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2848" uniqueCount="1622">
   <si>
     <t>Region</t>
   </si>
@@ -13464,51 +13464,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CD3 Automation Toolkit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Release - v2025.2.1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Updated Instances sheet, Exa-Infra sheet</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Enter Network Details as : </t>
     </r>
     <r>
@@ -13812,6 +13767,51 @@
   </si>
   <si>
     <t>cardiff</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CD3 Automation Toolkit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Release - v2025.2.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Updated Instances sheet, Exa-Infra sheet, LB-Listener sheet</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -20703,7 +20703,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1">
       <c r="A2" s="81" t="s">
-        <v>1597</v>
+        <v>1621</v>
       </c>
     </row>
   </sheetData>
@@ -24701,7 +24701,7 @@
       <c r="G1" s="152"/>
       <c r="H1" s="153"/>
       <c r="I1" s="136" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="J1" s="138"/>
       <c r="K1" s="138"/>
@@ -24776,52 +24776,52 @@
         <v>743</v>
       </c>
       <c r="O2" s="27" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="P2" s="27" t="s">
         <v>997</v>
       </c>
       <c r="Q2" s="27" t="s">
+        <v>1599</v>
+      </c>
+      <c r="R2" s="27" t="s">
         <v>1600</v>
       </c>
-      <c r="R2" s="27" t="s">
+      <c r="S2" s="27" t="s">
         <v>1601</v>
       </c>
-      <c r="S2" s="27" t="s">
+      <c r="T2" s="27" t="s">
         <v>1602</v>
       </c>
-      <c r="T2" s="27" t="s">
+      <c r="U2" s="27" t="s">
         <v>1603</v>
       </c>
-      <c r="U2" s="27" t="s">
+      <c r="V2" s="27" t="s">
         <v>1604</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="W2" s="27" t="s">
         <v>1605</v>
       </c>
-      <c r="W2" s="27" t="s">
+      <c r="X2" s="27" t="s">
         <v>1606</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="Y2" s="27" t="s">
         <v>1607</v>
       </c>
-      <c r="Y2" s="27" t="s">
+      <c r="Z2" s="27" t="s">
         <v>1608</v>
       </c>
-      <c r="Z2" s="27" t="s">
+      <c r="AA2" s="27" t="s">
         <v>1609</v>
       </c>
-      <c r="AA2" s="27" t="s">
+      <c r="AB2" s="27" t="s">
         <v>1610</v>
       </c>
-      <c r="AB2" s="27" t="s">
+      <c r="AC2" s="27" t="s">
+        <v>1616</v>
+      </c>
+      <c r="AD2" s="27" t="s">
         <v>1611</v>
-      </c>
-      <c r="AC2" s="27" t="s">
-        <v>1617</v>
-      </c>
-      <c r="AD2" s="27" t="s">
-        <v>1612</v>
       </c>
       <c r="AE2" s="26" t="s">
         <v>94</v>
@@ -24862,19 +24862,19 @@
         <v>349</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="G3" s="33" t="b">
         <v>0</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="I3" s="33" t="s">
         <v>431</v>
       </c>
       <c r="J3" s="134" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="K3" s="33">
         <v>8</v>
@@ -25033,7 +25033,7 @@
         <v>349</v>
       </c>
       <c r="F6" s="54" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="G6" s="53" t="b">
         <v>0</v>
@@ -27184,21 +27184,22 @@
   <sheetPr>
     <tabColor theme="2" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="9.5" customWidth="1"/>
     <col min="3" max="3" width="10.5" customWidth="1"/>
     <col min="4" max="4" width="17.83203125" customWidth="1"/>
-    <col min="5" max="5" width="9.83203125" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" customWidth="1"/>
-    <col min="8" max="9" width="12.5" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="13" max="13" width="10.1640625" customWidth="1"/>
-    <col min="17" max="17" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="9.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" customWidth="1"/>
+    <col min="9" max="10" width="12.5" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="14" max="14" width="10.1640625" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="124" customHeight="1">
+    <row r="1" spans="1:18" ht="124" customHeight="1">
       <c r="A1" s="136" t="s">
         <v>1143</v>
       </c>
@@ -27218,8 +27219,9 @@
       <c r="O1" s="136"/>
       <c r="P1" s="136"/>
       <c r="Q1" s="136"/>
-    </row>
-    <row r="2" spans="1:17" ht="46.5" customHeight="1">
+      <c r="R1" s="136"/>
+    </row>
+    <row r="2" spans="1:18" ht="46.5" customHeight="1">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
@@ -27232,47 +27234,50 @@
       <c r="D2" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="27" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="I2" s="27" t="s">
         <v>741</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="J2" s="27" t="s">
         <v>748</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="K2" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="L2" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="M2" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="N2" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="O2" s="27" t="s">
         <v>400</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="P2" s="27" t="s">
         <v>399</v>
       </c>
-      <c r="P2" s="27" t="s">
+      <c r="Q2" s="27" t="s">
         <v>439</v>
       </c>
-      <c r="Q2" s="27" t="s">
+      <c r="R2" s="27" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3" s="33" t="s">
         <v>4</v>
       </c>
@@ -27292,8 +27297,9 @@
       <c r="O3" s="33"/>
       <c r="P3" s="33"/>
       <c r="Q3" s="33"/>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" s="33"/>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="53" t="s">
         <v>5</v>
       </c>
@@ -27306,66 +27312,68 @@
       <c r="D4" s="53" t="s">
         <v>245</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="53"/>
+      <c r="F4" s="53" t="s">
         <v>230</v>
       </c>
-      <c r="F4" s="53" t="s">
+      <c r="G4" s="53" t="s">
         <v>190</v>
       </c>
-      <c r="G4" s="53" t="s">
+      <c r="H4" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="53"/>
       <c r="I4" s="53"/>
-      <c r="J4" s="53" t="s">
+      <c r="J4" s="53"/>
+      <c r="K4" s="53" t="s">
         <v>365</v>
       </c>
-      <c r="K4" s="53"/>
       <c r="L4" s="53"/>
       <c r="M4" s="53"/>
-      <c r="N4" s="53" t="s">
+      <c r="N4" s="53"/>
+      <c r="O4" s="53" t="s">
         <v>415</v>
       </c>
-      <c r="O4" s="88" t="s">
+      <c r="P4" s="88" t="s">
         <v>416</v>
       </c>
-      <c r="P4" s="53">
+      <c r="Q4" s="53">
         <v>2</v>
       </c>
-      <c r="Q4" s="53" t="b">
+      <c r="R4" s="53" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5" s="53"/>
       <c r="B5" s="53"/>
       <c r="C5" s="53" t="s">
         <v>171</v>
       </c>
       <c r="D5" s="53"/>
-      <c r="E5" s="53" t="s">
+      <c r="E5" s="53"/>
+      <c r="F5" s="53" t="s">
         <v>233</v>
       </c>
-      <c r="F5" s="53" t="s">
+      <c r="G5" s="53" t="s">
         <v>226</v>
       </c>
-      <c r="G5" s="53" t="s">
+      <c r="H5" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="53"/>
       <c r="I5" s="53"/>
-      <c r="J5" s="53" t="s">
+      <c r="J5" s="53"/>
+      <c r="K5" s="53" t="s">
         <v>425</v>
       </c>
-      <c r="K5" s="53"/>
       <c r="L5" s="53"/>
       <c r="M5" s="53"/>
       <c r="N5" s="53"/>
       <c r="O5" s="53"/>
       <c r="P5" s="53"/>
       <c r="Q5" s="53"/>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" s="53"/>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="53" t="s">
         <v>5</v>
       </c>
@@ -27378,39 +27386,40 @@
       <c r="D6" s="53" t="s">
         <v>246</v>
       </c>
-      <c r="E6" s="53" t="s">
+      <c r="E6" s="53"/>
+      <c r="F6" s="53" t="s">
         <v>236</v>
       </c>
-      <c r="F6" s="53" t="s">
+      <c r="G6" s="53" t="s">
         <v>247</v>
       </c>
-      <c r="G6" s="53" t="s">
+      <c r="H6" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="53" t="s">
+      <c r="I6" s="53" t="s">
         <v>152</v>
       </c>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53" t="s">
+      <c r="J6" s="53"/>
+      <c r="K6" s="53" t="s">
         <v>248</v>
       </c>
-      <c r="K6" s="53" t="s">
+      <c r="L6" s="53" t="s">
         <v>167</v>
       </c>
-      <c r="L6" s="53">
+      <c r="M6" s="53">
         <v>80</v>
       </c>
-      <c r="M6" s="53">
+      <c r="N6" s="53">
         <v>5</v>
       </c>
-      <c r="N6" s="53"/>
       <c r="O6" s="53"/>
       <c r="P6" s="53"/>
       <c r="Q6" s="53"/>
+      <c r="R6" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" prompt="Select an OCI region" sqref="A1:A2 B1:XFD1048576" xr:uid="{7533ABC3-6794-6D44-B74C-A996D26E3DC2}"/>
@@ -56061,7 +56070,7 @@
       <c r="I49" s="33"/>
       <c r="J49" s="33"/>
       <c r="L49" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="P49" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P49" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A49,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A49,4,4,1,"DHCP")))</f>
@@ -56107,7 +56116,7 @@
       <c r="I50" s="33"/>
       <c r="J50" s="33"/>
       <c r="L50" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="P50" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P50" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A50,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A50,4,4,1,"DHCP")))</f>
@@ -56182,7 +56191,7 @@
       <c r="I53" s="33"/>
       <c r="J53" s="33"/>
       <c r="L53" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="AU53" s="101" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -56202,7 +56211,7 @@
       <c r="I54" s="33"/>
       <c r="J54" s="33"/>
       <c r="L54" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="AU54" s="101" t="str">
         <f t="shared" ca="1" si="1"/>

--- a/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-SingleVCN-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB6CFEA-6122-C244-828C-605A7E145C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B34F0F-4382-4845-8E2F-F2B925C19A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="27080" windowHeight="17400" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19820" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
@@ -883,7 +883,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2848" uniqueCount="1622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2853" uniqueCount="1626">
   <si>
     <t>Region</t>
   </si>
@@ -3844,9 +3844,6 @@
     <t>Storage Servers</t>
   </si>
   <si>
-    <t>Exadata.X8M</t>
-  </si>
-  <si>
     <t>VM Cluster Display Name</t>
   </si>
   <si>
@@ -13812,6 +13809,21 @@
       <t xml:space="preserve">
 Updated Instances sheet, Exa-Infra sheet, LB-Listener sheet</t>
     </r>
+  </si>
+  <si>
+    <t>Exadata.X11M</t>
+  </si>
+  <si>
+    <t>Database Server Type</t>
+  </si>
+  <si>
+    <t>Storage Server Type</t>
+  </si>
+  <si>
+    <t>X11M</t>
+  </si>
+  <si>
+    <t>X11M-HC</t>
   </si>
 </sst>
 </file>
@@ -20703,7 +20715,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1">
       <c r="A2" s="81" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
   </sheetData>
@@ -20739,7 +20751,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="250" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="B1" s="141"/>
       <c r="C1" s="141"/>
@@ -20750,7 +20762,7 @@
       <c r="H1" s="141"/>
       <c r="I1" s="142"/>
       <c r="J1" s="140" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="K1" s="141"/>
       <c r="L1" s="141"/>
@@ -20769,16 +20781,16 @@
         <v>10</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="F2" s="16" t="s">
+        <v>1514</v>
+      </c>
+      <c r="G2" s="16" t="s">
         <v>1515</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>1516</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>12</v>
@@ -20813,7 +20825,7 @@
         <v>350</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D3" s="33" t="s">
         <v>20</v>
@@ -20822,7 +20834,7 @@
       <c r="F3" s="33"/>
       <c r="G3" s="33"/>
       <c r="H3" s="33" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="I3" s="33" t="s">
         <v>21</v>
@@ -20837,7 +20849,7 @@
         <v>23</v>
       </c>
       <c r="M3" s="33" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N3" s="33"/>
       <c r="O3" s="28"/>
@@ -20878,7 +20890,7 @@
       <c r="F5" s="53"/>
       <c r="G5" s="53"/>
       <c r="H5" s="53" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="I5" s="53" t="s">
         <v>23</v>
@@ -20890,13 +20902,13 @@
         <v>21</v>
       </c>
       <c r="L5" s="53" t="s">
+        <v>724</v>
+      </c>
+      <c r="M5" s="53" t="s">
         <v>725</v>
       </c>
-      <c r="M5" s="53" t="s">
+      <c r="N5" s="53" t="s">
         <v>726</v>
-      </c>
-      <c r="N5" s="53" t="s">
-        <v>727</v>
       </c>
       <c r="O5" s="54" t="s">
         <v>429</v>
@@ -20931,10 +20943,10 @@
         <v>21</v>
       </c>
       <c r="L6" s="53" t="s">
+        <v>727</v>
+      </c>
+      <c r="M6" s="53" t="s">
         <v>728</v>
-      </c>
-      <c r="M6" s="53" t="s">
-        <v>729</v>
       </c>
       <c r="N6" s="53"/>
       <c r="O6" s="53"/>
@@ -20968,10 +20980,10 @@
         <v>21</v>
       </c>
       <c r="L7" s="53" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="M7" s="53" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="N7" s="53"/>
       <c r="O7" s="53"/>
@@ -21033,7 +21045,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="222" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -21041,7 +21053,7 @@
       <c r="E1" s="136"/>
       <c r="F1" s="136"/>
       <c r="G1" s="146" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H1" s="146"/>
       <c r="I1" s="146"/>
@@ -21060,7 +21072,7 @@
         <v>603</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>604</v>
@@ -21083,17 +21095,17 @@
         <v>350</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E3" s="32"/>
       <c r="F3" s="32" t="s">
+        <v>730</v>
+      </c>
+      <c r="G3" s="32" t="s">
         <v>731</v>
-      </c>
-      <c r="G3" s="32" t="s">
-        <v>732</v>
       </c>
       <c r="H3" s="32" t="s">
         <v>610</v>
@@ -21121,16 +21133,16 @@
         <v>350</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D5" s="32" t="s">
+        <v>970</v>
+      </c>
+      <c r="E5" s="33" t="s">
         <v>971</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="F5" s="32" t="s">
         <v>972</v>
-      </c>
-      <c r="F5" s="32" t="s">
-        <v>973</v>
       </c>
       <c r="G5" s="33"/>
       <c r="H5" s="33"/>
@@ -21144,16 +21156,16 @@
         <v>350</v>
       </c>
       <c r="C6" s="32" t="s">
+        <v>973</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>977</v>
+      </c>
+      <c r="E6" s="33" t="s">
         <v>974</v>
       </c>
-      <c r="D6" s="32" t="s">
-        <v>978</v>
-      </c>
-      <c r="E6" s="33" t="s">
+      <c r="F6" s="32" t="s">
         <v>975</v>
-      </c>
-      <c r="F6" s="32" t="s">
-        <v>976</v>
       </c>
       <c r="G6" s="33"/>
       <c r="H6" s="33"/>
@@ -21215,7 +21227,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="40" customFormat="1" ht="92.25" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B1" s="145"/>
     </row>
@@ -21287,7 +21299,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="103.75" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -21331,7 +21343,7 @@
         <v>350</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D3" s="33" t="s">
         <v>35</v>
@@ -21340,7 +21352,7 @@
         <v>38</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G3" s="33"/>
       <c r="H3" s="33"/>
@@ -21496,7 +21508,7 @@
   <sheetData>
     <row r="1" spans="1:21" ht="203.25" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B1" s="141"/>
       <c r="C1" s="141"/>
@@ -21507,7 +21519,7 @@
       <c r="H1" s="141"/>
       <c r="I1" s="142"/>
       <c r="J1" s="147" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="K1" s="147"/>
       <c r="L1" s="147"/>
@@ -21534,13 +21546,13 @@
         <v>311</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2" s="27" t="s">
         <v>39</v>
@@ -21593,10 +21605,10 @@
         <v>350</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E3" s="33" t="s">
         <v>617</v>
@@ -21605,7 +21617,7 @@
         <v>49</v>
       </c>
       <c r="G3" s="32" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H3" s="33" t="s">
         <v>50</v>
@@ -21648,10 +21660,10 @@
         <v>350</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E4" s="33" t="s">
         <v>617</v>
@@ -21701,10 +21713,10 @@
         <v>350</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="E5" s="33" t="s">
         <v>617</v>
@@ -21779,16 +21791,16 @@
         <v>350</v>
       </c>
       <c r="C7" s="53" t="s">
+        <v>858</v>
+      </c>
+      <c r="D7" s="53" t="s">
         <v>859</v>
       </c>
-      <c r="D7" s="53" t="s">
+      <c r="E7" s="53" t="s">
+        <v>856</v>
+      </c>
+      <c r="F7" s="53" t="s">
         <v>860</v>
-      </c>
-      <c r="E7" s="53" t="s">
-        <v>857</v>
-      </c>
-      <c r="F7" s="53" t="s">
-        <v>861</v>
       </c>
       <c r="G7" s="133"/>
       <c r="H7" s="53" t="s">
@@ -21799,11 +21811,11 @@
       </c>
       <c r="J7" s="53"/>
       <c r="K7" s="53" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="L7" s="53"/>
       <c r="M7" s="54" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="N7" s="53" t="s">
         <v>21</v>
@@ -21834,16 +21846,16 @@
         <v>350</v>
       </c>
       <c r="C8" s="53" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="D8" s="53" t="s">
+        <v>862</v>
+      </c>
+      <c r="E8" s="53" t="s">
+        <v>857</v>
+      </c>
+      <c r="F8" s="53" t="s">
         <v>863</v>
-      </c>
-      <c r="E8" s="53" t="s">
-        <v>858</v>
-      </c>
-      <c r="F8" s="53" t="s">
-        <v>864</v>
       </c>
       <c r="G8" s="133"/>
       <c r="H8" s="53" t="s">
@@ -21854,7 +21866,7 @@
       </c>
       <c r="J8" s="53"/>
       <c r="K8" s="53" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="L8" s="53"/>
       <c r="M8" s="53"/>
@@ -22293,7 +22305,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="63" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -22392,7 +22404,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="63" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -22492,7 +22504,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="60" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -22646,7 +22658,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="139" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -22738,7 +22750,7 @@
         <v>350</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D3" s="32" t="s">
         <v>568</v>
@@ -22784,7 +22796,7 @@
         <v>350</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>568</v>
@@ -22830,7 +22842,7 @@
         <v>350</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>568</v>
@@ -22876,7 +22888,7 @@
         <v>350</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D6" s="32" t="s">
         <v>577</v>
@@ -22922,7 +22934,7 @@
         <v>350</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D7" s="32" t="s">
         <v>577</v>
@@ -22968,7 +22980,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D8" s="32" t="s">
         <v>577</v>
@@ -23014,7 +23026,7 @@
         <v>350</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D9" s="32" t="s">
         <v>577</v>
@@ -23060,7 +23072,7 @@
         <v>350</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D10" s="32" t="s">
         <v>582</v>
@@ -23106,7 +23118,7 @@
         <v>350</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D11" s="32" t="s">
         <v>582</v>
@@ -23152,7 +23164,7 @@
         <v>350</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D12" s="32" t="s">
         <v>582</v>
@@ -23198,7 +23210,7 @@
         <v>350</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D13" s="32" t="s">
         <v>570</v>
@@ -23244,7 +23256,7 @@
         <v>350</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D14" s="32" t="s">
         <v>570</v>
@@ -23290,7 +23302,7 @@
         <v>350</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D15" s="32" t="s">
         <v>570</v>
@@ -23336,7 +23348,7 @@
         <v>350</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>570</v>
@@ -23645,7 +23657,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="175" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B1" s="148"/>
       <c r="C1" s="148"/>
@@ -23664,22 +23676,22 @@
         <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>864</v>
+      </c>
+      <c r="D2" s="26" t="s">
         <v>865</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="E2" s="26" t="s">
         <v>866</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="F2" s="26" t="s">
         <v>867</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="G2" s="26" t="s">
         <v>868</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="H2" s="26" t="s">
         <v>869</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>870</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>421</v>
@@ -23706,19 +23718,19 @@
         <v>350</v>
       </c>
       <c r="C4" s="32" t="s">
+        <v>870</v>
+      </c>
+      <c r="D4" s="32" t="s">
         <v>871</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="E4" s="32" t="s">
         <v>872</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="F4" s="32" t="s">
         <v>873</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="G4" s="32" t="s">
         <v>874</v>
-      </c>
-      <c r="G4" s="32" t="s">
-        <v>875</v>
       </c>
       <c r="H4" s="32">
         <v>3600</v>
@@ -23733,19 +23745,19 @@
         <v>350</v>
       </c>
       <c r="C5" s="32" t="s">
+        <v>870</v>
+      </c>
+      <c r="D5" s="32" t="s">
         <v>871</v>
       </c>
-      <c r="D5" s="32" t="s">
-        <v>872</v>
-      </c>
       <c r="E5" s="32" t="s">
+        <v>875</v>
+      </c>
+      <c r="F5" s="32" t="s">
         <v>876</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="G5" s="32" t="s">
         <v>877</v>
-      </c>
-      <c r="G5" s="32" t="s">
-        <v>878</v>
       </c>
       <c r="H5" s="32">
         <v>300</v>
@@ -23760,19 +23772,19 @@
         <v>350</v>
       </c>
       <c r="C6" s="32" t="s">
+        <v>878</v>
+      </c>
+      <c r="D6" s="32" t="s">
         <v>879</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="E6" s="32" t="s">
         <v>880</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="F6" s="32" t="s">
+        <v>873</v>
+      </c>
+      <c r="G6" s="32" t="s">
         <v>881</v>
-      </c>
-      <c r="F6" s="32" t="s">
-        <v>874</v>
-      </c>
-      <c r="G6" s="32" t="s">
-        <v>882</v>
       </c>
       <c r="H6" s="32">
         <v>300</v>
@@ -24042,7 +24054,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="40" customFormat="1" ht="108" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -24074,7 +24086,7 @@
         <v>552</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="D3" s="32" t="s">
         <v>397</v>
@@ -24089,7 +24101,7 @@
         <v>553</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>397</v>
@@ -24104,7 +24116,7 @@
         <v>350</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>397</v>
@@ -24119,7 +24131,7 @@
         <v>554</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="D6" s="32" t="s">
         <v>397</v>
@@ -24305,7 +24317,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="200" customHeight="1">
       <c r="A1" s="149" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B1" s="150"/>
       <c r="C1" s="150"/>
@@ -24332,22 +24344,22 @@
         <v>311</v>
       </c>
       <c r="E2" s="26" t="s">
+        <v>882</v>
+      </c>
+      <c r="F2" s="26" t="s">
         <v>883</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="G2" s="26" t="s">
         <v>884</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="H2" s="26" t="s">
         <v>885</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="I2" s="26" t="s">
         <v>886</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="J2" s="26" t="s">
         <v>887</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>888</v>
       </c>
       <c r="K2" s="26" t="s">
         <v>421</v>
@@ -24376,26 +24388,26 @@
         <v>350</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E4" s="32" t="s">
+        <v>888</v>
+      </c>
+      <c r="F4" s="29" t="s">
         <v>889</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="G4" s="33" t="s">
+        <v>733</v>
+      </c>
+      <c r="H4" s="29" t="s">
         <v>890</v>
-      </c>
-      <c r="G4" s="33" t="s">
-        <v>734</v>
-      </c>
-      <c r="H4" s="29" t="s">
-        <v>891</v>
       </c>
       <c r="I4" s="28"/>
       <c r="J4" s="29" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K4" s="29"/>
     </row>
@@ -24407,22 +24419,22 @@
         <v>350</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F5" s="29" t="s">
+        <v>892</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>733</v>
+      </c>
+      <c r="H5" s="29" t="s">
         <v>893</v>
-      </c>
-      <c r="G5" s="33" t="s">
-        <v>734</v>
-      </c>
-      <c r="H5" s="29" t="s">
-        <v>894</v>
       </c>
       <c r="I5" s="29"/>
       <c r="J5" s="29"/>
@@ -24491,7 +24503,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="89.25" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -24691,7 +24703,7 @@
   <sheetData>
     <row r="1" spans="1:37" ht="250" customHeight="1">
       <c r="A1" s="151" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="B1" s="152"/>
       <c r="C1" s="152"/>
@@ -24701,7 +24713,7 @@
       <c r="G1" s="152"/>
       <c r="H1" s="153"/>
       <c r="I1" s="136" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="J1" s="138"/>
       <c r="K1" s="138"/>
@@ -24749,7 +24761,7 @@
         <v>85</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G2" s="26" t="s">
         <v>91</v>
@@ -24764,64 +24776,64 @@
         <v>84</v>
       </c>
       <c r="K2" s="27" t="s">
+        <v>738</v>
+      </c>
+      <c r="L2" s="27" t="s">
         <v>739</v>
       </c>
-      <c r="L2" s="27" t="s">
-        <v>740</v>
-      </c>
       <c r="M2" s="27" t="s">
+        <v>741</v>
+      </c>
+      <c r="N2" s="27" t="s">
         <v>742</v>
       </c>
-      <c r="N2" s="27" t="s">
-        <v>743</v>
-      </c>
       <c r="O2" s="27" t="s">
+        <v>1597</v>
+      </c>
+      <c r="P2" s="27" t="s">
+        <v>996</v>
+      </c>
+      <c r="Q2" s="27" t="s">
         <v>1598</v>
       </c>
-      <c r="P2" s="27" t="s">
-        <v>997</v>
-      </c>
-      <c r="Q2" s="27" t="s">
+      <c r="R2" s="27" t="s">
         <v>1599</v>
       </c>
-      <c r="R2" s="27" t="s">
+      <c r="S2" s="27" t="s">
         <v>1600</v>
       </c>
-      <c r="S2" s="27" t="s">
+      <c r="T2" s="27" t="s">
         <v>1601</v>
       </c>
-      <c r="T2" s="27" t="s">
+      <c r="U2" s="27" t="s">
         <v>1602</v>
       </c>
-      <c r="U2" s="27" t="s">
+      <c r="V2" s="27" t="s">
         <v>1603</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="W2" s="27" t="s">
         <v>1604</v>
       </c>
-      <c r="W2" s="27" t="s">
+      <c r="X2" s="27" t="s">
         <v>1605</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="Y2" s="27" t="s">
         <v>1606</v>
       </c>
-      <c r="Y2" s="27" t="s">
+      <c r="Z2" s="27" t="s">
         <v>1607</v>
       </c>
-      <c r="Z2" s="27" t="s">
+      <c r="AA2" s="27" t="s">
         <v>1608</v>
       </c>
-      <c r="AA2" s="27" t="s">
+      <c r="AB2" s="27" t="s">
         <v>1609</v>
       </c>
-      <c r="AB2" s="27" t="s">
+      <c r="AC2" s="27" t="s">
+        <v>1615</v>
+      </c>
+      <c r="AD2" s="27" t="s">
         <v>1610</v>
-      </c>
-      <c r="AC2" s="27" t="s">
-        <v>1616</v>
-      </c>
-      <c r="AD2" s="27" t="s">
-        <v>1611</v>
       </c>
       <c r="AE2" s="26" t="s">
         <v>94</v>
@@ -24839,7 +24851,7 @@
         <v>97</v>
       </c>
       <c r="AJ2" s="27" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="AK2" s="26" t="s">
         <v>421</v>
@@ -24856,25 +24868,25 @@
         <v>55</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E3" s="33" t="s">
         <v>349</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="G3" s="33" t="b">
         <v>0</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="I3" s="33" t="s">
         <v>431</v>
       </c>
       <c r="J3" s="134" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="K3" s="33">
         <v>8</v>
@@ -24960,7 +24972,7 @@
         <v>103</v>
       </c>
       <c r="F5" s="54" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G5" s="53" t="b">
         <v>0</v>
@@ -24979,7 +24991,7 @@
       </c>
       <c r="N5" s="53"/>
       <c r="O5" s="53" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="P5" s="53"/>
       <c r="Q5" s="53"/>
@@ -25010,7 +25022,7 @@
         <v>90</v>
       </c>
       <c r="AJ5" s="54" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="AK5" s="54" t="s">
         <v>429</v>
@@ -25033,7 +25045,7 @@
         <v>349</v>
       </c>
       <c r="F6" s="54" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="G6" s="53" t="b">
         <v>0</v>
@@ -25081,7 +25093,7 @@
       </c>
       <c r="AI6" s="53"/>
       <c r="AJ6" s="54" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="AK6" s="53"/>
     </row>
@@ -25102,7 +25114,7 @@
         <v>103</v>
       </c>
       <c r="F7" s="54" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G7" s="53" t="b">
         <v>0</v>
@@ -25159,20 +25171,20 @@
         <v>55</v>
       </c>
       <c r="D8" s="53" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E8" s="53" t="s">
         <v>349</v>
       </c>
       <c r="F8" s="54" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G8" s="53" t="b">
         <v>0</v>
       </c>
       <c r="H8" s="53"/>
       <c r="I8" s="53" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="J8" s="135" t="s">
         <v>104</v>
@@ -25257,7 +25269,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="202" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B1" s="141"/>
       <c r="C1" s="141"/>
@@ -25288,7 +25300,7 @@
         <v>105</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="E2" s="26" t="s">
         <v>106</v>
@@ -25303,25 +25315,25 @@
         <v>108</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="J2" s="27" t="s">
         <v>430</v>
       </c>
       <c r="K2" s="27" t="s">
+        <v>1052</v>
+      </c>
+      <c r="L2" s="27" t="s">
         <v>1053</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="M2" s="27" t="s">
         <v>1054</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="N2" s="27" t="s">
         <v>1055</v>
       </c>
-      <c r="N2" s="27" t="s">
-        <v>1056</v>
-      </c>
       <c r="O2" s="27" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="P2" s="27" t="s">
         <v>95</v>
@@ -25381,22 +25393,22 @@
         <v>109</v>
       </c>
       <c r="I4" s="54" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="J4" s="117" t="s">
+        <v>1056</v>
+      </c>
+      <c r="K4" s="117" t="s">
         <v>1057</v>
-      </c>
-      <c r="K4" s="117" t="s">
-        <v>1058</v>
       </c>
       <c r="L4" s="117">
         <v>100</v>
       </c>
       <c r="M4" s="117" t="s">
+        <v>1058</v>
+      </c>
+      <c r="N4" s="117" t="s">
         <v>1059</v>
-      </c>
-      <c r="N4" s="117" t="s">
-        <v>1060</v>
       </c>
       <c r="O4" s="84" t="b">
         <v>1</v>
@@ -25515,7 +25527,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="190" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1" s="141"/>
       <c r="C1" s="141"/>
@@ -25529,7 +25541,7 @@
       <c r="K1" s="141"/>
       <c r="L1" s="142"/>
       <c r="M1" s="154" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="N1" s="155"/>
       <c r="O1" s="155"/>
@@ -25555,7 +25567,7 @@
         <v>110</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="F2" s="27" t="s">
         <v>111</v>
@@ -25570,13 +25582,13 @@
         <v>113</v>
       </c>
       <c r="J2" s="27" t="s">
+        <v>1060</v>
+      </c>
+      <c r="K2" s="27" t="s">
         <v>1061</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="L2" s="27" t="s">
         <v>1062</v>
-      </c>
-      <c r="L2" s="27" t="s">
-        <v>1063</v>
       </c>
       <c r="M2" s="27" t="s">
         <v>114</v>
@@ -25600,10 +25612,10 @@
         <v>120</v>
       </c>
       <c r="T2" s="27" t="s">
+        <v>1063</v>
+      </c>
+      <c r="U2" s="27" t="s">
         <v>1064</v>
-      </c>
-      <c r="U2" s="27" t="s">
-        <v>1065</v>
       </c>
       <c r="V2" s="27" t="s">
         <v>421</v>
@@ -25651,7 +25663,7 @@
         <v>121</v>
       </c>
       <c r="E4" s="54" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="F4" s="53"/>
       <c r="G4" s="53" t="s">
@@ -25755,7 +25767,7 @@
         <v>121</v>
       </c>
       <c r="E7" s="54" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="F7" s="53"/>
       <c r="G7" s="53"/>
@@ -25793,7 +25805,7 @@
         <v>129</v>
       </c>
       <c r="E8" s="54" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="F8" s="53"/>
       <c r="G8" s="53"/>
@@ -25835,7 +25847,7 @@
         <v>132</v>
       </c>
       <c r="E9" s="54" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="F9" s="53"/>
       <c r="G9" s="53"/>
@@ -25877,7 +25889,7 @@
         <v>134</v>
       </c>
       <c r="E10" s="54" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="F10" s="53"/>
       <c r="G10" s="53"/>
@@ -25912,10 +25924,10 @@
         <v>89</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="E11" s="54" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="F11" s="53"/>
       <c r="G11" s="53"/>
@@ -25951,7 +25963,7 @@
       <c r="G12" s="53"/>
       <c r="H12" s="53"/>
       <c r="I12" s="53" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="J12" s="53"/>
       <c r="K12" s="53"/>
@@ -26055,7 +26067,7 @@
   <sheetData>
     <row r="1" spans="1:35" ht="106" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B1" s="141"/>
       <c r="C1" s="141"/>
@@ -26072,7 +26084,7 @@
       <c r="N1" s="141"/>
       <c r="O1" s="142"/>
       <c r="P1" s="151" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="Q1" s="152"/>
       <c r="R1" s="152"/>
@@ -26102,82 +26114,82 @@
         <v>6</v>
       </c>
       <c r="C2" s="27" t="s">
+        <v>796</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E2" s="27" t="s">
         <v>797</v>
       </c>
-      <c r="D2" s="27" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E2" s="27" t="s">
+      <c r="F2" s="27" t="s">
         <v>798</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="G2" s="27" t="s">
         <v>799</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="H2" s="27" t="s">
+        <v>1135</v>
+      </c>
+      <c r="I2" s="27" t="s">
+        <v>1136</v>
+      </c>
+      <c r="J2" s="27" t="s">
         <v>800</v>
       </c>
-      <c r="H2" s="27" t="s">
-        <v>1136</v>
-      </c>
-      <c r="I2" s="27" t="s">
-        <v>1137</v>
-      </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="27" t="s">
         <v>801</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="L2" s="27" t="s">
         <v>802</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="M2" s="27" t="s">
         <v>803</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="N2" s="27" t="s">
+        <v>1173</v>
+      </c>
+      <c r="O2" s="27" t="s">
         <v>804</v>
       </c>
-      <c r="N2" s="27" t="s">
-        <v>1174</v>
-      </c>
-      <c r="O2" s="27" t="s">
+      <c r="P2" s="27" t="s">
         <v>805</v>
-      </c>
-      <c r="P2" s="27" t="s">
-        <v>806</v>
       </c>
       <c r="Q2" s="27" t="s">
         <v>84</v>
       </c>
       <c r="R2" s="27" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="S2" s="27" t="s">
         <v>430</v>
       </c>
       <c r="T2" s="27" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="U2" s="27" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="V2" s="27" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="W2" s="27" t="s">
         <v>83</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="Y2" s="27" t="s">
+        <v>807</v>
+      </c>
+      <c r="Z2" s="27" t="s">
         <v>808</v>
       </c>
-      <c r="Z2" s="27" t="s">
+      <c r="AA2" s="27" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AB2" s="27" t="s">
         <v>809</v>
-      </c>
-      <c r="AA2" s="27" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AB2" s="27" t="s">
-        <v>810</v>
       </c>
       <c r="AC2" s="27" t="s">
         <v>94</v>
@@ -26186,19 +26198,19 @@
         <v>421</v>
       </c>
       <c r="AE2" s="27" t="s">
+        <v>810</v>
+      </c>
+      <c r="AF2" s="27" t="s">
         <v>811</v>
       </c>
-      <c r="AF2" s="27" t="s">
-        <v>812</v>
-      </c>
       <c r="AG2" s="27" t="s">
+        <v>1010</v>
+      </c>
+      <c r="AH2" s="27" t="s">
         <v>1011</v>
       </c>
-      <c r="AH2" s="27" t="s">
-        <v>1012</v>
-      </c>
       <c r="AI2" s="27" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1">
@@ -26248,76 +26260,76 @@
         <v>552</v>
       </c>
       <c r="C4" s="94" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D4" s="94" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E4" s="94" t="s">
         <v>1013</v>
       </c>
-      <c r="E4" s="94" t="s">
-        <v>1014</v>
-      </c>
       <c r="F4" s="94" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="G4" s="94" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="94" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="I4" s="94" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="J4" s="54" t="b">
         <v>0</v>
       </c>
       <c r="K4" s="94" t="s">
+        <v>815</v>
+      </c>
+      <c r="L4" s="94" t="s">
         <v>816</v>
       </c>
-      <c r="L4" s="94" t="s">
-        <v>817</v>
-      </c>
       <c r="M4" s="94" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="N4" s="94" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="O4" s="94" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="P4" s="94">
         <v>1</v>
       </c>
       <c r="Q4" s="94" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="R4" s="94">
         <v>32</v>
       </c>
       <c r="S4" s="94" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="T4" s="94">
         <v>32</v>
       </c>
       <c r="U4" s="94" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="V4" s="94" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="W4" s="94" t="s">
         <v>98</v>
       </c>
       <c r="X4" s="94" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="Y4" s="94"/>
       <c r="Z4" s="94"/>
       <c r="AA4" s="94"/>
       <c r="AB4" s="95" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AC4" s="94" t="s">
         <v>102</v>
@@ -26346,41 +26358,41 @@
       <c r="L5" s="54"/>
       <c r="M5" s="54"/>
       <c r="N5" s="54" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="O5" s="94" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="P5" s="54">
         <v>2</v>
       </c>
       <c r="Q5" s="54" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="R5" s="54">
         <v>16</v>
       </c>
       <c r="S5" s="54" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="T5" s="54">
         <v>32</v>
       </c>
       <c r="U5" s="54"/>
       <c r="V5" s="94" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="W5" s="54" t="s">
         <v>89</v>
       </c>
       <c r="X5" s="94" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="Y5" s="54"/>
       <c r="Z5" s="54"/>
       <c r="AA5" s="54"/>
       <c r="AB5" s="53" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="AC5" s="54" t="s">
         <v>102</v>
@@ -26400,25 +26412,25 @@
         <v>552</v>
       </c>
       <c r="C6" s="54" t="s">
+        <v>822</v>
+      </c>
+      <c r="D6" s="54" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E6" s="54" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F6" s="54" t="s">
         <v>823</v>
-      </c>
-      <c r="D6" s="54" t="s">
-        <v>1017</v>
-      </c>
-      <c r="E6" s="54" t="s">
-        <v>1014</v>
-      </c>
-      <c r="F6" s="54" t="s">
-        <v>824</v>
       </c>
       <c r="G6" s="54" t="b">
         <v>0</v>
       </c>
       <c r="H6" s="94" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="I6" s="94" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="J6" s="54" t="b">
         <v>0</v>
@@ -26427,44 +26439,44 @@
       <c r="L6" s="54"/>
       <c r="M6" s="54"/>
       <c r="N6" s="54" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="O6" s="94" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="P6" s="54">
         <v>1</v>
       </c>
       <c r="Q6" s="54" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="R6" s="54">
         <v>32</v>
       </c>
       <c r="S6" s="54" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="T6" s="54">
         <v>32</v>
       </c>
       <c r="U6" s="94" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="V6" s="94" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="W6" s="54" t="s">
         <v>98</v>
       </c>
       <c r="X6" s="94" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="Y6" s="54">
         <v>2</v>
       </c>
       <c r="Z6" s="54"/>
       <c r="AA6" s="94" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="AB6" s="96"/>
       <c r="AC6" s="54" t="s">
@@ -26476,7 +26488,7 @@
       <c r="AG6" s="53"/>
       <c r="AH6" s="53"/>
       <c r="AI6" s="54" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
   </sheetData>
@@ -26546,7 +26558,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="122.5" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -26578,7 +26590,7 @@
         <v>136</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E2" s="16" t="s">
         <v>611</v>
@@ -26587,7 +26599,7 @@
         <v>612</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H2" s="16" t="s">
         <v>137</v>
@@ -26596,7 +26608,7 @@
         <v>96</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="K2" s="16" t="s">
         <v>138</v>
@@ -26665,7 +26677,7 @@
       <c r="E4" s="53"/>
       <c r="F4" s="53"/>
       <c r="G4" s="54" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H4" s="53" t="b">
         <v>1</v>
@@ -26739,7 +26751,7 @@
       <c r="E6" s="53"/>
       <c r="F6" s="53"/>
       <c r="G6" s="54" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H6" s="53" t="b">
         <v>0</v>
@@ -26847,7 +26859,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="119.25" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B1" s="141"/>
       <c r="C1" s="141"/>
@@ -26882,16 +26894,16 @@
         <v>136</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F2" s="34" t="s">
         <v>154</v>
       </c>
       <c r="G2" s="34" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2" s="34" t="s">
         <v>155</v>
@@ -26981,7 +26993,7 @@
         <v>165</v>
       </c>
       <c r="G4" s="53" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H4" s="53" t="s">
         <v>166</v>
@@ -27041,7 +27053,7 @@
         <v>171</v>
       </c>
       <c r="G5" s="53" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H5" s="53" t="s">
         <v>166</v>
@@ -27089,7 +27101,7 @@
         <v>174</v>
       </c>
       <c r="G6" s="53" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H6" s="53" t="s">
         <v>166</v>
@@ -27201,7 +27213,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="124" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -27235,7 +27247,7 @@
         <v>239</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>228</v>
@@ -27247,10 +27259,10 @@
         <v>241</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>242</v>
@@ -28192,7 +28204,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="40" customFormat="1" ht="173" customHeight="1">
       <c r="A1" s="137" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B1" s="138"/>
       <c r="C1" s="138"/>
@@ -28212,13 +28224,13 @@
         <v>2</v>
       </c>
       <c r="D2" s="106" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="E2" s="106" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F2" s="127" t="s">
         <v>1191</v>
-      </c>
-      <c r="F2" s="127" t="s">
-        <v>1192</v>
       </c>
       <c r="G2" s="106" t="s">
         <v>421</v>
@@ -28229,10 +28241,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="32" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C3" s="32" t="s">
         <v>1535</v>
-      </c>
-      <c r="C3" s="32" t="s">
-        <v>1536</v>
       </c>
       <c r="D3" s="32"/>
       <c r="E3" s="33"/>
@@ -28244,10 +28256,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="32" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>1537</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>1538</v>
       </c>
       <c r="D4" s="32"/>
       <c r="E4" s="33"/>
@@ -28259,10 +28271,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="32" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C5" s="32" t="s">
         <v>1539</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>1540</v>
       </c>
       <c r="D5" s="32"/>
       <c r="E5" s="33"/>
@@ -28274,10 +28286,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="32" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>1541</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>1542</v>
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="33"/>
@@ -28289,10 +28301,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="32" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C7" s="32" t="s">
         <v>1543</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>1544</v>
       </c>
       <c r="D7" s="32"/>
       <c r="E7" s="19"/>
@@ -28304,10 +28316,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="128" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C8" s="128" t="s">
         <v>1545</v>
-      </c>
-      <c r="C8" s="128" t="s">
-        <v>1546</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="32"/>
@@ -28319,10 +28331,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="32" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C9" s="32" t="s">
         <v>1547</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>1548</v>
       </c>
       <c r="D9" s="32"/>
       <c r="E9" s="32"/>
@@ -28334,10 +28346,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="32" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>1549</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>1550</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="32"/>
@@ -28349,10 +28361,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="32" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C11" s="32" t="s">
         <v>1551</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>1552</v>
       </c>
       <c r="D11" s="32"/>
       <c r="E11" s="32"/>
@@ -28364,10 +28376,10 @@
         <v>5</v>
       </c>
       <c r="B12" s="32" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C12" s="32" t="s">
         <v>1553</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>1554</v>
       </c>
       <c r="D12" s="32"/>
       <c r="E12" s="33"/>
@@ -28379,10 +28391,10 @@
         <v>5</v>
       </c>
       <c r="B13" s="32" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C13" s="32" t="s">
         <v>1555</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>1556</v>
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="33"/>
@@ -28405,15 +28417,15 @@
         <v>5</v>
       </c>
       <c r="B15" s="18" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C15" s="18" t="s">
         <v>1557</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>1558</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="8"/>
       <c r="F15" s="32" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="G15" s="33"/>
     </row>
@@ -28422,15 +28434,15 @@
         <v>5</v>
       </c>
       <c r="B16" s="32" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C16" s="32" t="s">
         <v>1560</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>1561</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
       <c r="F16" s="32" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="G16" s="33"/>
     </row>
@@ -28439,15 +28451,15 @@
         <v>5</v>
       </c>
       <c r="B17" s="32" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C17" s="32" t="s">
         <v>1563</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>1564</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33"/>
       <c r="F17" s="32" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="G17" s="33"/>
     </row>
@@ -28456,15 +28468,15 @@
         <v>5</v>
       </c>
       <c r="B18" s="32" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C18" s="32" t="s">
         <v>1566</v>
-      </c>
-      <c r="C18" s="32" t="s">
-        <v>1567</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="33"/>
       <c r="F18" s="32" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="G18" s="33"/>
     </row>
@@ -28656,7 +28668,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="64" customHeight="1">
       <c r="A1" s="147" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B1" s="138"/>
       <c r="C1" s="138"/>
@@ -28670,10 +28682,10 @@
         <v>136</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="79" customHeight="1">
@@ -28692,10 +28704,10 @@
         <v>395</v>
       </c>
       <c r="C4" s="54" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D4" s="54" t="s">
         <v>1146</v>
-      </c>
-      <c r="D4" s="54" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="93.5" customHeight="1">
@@ -28706,10 +28718,10 @@
         <v>395</v>
       </c>
       <c r="C5" s="54" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D5" s="54" t="s">
         <v>1148</v>
-      </c>
-      <c r="D5" s="54" t="s">
-        <v>1149</v>
       </c>
     </row>
   </sheetData>
@@ -28763,7 +28775,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B1" s="141"/>
       <c r="C1" s="141"/>
@@ -28787,13 +28799,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F2" s="27" t="s">
         <v>96</v>
@@ -28805,7 +28817,7 @@
         <v>92</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="J2" s="27" t="s">
         <v>242</v>
@@ -28814,7 +28826,7 @@
         <v>154</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="M2" s="27" t="s">
         <v>243</v>
@@ -28849,16 +28861,16 @@
         <v>350</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D4" s="54" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="E4" s="54" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="54" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G4" s="54" t="b">
         <v>1</v>
@@ -28866,13 +28878,13 @@
       <c r="H4" s="54"/>
       <c r="I4" s="54"/>
       <c r="J4" s="54" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="K4" s="54" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="L4" s="54" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="M4" s="54">
         <v>7003</v>
@@ -28887,10 +28899,10 @@
         <v>350</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="E5" s="54" t="b">
         <v>1</v>
@@ -28901,16 +28913,16 @@
       </c>
       <c r="H5" s="54"/>
       <c r="I5" s="54" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="J5" s="54" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K5" s="54" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="L5" s="54" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="M5" s="54">
         <v>53</v>
@@ -28928,10 +28940,10 @@
       <c r="H6" s="54"/>
       <c r="I6" s="54"/>
       <c r="J6" s="54" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="K6" s="54" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="L6" s="54" t="s">
         <v>645</v>
@@ -29322,7 +29334,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="22" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B1" s="141"/>
       <c r="C1" s="141"/>
@@ -29344,22 +29356,22 @@
         <v>6</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D2" s="27" t="s">
         <v>154</v>
       </c>
       <c r="E2" s="27" t="s">
+        <v>770</v>
+      </c>
+      <c r="F2" s="27" t="s">
         <v>771</v>
       </c>
-      <c r="F2" s="27" t="s">
-        <v>772</v>
-      </c>
       <c r="G2" s="27" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H2" s="27" t="s">
         <v>1067</v>
-      </c>
-      <c r="H2" s="27" t="s">
-        <v>1068</v>
       </c>
       <c r="I2" s="27" t="s">
         <v>157</v>
@@ -29371,7 +29383,7 @@
         <v>441</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="29.25" customHeight="1">
@@ -29398,13 +29410,13 @@
         <v>350</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D4" s="54" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E4" s="54" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F4" s="54" t="b">
         <v>0</v>
@@ -29417,13 +29429,13 @@
         <v>7003</v>
       </c>
       <c r="J4" s="54" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="K4" s="54">
         <v>10000</v>
       </c>
       <c r="L4" s="54" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="32">
@@ -29434,19 +29446,19 @@
         <v>350</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F5" s="54" t="b">
         <v>1</v>
       </c>
       <c r="G5" s="54" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H5" s="54"/>
       <c r="I5" s="54">
@@ -29457,7 +29469,7 @@
         <v>10000</v>
       </c>
       <c r="L5" s="54" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="16">
@@ -29465,19 +29477,19 @@
       <c r="B6" s="54"/>
       <c r="C6" s="54"/>
       <c r="D6" s="54" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E6" s="54" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F6" s="54" t="b">
         <v>0</v>
       </c>
       <c r="G6" s="54" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H6" s="54" t="s">
         <v>1069</v>
-      </c>
-      <c r="H6" s="54" t="s">
-        <v>1070</v>
       </c>
       <c r="I6" s="54">
         <v>53</v>
@@ -29487,7 +29499,7 @@
         <v>20000</v>
       </c>
       <c r="L6" s="54" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
   </sheetData>
@@ -29550,7 +29562,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="216" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -29580,16 +29592,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="50" t="s">
+        <v>789</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F2" s="16" t="s">
         <v>790</v>
-      </c>
-      <c r="D2" s="50" t="s">
-        <v>1519</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>1130</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>791</v>
       </c>
       <c r="G2" s="16" t="s">
         <v>312</v>
@@ -29601,19 +29613,19 @@
         <v>313</v>
       </c>
       <c r="J2" s="16" t="s">
+        <v>1519</v>
+      </c>
+      <c r="K2" s="16" t="s">
         <v>1520</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="L2" s="16" t="s">
         <v>1521</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="M2" s="16" t="s">
         <v>1522</v>
       </c>
-      <c r="M2" s="16" t="s">
-        <v>1523</v>
-      </c>
       <c r="N2" s="16" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="O2" s="16" t="s">
         <v>403</v>
@@ -29666,15 +29678,15 @@
         <v>553</v>
       </c>
       <c r="C4" s="53" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D4" s="53"/>
       <c r="E4" s="54" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="F4" s="53"/>
       <c r="G4" s="53" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H4" s="53" t="s">
         <v>412</v>
@@ -29683,20 +29695,20 @@
         <v>328</v>
       </c>
       <c r="J4" s="53" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="K4" s="53"/>
       <c r="L4" s="53" t="b">
         <v>1</v>
       </c>
       <c r="M4" s="54" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="N4" s="53" t="s">
         <v>317</v>
       </c>
       <c r="O4" s="54" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="P4" s="53" t="s">
         <v>406</v>
@@ -29718,39 +29730,39 @@
         <v>553</v>
       </c>
       <c r="C5" s="54" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D5" s="54" t="s">
         <v>1527</v>
       </c>
-      <c r="D5" s="54" t="s">
-        <v>1528</v>
-      </c>
       <c r="E5" s="54" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="F5" s="54"/>
       <c r="G5" s="54" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="H5" s="54"/>
       <c r="I5" s="131" t="s">
+        <v>1529</v>
+      </c>
+      <c r="J5" s="54" t="s">
         <v>1530</v>
       </c>
-      <c r="J5" s="54" t="s">
+      <c r="K5" s="54" t="s">
         <v>1531</v>
-      </c>
-      <c r="K5" s="54" t="s">
-        <v>1532</v>
       </c>
       <c r="L5" s="54" t="b">
         <v>1</v>
       </c>
       <c r="M5" s="54" t="s">
+        <v>1532</v>
+      </c>
+      <c r="N5" s="54" t="s">
         <v>1533</v>
       </c>
-      <c r="N5" s="54" t="s">
-        <v>1534</v>
-      </c>
       <c r="O5" s="54" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="P5" s="54" t="s">
         <v>324</v>
@@ -29951,7 +29963,7 @@
   <sheetData>
     <row r="1" spans="1:27" s="1" customFormat="1" ht="135.75" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B1" s="141"/>
       <c r="C1" s="141"/>
@@ -29991,7 +30003,7 @@
         <v>83</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="E2" s="50" t="s">
         <v>675</v>
@@ -30105,10 +30117,10 @@
         <v>55</v>
       </c>
       <c r="D4" s="54" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="E4" s="89" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="F4" s="90" t="s">
         <v>334</v>
@@ -30131,7 +30143,7 @@
         <v>324</v>
       </c>
       <c r="N4" s="90" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="O4" s="90" t="s">
         <v>325</v>
@@ -30180,10 +30192,10 @@
         <v>89</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="E5" s="89" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F5" s="90" t="s">
         <v>337</v>
@@ -30208,7 +30220,7 @@
         <v>324</v>
       </c>
       <c r="N5" s="90" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="O5" s="90" t="s">
         <v>339</v>
@@ -33333,7 +33345,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:H924"/>
+  <dimension ref="A1:J924"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
@@ -33341,12 +33353,13 @@
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="16.1640625" customWidth="1"/>
     <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="17.33203125" customWidth="1"/>
+    <col min="8" max="9" width="8.5"/>
+    <col min="10" max="10" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="119.25" customHeight="1">
+    <row r="1" spans="1:10" ht="119.25" customHeight="1">
       <c r="A1" s="140" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B1" s="141"/>
       <c r="C1" s="141"/>
@@ -33355,8 +33368,10 @@
       <c r="F1" s="141"/>
       <c r="G1" s="141"/>
       <c r="H1" s="141"/>
-    </row>
-    <row r="2" spans="1:8" ht="48">
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+    </row>
+    <row r="2" spans="1:10" ht="48">
       <c r="A2" s="65" t="s">
         <v>0</v>
       </c>
@@ -33378,11 +33393,17 @@
       <c r="G2" s="65" t="s">
         <v>697</v>
       </c>
-      <c r="H2" s="68" t="s">
+      <c r="H2" s="65" t="s">
+        <v>1622</v>
+      </c>
+      <c r="I2" s="65" t="s">
+        <v>1623</v>
+      </c>
+      <c r="J2" s="68" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="A3" s="73" t="s">
         <v>4</v>
       </c>
@@ -33392,9 +33413,9 @@
       <c r="E3" s="43"/>
       <c r="F3" s="33"/>
       <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="J3" s="33"/>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="53" t="s">
         <v>315</v>
       </c>
@@ -33408,7 +33429,7 @@
         <v>55</v>
       </c>
       <c r="E4" s="90" t="s">
-        <v>698</v>
+        <v>1621</v>
       </c>
       <c r="F4" s="54">
         <v>2</v>
@@ -33416,42 +33437,48 @@
       <c r="G4" s="53">
         <v>3</v>
       </c>
-      <c r="H4" s="54"/>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="H4" s="53" t="s">
+        <v>1624</v>
+      </c>
+      <c r="I4" s="53" t="s">
+        <v>1625</v>
+      </c>
+      <c r="J4" s="54"/>
+    </row>
+    <row r="5" spans="1:10">
       <c r="E5" s="69"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:10">
       <c r="E6" s="69"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:10">
       <c r="E7" s="69"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:10">
       <c r="E8" s="69"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:10">
       <c r="E9" s="69"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:10">
       <c r="E10" s="69"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:10">
       <c r="E11" s="69"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:10">
       <c r="E12" s="69"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:10">
       <c r="E13" s="69"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:10">
       <c r="E14" s="69"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:10">
       <c r="E15" s="69"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:10">
       <c r="E16" s="69"/>
     </row>
     <row r="17" spans="5:5">
@@ -36180,10 +36207,10 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="D1:E2 A1:B2 F1:XFD1048576 C1:C1048576" xr:uid="{2C64D8ED-7E49-3F4B-801A-9EBEDAB2003A}"/>
+    <dataValidation allowBlank="1" sqref="D1:E2 A1:B2 C1:C1048576 F1:G1048576 J1:XFD1048576 H4:I1048576 H1:I2" xr:uid="{2C64D8ED-7E49-3F4B-801A-9EBEDAB2003A}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -36192,7 +36219,7 @@
   </headerFooter>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{692F3E3E-9B31-0743-9032-3103E69F6D0D}">
           <x14:formula1>
             <xm:f>drop_down_rule_set!$W$2:$W$4</xm:f>
@@ -36203,7 +36230,7 @@
           <x14:formula1>
             <xm:f>Database_Dropdown!$E$2:$E$13</xm:f>
           </x14:formula1>
-          <xm:sqref>E3:E1048576</xm:sqref>
+          <xm:sqref>E3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{4D98FFF4-AA54-014D-9C48-5C4A6A859D6A}">
           <x14:formula1>
@@ -36216,6 +36243,12 @@
             <xm:f>drop_down_rule_set!$L$2:$L$55</xm:f>
           </x14:formula1>
           <xm:sqref>A3:A1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{C7A033E9-2058-1D46-9EB9-EF7CC1E69D9F}">
+          <x14:formula1>
+            <xm:f>Database_Dropdown!$E$2:$E$14</xm:f>
+          </x14:formula1>
+          <xm:sqref>E4:E1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -36264,7 +36297,7 @@
   <sheetData>
     <row r="1" spans="1:28" s="1" customFormat="1" ht="195" customHeight="1">
       <c r="A1" s="151" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B1" s="152"/>
       <c r="C1" s="152"/>
@@ -36305,13 +36338,13 @@
         <v>695</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E2" s="65" t="s">
+        <v>1155</v>
+      </c>
+      <c r="F2" s="65" t="s">
         <v>1156</v>
-      </c>
-      <c r="F2" s="65" t="s">
-        <v>1157</v>
       </c>
       <c r="G2" s="65" t="s">
         <v>677</v>
@@ -36323,25 +36356,25 @@
         <v>402</v>
       </c>
       <c r="J2" s="65" t="s">
+        <v>699</v>
+      </c>
+      <c r="K2" s="65" t="s">
+        <v>991</v>
+      </c>
+      <c r="L2" s="65" t="s">
+        <v>992</v>
+      </c>
+      <c r="M2" s="65" t="s">
+        <v>993</v>
+      </c>
+      <c r="N2" s="65" t="s">
+        <v>994</v>
+      </c>
+      <c r="O2" s="65" t="s">
         <v>700</v>
       </c>
-      <c r="K2" s="65" t="s">
-        <v>992</v>
-      </c>
-      <c r="L2" s="65" t="s">
-        <v>993</v>
-      </c>
-      <c r="M2" s="65" t="s">
-        <v>994</v>
-      </c>
-      <c r="N2" s="65" t="s">
-        <v>995</v>
-      </c>
-      <c r="O2" s="65" t="s">
+      <c r="P2" s="65" t="s">
         <v>701</v>
-      </c>
-      <c r="P2" s="65" t="s">
-        <v>702</v>
       </c>
       <c r="Q2" s="65" t="s">
         <v>94</v>
@@ -36353,7 +36386,7 @@
         <v>96</v>
       </c>
       <c r="T2" s="77" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="U2" s="72" t="s">
         <v>421</v>
@@ -36401,13 +36434,13 @@
         <v>409</v>
       </c>
       <c r="D4" s="53" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E4" s="54" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="F4" s="54" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G4" s="53">
         <v>4</v>
@@ -36416,7 +36449,7 @@
         <v>324</v>
       </c>
       <c r="I4" s="90" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J4" s="90" t="s">
         <v>414</v>
@@ -36431,7 +36464,7 @@
         <v>96</v>
       </c>
       <c r="N4" s="90" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="O4" s="90" t="b">
         <v>1</v>
@@ -40732,7 +40765,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="169.5" customHeight="1">
       <c r="A1" s="159" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="B1" s="160"/>
       <c r="C1" s="160"/>
@@ -40761,46 +40794,46 @@
         <v>6</v>
       </c>
       <c r="C2" s="34" t="s">
+        <v>895</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E2" s="103" t="s">
         <v>896</v>
       </c>
-      <c r="D2" s="34" t="s">
-        <v>1020</v>
-      </c>
-      <c r="E2" s="103" t="s">
+      <c r="F2" s="103" t="s">
         <v>897</v>
       </c>
-      <c r="F2" s="103" t="s">
+      <c r="G2" s="34" t="s">
         <v>898</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="H2" s="103" t="s">
         <v>899</v>
       </c>
-      <c r="H2" s="103" t="s">
+      <c r="I2" s="34" t="s">
         <v>900</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="J2" s="34" t="s">
         <v>901</v>
       </c>
-      <c r="J2" s="34" t="s">
+      <c r="K2" s="34" t="s">
         <v>902</v>
       </c>
-      <c r="K2" s="34" t="s">
+      <c r="L2" s="124" t="s">
+        <v>989</v>
+      </c>
+      <c r="M2" s="124" t="s">
+        <v>990</v>
+      </c>
+      <c r="N2" s="34" t="s">
         <v>903</v>
       </c>
-      <c r="L2" s="124" t="s">
-        <v>990</v>
-      </c>
-      <c r="M2" s="124" t="s">
-        <v>991</v>
-      </c>
-      <c r="N2" s="34" t="s">
+      <c r="O2" s="34" t="s">
         <v>904</v>
       </c>
-      <c r="O2" s="34" t="s">
+      <c r="P2" s="34" t="s">
         <v>905</v>
-      </c>
-      <c r="P2" s="34" t="s">
-        <v>906</v>
       </c>
       <c r="Q2" s="34" t="s">
         <v>94</v>
@@ -40817,49 +40850,49 @@
         <v>552</v>
       </c>
       <c r="C3" s="32" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D3" s="32" t="s">
         <v>1071</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="E3" s="32" t="s">
         <v>1072</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="F3" s="32" t="s">
         <v>1073</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="G3" s="32" t="s">
         <v>1074</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="H3" s="32" t="s">
         <v>1075</v>
-      </c>
-      <c r="H3" s="32" t="s">
-        <v>1076</v>
       </c>
       <c r="I3" s="32" t="s">
         <v>55</v>
       </c>
       <c r="J3" s="32" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="K3" s="32">
         <v>16</v>
       </c>
       <c r="L3" t="s">
+        <v>1077</v>
+      </c>
+      <c r="M3" t="s">
         <v>1078</v>
-      </c>
-      <c r="M3" t="s">
-        <v>1079</v>
       </c>
       <c r="N3" s="32">
         <v>3</v>
       </c>
       <c r="O3" s="32" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="P3" s="32" t="b">
         <v>0</v>
       </c>
       <c r="Q3" s="32" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="R3" s="28"/>
     </row>
@@ -40871,18 +40904,18 @@
         <v>552</v>
       </c>
       <c r="C4" s="32" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D4" s="32" t="s">
         <v>1082</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>1083</v>
       </c>
       <c r="E4" s="32"/>
       <c r="F4" s="32"/>
       <c r="G4" s="32" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H4" s="32" t="s">
         <v>1075</v>
-      </c>
-      <c r="H4" s="32" t="s">
-        <v>1076</v>
       </c>
       <c r="I4" s="32" t="s">
         <v>55</v>
@@ -40899,7 +40932,7 @@
         <v>3</v>
       </c>
       <c r="O4" s="32" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="P4" s="32" t="b">
         <v>0</v>
@@ -41004,7 +41037,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="52" customHeight="1">
       <c r="A1" s="151" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B1" s="160"/>
       <c r="C1" s="160"/>
@@ -41025,43 +41058,43 @@
         <v>0</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C2" s="103" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D2" s="34" t="s">
+        <v>906</v>
+      </c>
+      <c r="E2" s="34" t="s">
         <v>907</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="F2" s="34" t="s">
         <v>908</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="G2" s="34" t="s">
         <v>909</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="H2" s="34" t="s">
         <v>910</v>
       </c>
-      <c r="H2" s="34" t="s">
+      <c r="I2" s="34" t="s">
         <v>911</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="J2" s="34" t="s">
         <v>912</v>
       </c>
-      <c r="J2" s="34" t="s">
+      <c r="K2" s="34" t="s">
         <v>913</v>
       </c>
-      <c r="K2" s="34" t="s">
+      <c r="L2" s="34" t="s">
         <v>914</v>
       </c>
-      <c r="L2" s="34" t="s">
+      <c r="M2" s="34" t="s">
         <v>915</v>
       </c>
-      <c r="M2" s="34" t="s">
+      <c r="N2" s="34" t="s">
         <v>916</v>
-      </c>
-      <c r="N2" s="34" t="s">
-        <v>917</v>
       </c>
       <c r="O2" s="48"/>
     </row>
@@ -41070,43 +41103,43 @@
         <v>5</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="D3" s="32" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E3" s="32" t="s">
         <v>1085</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="F3" s="32" t="s">
         <v>1086</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="G3" s="32" t="s">
         <v>1087</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="H3" s="32" t="s">
         <v>1088</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="I3" s="32" t="s">
         <v>1089</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="J3" s="32" t="s">
         <v>1090</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="K3" s="32" t="s">
         <v>1091</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="L3" s="32" t="s">
         <v>1092</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="M3" s="32" t="s">
         <v>1093</v>
       </c>
-      <c r="M3" s="32" t="s">
+      <c r="N3" s="32" t="s">
         <v>1094</v>
-      </c>
-      <c r="N3" s="32" t="s">
-        <v>1095</v>
       </c>
       <c r="O3" s="118"/>
     </row>
@@ -41115,41 +41148,41 @@
         <v>5</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="E4" s="32"/>
       <c r="F4" s="32" t="s">
+        <v>1086</v>
+      </c>
+      <c r="G4" s="32" t="s">
         <v>1087</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="H4" s="32" t="s">
         <v>1088</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="I4" s="32" t="s">
         <v>1089</v>
       </c>
-      <c r="I4" s="32" t="s">
+      <c r="J4" s="32" t="s">
         <v>1090</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="K4" s="32" t="s">
         <v>1091</v>
       </c>
-      <c r="K4" s="32" t="s">
+      <c r="L4" s="32" t="s">
         <v>1092</v>
       </c>
-      <c r="L4" s="32" t="s">
+      <c r="M4" s="32" t="s">
         <v>1093</v>
       </c>
-      <c r="M4" s="32" t="s">
-        <v>1094</v>
-      </c>
       <c r="N4" s="32" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="O4" s="118"/>
     </row>
@@ -41241,7 +41274,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="40" customFormat="1" ht="166" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B1" s="138"/>
       <c r="C1" s="138"/>
@@ -41256,22 +41289,22 @@
         <v>0</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="D2" s="26" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>1165</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>1166</v>
-      </c>
       <c r="G2" s="125" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="H2" s="26" t="s">
         <v>421</v>
@@ -42231,7 +42264,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="292" customHeight="1">
       <c r="A1" s="162" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B1" s="163"/>
       <c r="C1" s="163"/>
@@ -42259,49 +42292,49 @@
         <v>6</v>
       </c>
       <c r="C2" s="26" t="s">
+        <v>917</v>
+      </c>
+      <c r="D2" s="26" t="s">
         <v>918</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="E2" s="26" t="s">
         <v>919</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="F2" s="26" t="s">
         <v>920</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="G2" s="26" t="s">
         <v>921</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="H2" s="26" t="s">
         <v>922</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="I2" s="26" t="s">
         <v>923</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="J2" s="26" t="s">
         <v>924</v>
       </c>
-      <c r="J2" s="26" t="s">
+      <c r="K2" s="27" t="s">
         <v>925</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="L2" s="26" t="s">
         <v>926</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="M2" s="27" t="s">
         <v>927</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="N2" s="27" t="s">
         <v>928</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="O2" s="27" t="s">
         <v>929</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="P2" s="27" t="s">
         <v>930</v>
       </c>
-      <c r="P2" s="27" t="s">
+      <c r="Q2" s="27" t="s">
         <v>931</v>
-      </c>
-      <c r="Q2" s="27" t="s">
-        <v>932</v>
       </c>
       <c r="R2" s="26" t="s">
         <v>421</v>
@@ -42320,43 +42353,43 @@
         <v>552</v>
       </c>
       <c r="C4" s="33" t="s">
+        <v>932</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>933</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="E4" s="33" t="s">
         <v>934</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="F4" s="33" t="s">
+        <v>934</v>
+      </c>
+      <c r="G4" s="33" t="s">
         <v>935</v>
       </c>
-      <c r="F4" s="33" t="s">
-        <v>935</v>
-      </c>
-      <c r="G4" s="33" t="s">
+      <c r="H4" s="33" t="s">
         <v>936</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="I4" s="29" t="s">
+        <v>982</v>
+      </c>
+      <c r="J4" s="28" t="s">
         <v>937</v>
       </c>
-      <c r="I4" s="29" t="s">
-        <v>983</v>
-      </c>
-      <c r="J4" s="28" t="s">
+      <c r="K4" s="28" t="s">
         <v>938</v>
       </c>
-      <c r="K4" s="28" t="s">
+      <c r="L4" s="28" t="s">
         <v>939</v>
-      </c>
-      <c r="L4" s="28" t="s">
-        <v>940</v>
       </c>
       <c r="M4" s="28" t="b">
         <v>1</v>
       </c>
       <c r="N4" s="29" t="s">
+        <v>940</v>
+      </c>
+      <c r="O4" s="28" t="s">
         <v>941</v>
-      </c>
-      <c r="O4" s="28" t="s">
-        <v>942</v>
       </c>
       <c r="P4" s="28"/>
       <c r="Q4" s="28"/>
@@ -42369,40 +42402,40 @@
         <v>552</v>
       </c>
       <c r="C5" s="33" t="s">
+        <v>932</v>
+      </c>
+      <c r="D5" s="33" t="s">
         <v>933</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="E5" s="33" t="s">
         <v>934</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="F5" s="33" t="s">
+        <v>934</v>
+      </c>
+      <c r="G5" s="33" t="s">
         <v>935</v>
       </c>
-      <c r="F5" s="33" t="s">
-        <v>935</v>
-      </c>
-      <c r="G5" s="33" t="s">
+      <c r="H5" s="33" t="s">
         <v>936</v>
       </c>
-      <c r="H5" s="33" t="s">
-        <v>937</v>
-      </c>
       <c r="I5" s="29" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="J5" s="28" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="K5" s="28" t="s">
+        <v>942</v>
+      </c>
+      <c r="L5" s="28" t="s">
         <v>943</v>
-      </c>
-      <c r="L5" s="28" t="s">
-        <v>944</v>
       </c>
       <c r="M5" s="28" t="b">
         <v>1</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="O5" s="28"/>
       <c r="P5" s="28"/>
@@ -42416,22 +42449,22 @@
         <v>552</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="D6" s="33" t="s">
+        <v>933</v>
+      </c>
+      <c r="E6" s="33" t="s">
         <v>934</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="F6" s="33" t="s">
+        <v>934</v>
+      </c>
+      <c r="G6" s="33" t="s">
         <v>935</v>
       </c>
-      <c r="F6" s="33" t="s">
-        <v>935</v>
-      </c>
-      <c r="G6" s="33" t="s">
+      <c r="H6" s="33" t="s">
         <v>936</v>
-      </c>
-      <c r="H6" s="33" t="s">
-        <v>937</v>
       </c>
       <c r="I6" s="29"/>
       <c r="J6" s="28"/>
@@ -42451,38 +42484,38 @@
         <v>552</v>
       </c>
       <c r="C7" s="33" t="s">
+        <v>978</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>933</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>934</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>934</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>935</v>
+      </c>
+      <c r="H7" s="33" t="s">
+        <v>936</v>
+      </c>
+      <c r="I7" s="29" t="s">
         <v>979</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>934</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>935</v>
-      </c>
-      <c r="F7" s="33" t="s">
-        <v>935</v>
-      </c>
-      <c r="G7" s="33" t="s">
-        <v>936</v>
-      </c>
-      <c r="H7" s="33" t="s">
-        <v>937</v>
-      </c>
-      <c r="I7" s="29" t="s">
-        <v>980</v>
       </c>
       <c r="J7" s="28"/>
       <c r="K7" s="28" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="L7" s="28" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="M7" s="28" t="b">
         <v>1</v>
       </c>
       <c r="N7" s="29" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="O7" s="28"/>
       <c r="P7" s="28"/>
@@ -42604,7 +42637,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="234" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -42613,7 +42646,7 @@
       <c r="F1" s="136"/>
       <c r="G1" s="136"/>
       <c r="H1" s="147" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="I1" s="136"/>
       <c r="J1" s="136"/>
@@ -42628,46 +42661,46 @@
         <v>0</v>
       </c>
       <c r="B2" s="16" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C2" s="120" t="s">
         <v>1098</v>
       </c>
-      <c r="C2" s="120" t="s">
+      <c r="D2" s="16" t="s">
         <v>1099</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="E2" s="16" t="s">
         <v>1100</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="F2" s="16" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G2" s="49" t="s">
+        <v>1103</v>
+      </c>
+      <c r="H2" s="92" t="s">
+        <v>1104</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>1105</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>1106</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>1107</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>1108</v>
+      </c>
+      <c r="M2" s="122" t="s">
+        <v>1109</v>
+      </c>
+      <c r="N2" s="16" t="s">
         <v>1101</v>
       </c>
-      <c r="F2" s="16" t="s">
-        <v>1103</v>
-      </c>
-      <c r="G2" s="49" t="s">
-        <v>1104</v>
-      </c>
-      <c r="H2" s="92" t="s">
-        <v>1105</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>1106</v>
-      </c>
-      <c r="J2" s="121" t="s">
-        <v>1107</v>
-      </c>
-      <c r="K2" s="16" t="s">
-        <v>1108</v>
-      </c>
-      <c r="L2" s="16" t="s">
-        <v>1109</v>
-      </c>
-      <c r="M2" s="122" t="s">
+      <c r="O2" s="16" t="s">
         <v>1110</v>
-      </c>
-      <c r="N2" s="16" t="s">
-        <v>1102</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="16">
@@ -42697,23 +42730,23 @@
         <v>554</v>
       </c>
       <c r="C4" s="32" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D4" s="32" t="s">
         <v>1112</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>1113</v>
       </c>
       <c r="E4" s="32"/>
       <c r="F4" s="32" t="s">
         <v>554</v>
       </c>
       <c r="G4" s="32" t="s">
+        <v>1113</v>
+      </c>
+      <c r="H4" s="32" t="s">
         <v>1114</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="I4" s="32" t="s">
         <v>1115</v>
-      </c>
-      <c r="I4" s="32" t="s">
-        <v>1116</v>
       </c>
       <c r="J4" s="123">
         <v>256</v>
@@ -42734,19 +42767,19 @@
         <v>552</v>
       </c>
       <c r="G5" s="32" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H5" s="32" t="s">
         <v>1117</v>
       </c>
-      <c r="H5" s="32" t="s">
+      <c r="I5" s="32" t="s">
         <v>1118</v>
-      </c>
-      <c r="I5" s="32" t="s">
-        <v>1119</v>
       </c>
       <c r="J5" s="123">
         <v>384</v>
       </c>
       <c r="K5" s="32" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="L5" s="32"/>
       <c r="M5" s="123"/>
@@ -42761,10 +42794,10 @@
         <v>554</v>
       </c>
       <c r="C6" s="32" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D6" s="32" t="s">
         <v>1121</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>1122</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>5</v>
@@ -42773,13 +42806,13 @@
         <v>554</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="J6" s="123">
         <v>128</v>
@@ -42804,13 +42837,13 @@
         <v>552</v>
       </c>
       <c r="G7" s="32" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H7" s="32" t="s">
         <v>1117</v>
       </c>
-      <c r="H7" s="32" t="s">
-        <v>1118</v>
-      </c>
       <c r="I7" s="32" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="J7" s="123">
         <v>3072</v>
@@ -42831,19 +42864,19 @@
         <v>553</v>
       </c>
       <c r="G8" s="32" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H8" s="32" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="J8" s="123">
         <v>521</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="L8" s="32" t="b">
         <v>1</v>
@@ -43909,7 +43942,7 @@
   <sheetData>
     <row r="1" spans="1:29" ht="212" customHeight="1">
       <c r="A1" s="165" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B1" s="160"/>
       <c r="C1" s="160"/>
@@ -43919,7 +43952,7 @@
       <c r="G1" s="160"/>
       <c r="H1" s="161"/>
       <c r="I1" s="151" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="J1" s="152"/>
       <c r="K1" s="152"/>
@@ -43956,10 +43989,10 @@
         <v>2</v>
       </c>
       <c r="E2" s="34" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F2" s="35" t="s">
         <v>1460</v>
-      </c>
-      <c r="F2" s="35" t="s">
-        <v>1461</v>
       </c>
       <c r="G2" s="34" t="s">
         <v>83</v>
@@ -43968,64 +44001,64 @@
         <v>85</v>
       </c>
       <c r="I2" s="34" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="J2" s="35" t="s">
         <v>84</v>
       </c>
       <c r="K2" s="35" t="s">
+        <v>1461</v>
+      </c>
+      <c r="L2" s="35" t="s">
         <v>1462</v>
-      </c>
-      <c r="L2" s="35" t="s">
-        <v>1463</v>
       </c>
       <c r="M2" s="34" t="s">
         <v>92</v>
       </c>
       <c r="N2" s="34" t="s">
+        <v>1463</v>
+      </c>
+      <c r="O2" s="34" t="s">
         <v>1464</v>
       </c>
-      <c r="O2" s="34" t="s">
+      <c r="P2" s="34" t="s">
         <v>1465</v>
       </c>
-      <c r="P2" s="34" t="s">
+      <c r="Q2" s="34" t="s">
         <v>1466</v>
       </c>
-      <c r="Q2" s="34" t="s">
+      <c r="R2" s="34" t="s">
         <v>1467</v>
       </c>
-      <c r="R2" s="34" t="s">
+      <c r="S2" s="34" t="s">
         <v>1468</v>
       </c>
-      <c r="S2" s="34" t="s">
+      <c r="T2" s="34" t="s">
         <v>1469</v>
       </c>
-      <c r="T2" s="34" t="s">
+      <c r="U2" s="34" t="s">
         <v>1470</v>
       </c>
-      <c r="U2" s="34" t="s">
+      <c r="V2" s="34" t="s">
         <v>1471</v>
       </c>
-      <c r="V2" s="34" t="s">
+      <c r="W2" s="34" t="s">
         <v>1472</v>
       </c>
-      <c r="W2" s="34" t="s">
+      <c r="X2" s="34" t="s">
         <v>1473</v>
       </c>
-      <c r="X2" s="34" t="s">
+      <c r="Y2" s="34" t="s">
         <v>1474</v>
       </c>
-      <c r="Y2" s="34" t="s">
+      <c r="Z2" s="34" t="s">
         <v>1475</v>
-      </c>
-      <c r="Z2" s="34" t="s">
-        <v>1476</v>
       </c>
       <c r="AA2" s="34" t="s">
         <v>75</v>
       </c>
       <c r="AB2" s="34" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="AC2" s="35" t="s">
         <v>421</v>
@@ -44072,16 +44105,16 @@
         <v>553</v>
       </c>
       <c r="C4" s="18" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D4" s="18" t="s">
         <v>1478</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="E4" s="18" t="s">
         <v>1479</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="F4" s="18" t="s">
         <v>1480</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>1481</v>
       </c>
       <c r="G4" s="18" t="s">
         <v>55</v>
@@ -44090,58 +44123,58 @@
         <v>349</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="33" t="s">
+        <v>1482</v>
+      </c>
+      <c r="N4" s="18" t="s">
         <v>1483</v>
       </c>
-      <c r="N4" s="18" t="s">
+      <c r="O4" s="18" t="s">
+        <v>1483</v>
+      </c>
+      <c r="P4" s="18" t="s">
         <v>1484</v>
       </c>
-      <c r="O4" s="18" t="s">
-        <v>1484</v>
-      </c>
-      <c r="P4" s="18" t="s">
+      <c r="Q4" s="18" t="s">
         <v>1485</v>
       </c>
-      <c r="Q4" s="18" t="s">
+      <c r="R4" s="18" t="s">
         <v>1486</v>
       </c>
-      <c r="R4" s="18" t="s">
+      <c r="S4" s="18" t="s">
         <v>1487</v>
       </c>
-      <c r="S4" s="18" t="s">
+      <c r="T4" s="18" t="s">
         <v>1488</v>
-      </c>
-      <c r="T4" s="18" t="s">
-        <v>1489</v>
       </c>
       <c r="U4" s="18" t="s">
         <v>192</v>
       </c>
       <c r="V4" s="18" t="s">
+        <v>1489</v>
+      </c>
+      <c r="W4" s="18" t="s">
+        <v>1480</v>
+      </c>
+      <c r="X4" s="129" t="s">
         <v>1490</v>
       </c>
-      <c r="W4" s="18" t="s">
-        <v>1481</v>
-      </c>
-      <c r="X4" s="129" t="s">
+      <c r="Y4" s="18" t="s">
         <v>1491</v>
       </c>
-      <c r="Y4" s="18" t="s">
+      <c r="Z4" s="18" t="s">
         <v>1492</v>
-      </c>
-      <c r="Z4" s="18" t="s">
-        <v>1493</v>
       </c>
       <c r="AA4" s="18"/>
       <c r="AB4" s="8" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="AC4" s="18"/>
     </row>
@@ -44153,16 +44186,16 @@
         <v>553</v>
       </c>
       <c r="C5" s="32" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D5" s="32" t="s">
         <v>1495</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="E5" s="32" t="s">
         <v>1496</v>
       </c>
-      <c r="E5" s="32" t="s">
-        <v>1497</v>
-      </c>
       <c r="F5" s="32" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G5" s="32" t="s">
         <v>89</v>
@@ -44171,56 +44204,56 @@
         <v>103</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="K5" s="32"/>
       <c r="L5" s="32"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32" t="s">
+        <v>1483</v>
+      </c>
+      <c r="O5" s="32" t="s">
+        <v>1483</v>
+      </c>
+      <c r="P5" s="32" t="s">
         <v>1484</v>
       </c>
-      <c r="O5" s="32" t="s">
-        <v>1484</v>
-      </c>
-      <c r="P5" s="32" t="s">
+      <c r="Q5" s="32" t="s">
         <v>1485</v>
       </c>
-      <c r="Q5" s="32" t="s">
+      <c r="R5" s="32" t="s">
         <v>1486</v>
       </c>
-      <c r="R5" s="32" t="s">
+      <c r="S5" s="32" t="s">
         <v>1487</v>
       </c>
-      <c r="S5" s="32" t="s">
+      <c r="T5" s="32" t="s">
         <v>1488</v>
-      </c>
-      <c r="T5" s="32" t="s">
-        <v>1489</v>
       </c>
       <c r="U5" s="32" t="s">
         <v>192</v>
       </c>
       <c r="V5" s="32" t="s">
+        <v>1489</v>
+      </c>
+      <c r="W5" s="32" t="s">
+        <v>1480</v>
+      </c>
+      <c r="X5" s="32" t="s">
         <v>1490</v>
       </c>
-      <c r="W5" s="32" t="s">
-        <v>1481</v>
-      </c>
-      <c r="X5" s="32" t="s">
+      <c r="Y5" s="32" t="s">
         <v>1491</v>
       </c>
-      <c r="Y5" s="32" t="s">
+      <c r="Z5" s="32" t="s">
         <v>1492</v>
-      </c>
-      <c r="Z5" s="32" t="s">
-        <v>1493</v>
       </c>
       <c r="AA5" s="32"/>
       <c r="AB5" s="33" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="AC5" s="32"/>
     </row>
@@ -50184,7 +50217,7 @@
   <sheetData>
     <row r="1" spans="1:81" ht="185" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -50210,13 +50243,13 @@
         <v>2</v>
       </c>
       <c r="E2" s="26" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F2" s="26" t="s">
         <v>1500</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="G2" s="26" t="s">
         <v>1501</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>1502</v>
       </c>
       <c r="H2" s="26" t="s">
         <v>421</v>
@@ -50239,23 +50272,23 @@
     </row>
     <row r="4" spans="1:81" ht="32" customHeight="1">
       <c r="A4" s="32" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>553</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="D4" s="32"/>
       <c r="E4" s="32" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="F4" s="32" t="s">
+        <v>1503</v>
+      </c>
+      <c r="G4" s="32" t="s">
         <v>1504</v>
-      </c>
-      <c r="G4" s="32" t="s">
-        <v>1505</v>
       </c>
       <c r="H4" s="32"/>
     </row>
@@ -50266,32 +50299,32 @@
       <c r="D5" s="32"/>
       <c r="E5" s="32"/>
       <c r="F5" s="32" t="s">
+        <v>1505</v>
+      </c>
+      <c r="G5" s="32" t="s">
         <v>1506</v>
-      </c>
-      <c r="G5" s="32" t="s">
-        <v>1507</v>
       </c>
       <c r="H5" s="32"/>
     </row>
     <row r="6" spans="1:81" ht="32" customHeight="1">
       <c r="A6" s="32" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="B6" s="32" t="s">
         <v>553</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="32" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="F6" s="32" t="s">
+        <v>1503</v>
+      </c>
+      <c r="G6" s="32" t="s">
         <v>1504</v>
-      </c>
-      <c r="G6" s="32" t="s">
-        <v>1505</v>
       </c>
       <c r="H6" s="32"/>
     </row>
@@ -50302,10 +50335,10 @@
       <c r="D7" s="32"/>
       <c r="E7" s="32"/>
       <c r="F7" s="32" t="s">
+        <v>1507</v>
+      </c>
+      <c r="G7" s="32" t="s">
         <v>1508</v>
-      </c>
-      <c r="G7" s="32" t="s">
-        <v>1509</v>
       </c>
       <c r="H7" s="32"/>
     </row>
@@ -50316,10 +50349,10 @@
       <c r="D8" s="32"/>
       <c r="E8" s="32"/>
       <c r="F8" s="32" t="s">
+        <v>1509</v>
+      </c>
+      <c r="G8" s="32" t="s">
         <v>1510</v>
-      </c>
-      <c r="G8" s="32" t="s">
-        <v>1511</v>
       </c>
       <c r="H8" s="32"/>
     </row>
@@ -51577,7 +51610,7 @@
         <v>676</v>
       </c>
       <c r="L1" s="44" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="M1" s="44"/>
     </row>
@@ -51676,7 +51709,7 @@
         <v>443</v>
       </c>
       <c r="L4" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -51684,7 +51717,7 @@
         <v>334</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C5" s="33" t="s">
         <v>413</v>
@@ -51698,7 +51731,7 @@
         <v>444</v>
       </c>
       <c r="L5" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -51707,7 +51740,7 @@
       </c>
       <c r="B6" s="33"/>
       <c r="C6" s="33" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="33" t="s">
@@ -51724,7 +51757,7 @@
       </c>
       <c r="B7" s="33"/>
       <c r="C7" s="33" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D7" s="33"/>
       <c r="E7" s="33" t="s">
@@ -51741,7 +51774,7 @@
       </c>
       <c r="B8" s="33"/>
       <c r="C8" s="33" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D8" s="33"/>
       <c r="E8" s="33" t="s">
@@ -51775,7 +51808,7 @@
       </c>
       <c r="B10" s="33"/>
       <c r="C10" s="33" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33" t="s">
@@ -51792,7 +51825,7 @@
       </c>
       <c r="B11" s="33"/>
       <c r="C11" s="33" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D11" s="33"/>
       <c r="E11" s="33" t="s">
@@ -51809,11 +51842,11 @@
       </c>
       <c r="B12" s="33"/>
       <c r="C12" s="33" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="33" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F12" s="33"/>
       <c r="H12" s="33" t="s">
@@ -51826,11 +51859,11 @@
       </c>
       <c r="B13" s="33"/>
       <c r="C13" s="33" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D13" s="33"/>
       <c r="E13" s="33" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F13" s="33"/>
       <c r="H13" s="33" t="s">
@@ -51843,10 +51876,12 @@
       </c>
       <c r="B14" s="33"/>
       <c r="C14" s="33" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
+      <c r="E14" s="33" t="s">
+        <v>1621</v>
+      </c>
       <c r="F14" s="33"/>
       <c r="H14" s="33" t="s">
         <v>453</v>
@@ -52392,25 +52427,25 @@
         <v>616</v>
       </c>
       <c r="D1" s="64" t="s">
+        <v>984</v>
+      </c>
+      <c r="E1" s="64" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F1" s="64" t="s">
+        <v>947</v>
+      </c>
+      <c r="G1" s="64" t="s">
+        <v>948</v>
+      </c>
+      <c r="H1" s="64" t="s">
+        <v>949</v>
+      </c>
+      <c r="I1" s="64" t="s">
         <v>985</v>
       </c>
-      <c r="E1" s="64" t="s">
-        <v>1161</v>
-      </c>
-      <c r="F1" s="64" t="s">
-        <v>948</v>
-      </c>
-      <c r="G1" s="64" t="s">
-        <v>949</v>
-      </c>
-      <c r="H1" s="64" t="s">
+      <c r="J1" s="64" t="s">
         <v>950</v>
-      </c>
-      <c r="I1" s="64" t="s">
-        <v>986</v>
-      </c>
-      <c r="J1" s="64" t="s">
-        <v>951</v>
       </c>
       <c r="K1" s="64" t="s">
         <v>618</v>
@@ -52509,22 +52544,22 @@
         <v>314</v>
       </c>
       <c r="AQ1" s="55" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AR1" s="55" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AS1" s="55" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AT1" s="55" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="AU1" s="55" t="s">
         <v>617</v>
       </c>
       <c r="AV1" s="55" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="2" spans="1:48" s="57" customFormat="1" ht="16">
@@ -52570,7 +52605,7 @@
         <v>21</v>
       </c>
       <c r="L2" s="126" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="M2" s="58" t="s">
         <v>38</v>
@@ -52589,7 +52624,7 @@
         <v>23</v>
       </c>
       <c r="R2" s="58" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="S2" s="58" t="s">
         <v>569</v>
@@ -52666,13 +52701,13 @@
         <v>316</v>
       </c>
       <c r="AQ2" s="57" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="AR2" s="57" t="b">
         <v>0</v>
       </c>
       <c r="AS2" s="57" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AT2" s="57" t="str" cm="1">
         <f t="array" aca="1" ref="AT2:AT3" ca="1">_xlfn.UNIQUE(INDIRECT("B2:B"&amp;$G$5),FALSE,FALSE)</f>
@@ -52727,7 +52762,7 @@
         <v>23</v>
       </c>
       <c r="L3" s="33" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="M3" s="58" t="s">
         <v>36</v>
@@ -52824,13 +52859,13 @@
         <v>317</v>
       </c>
       <c r="AQ3" s="57" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AR3" s="57" t="b">
         <v>1</v>
       </c>
       <c r="AS3" s="57" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AT3" s="57" t="str">
         <f ca="1"/>
@@ -52954,7 +52989,7 @@
         <v>32</v>
       </c>
       <c r="AS4" s="57" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AU4" s="101" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -53088,7 +53123,7 @@
       <c r="J6" s="33"/>
       <c r="K6" s="58"/>
       <c r="L6" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="M6" s="58"/>
       <c r="N6" s="58"/>
@@ -53169,7 +53204,7 @@
       <c r="J7" s="33"/>
       <c r="K7" s="58"/>
       <c r="L7" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="M7" s="58"/>
       <c r="N7" s="58"/>
@@ -53248,7 +53283,7 @@
       <c r="J8" s="33"/>
       <c r="K8" s="58"/>
       <c r="L8" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="M8" s="58"/>
       <c r="N8" s="58"/>
@@ -53718,7 +53753,7 @@
       <c r="J14" s="33"/>
       <c r="K14" s="58"/>
       <c r="L14" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="M14" s="58"/>
       <c r="N14" s="58"/>
@@ -53795,7 +53830,7 @@
       <c r="J15" s="33"/>
       <c r="K15" s="58"/>
       <c r="L15" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="M15" s="58"/>
       <c r="N15" s="58"/>
@@ -53872,7 +53907,7 @@
       <c r="J16" s="33"/>
       <c r="K16" s="58"/>
       <c r="L16" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="M16" s="58"/>
       <c r="N16" s="58"/>
@@ -54026,7 +54061,7 @@
       <c r="J18" s="33"/>
       <c r="K18" s="58"/>
       <c r="L18" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="M18" s="58"/>
       <c r="N18" s="58"/>
@@ -54103,7 +54138,7 @@
       <c r="J19" s="33"/>
       <c r="K19" s="58"/>
       <c r="L19" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="M19" s="58"/>
       <c r="N19" s="58"/>
@@ -54249,7 +54284,7 @@
       <c r="J21" s="33"/>
       <c r="K21" s="58"/>
       <c r="L21" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="M21" s="58"/>
       <c r="N21" s="58"/>
@@ -54395,7 +54430,7 @@
       <c r="J23" s="33"/>
       <c r="K23" s="58"/>
       <c r="L23" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="M23" s="58"/>
       <c r="N23" s="58"/>
@@ -54541,7 +54576,7 @@
       <c r="J25" s="33"/>
       <c r="K25" s="58"/>
       <c r="L25" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="M25" s="58"/>
       <c r="N25" s="58"/>
@@ -54687,7 +54722,7 @@
       <c r="J27" s="33"/>
       <c r="K27" s="58"/>
       <c r="L27" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="M27" s="58"/>
       <c r="N27" s="58"/>
@@ -54833,7 +54868,7 @@
       <c r="J29" s="33"/>
       <c r="K29" s="58"/>
       <c r="L29" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="M29" s="58"/>
       <c r="N29" s="58"/>
@@ -54906,7 +54941,7 @@
       <c r="J30" s="33"/>
       <c r="K30" s="58"/>
       <c r="L30" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="M30" s="58"/>
       <c r="N30" s="58"/>
@@ -54979,7 +55014,7 @@
       <c r="J31" s="33"/>
       <c r="K31" s="58"/>
       <c r="L31" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="M31" s="58"/>
       <c r="N31" s="58"/>
@@ -55125,7 +55160,7 @@
       <c r="J33" s="33"/>
       <c r="K33" s="58"/>
       <c r="L33" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="M33" s="58"/>
       <c r="N33" s="58"/>
@@ -55255,7 +55290,7 @@
       <c r="J35" s="33"/>
       <c r="K35" s="58"/>
       <c r="L35" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="M35" s="58"/>
       <c r="N35" s="58"/>
@@ -55311,7 +55346,7 @@
       <c r="J36" s="33"/>
       <c r="K36" s="58"/>
       <c r="L36" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="M36" s="58"/>
       <c r="N36" s="58"/>
@@ -55384,7 +55419,7 @@
       <c r="J37" s="33"/>
       <c r="K37" s="58"/>
       <c r="L37" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="M37" s="58"/>
       <c r="N37" s="58"/>
@@ -55676,7 +55711,7 @@
       <c r="J41" s="33"/>
       <c r="K41" s="58"/>
       <c r="L41" s="63" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="M41" s="58"/>
       <c r="N41" s="58"/>
@@ -55794,7 +55829,7 @@
       <c r="I43" s="33"/>
       <c r="J43" s="33"/>
       <c r="L43" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="P43" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P43" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A43,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A43,4,4,1,"DHCP")))</f>
@@ -55886,7 +55921,7 @@
       <c r="I45" s="33"/>
       <c r="J45" s="33"/>
       <c r="L45" s="57" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="P45" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P45" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A45,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A45,4,4,1,"DHCP")))</f>
@@ -55932,7 +55967,7 @@
       <c r="I46" s="33"/>
       <c r="J46" s="33"/>
       <c r="L46" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="P46" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P46" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A46,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A46,4,4,1,"DHCP")))</f>
@@ -55978,7 +56013,7 @@
       <c r="I47" s="33"/>
       <c r="J47" s="33"/>
       <c r="L47" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="P47" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P47" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A47,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A47,4,4,1,"DHCP")))</f>
@@ -56024,7 +56059,7 @@
       <c r="I48" s="33"/>
       <c r="J48" s="33"/>
       <c r="L48" s="40" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="P48" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P48" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A48,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A48,4,4,1,"DHCP")))</f>
@@ -56070,7 +56105,7 @@
       <c r="I49" s="33"/>
       <c r="J49" s="33"/>
       <c r="L49" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="P49" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P49" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A49,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A49,4,4,1,"DHCP")))</f>
@@ -56116,7 +56151,7 @@
       <c r="I50" s="33"/>
       <c r="J50" s="33"/>
       <c r="L50" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="P50" s="58" t="str" cm="1">
         <f t="array" aca="1" ref="P50" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"DHCP")&amp;":"&amp;ADDRESS(A50,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A50,4,4,1,"DHCP")))</f>
@@ -56151,7 +56186,7 @@
       <c r="I51" s="33"/>
       <c r="J51" s="33"/>
       <c r="L51" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="AG51" s="63"/>
       <c r="AU51" s="101" t="str">
@@ -56171,7 +56206,7 @@
       <c r="I52" s="33"/>
       <c r="J52" s="33"/>
       <c r="L52" s="40" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="AU52" s="101" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -56191,7 +56226,7 @@
       <c r="I53" s="33"/>
       <c r="J53" s="33"/>
       <c r="L53" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="AU53" s="101" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -56211,7 +56246,7 @@
       <c r="I54" s="33"/>
       <c r="J54" s="33"/>
       <c r="L54" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="AU54" s="101" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -59085,10 +59120,10 @@
         <v>668</v>
       </c>
       <c r="C1" s="55" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D1" s="55" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -59588,7 +59623,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="40" customFormat="1" ht="134.25" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B1" s="138"/>
       <c r="C1" s="138"/>
@@ -59607,10 +59642,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="26" t="s">
+        <v>853</v>
+      </c>
+      <c r="E2" s="26" t="s">
         <v>854</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>855</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>421</v>
@@ -59660,7 +59695,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="40" customFormat="1" ht="131" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -59710,7 +59745,7 @@
         <v>593</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="F3" s="32"/>
       <c r="G3" s="32"/>
@@ -59722,7 +59757,7 @@
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
       <c r="E4" s="32" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="F4" s="32"/>
       <c r="G4" s="32"/>
@@ -59733,16 +59768,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="C5" s="32" t="s">
         <v>397</v>
       </c>
       <c r="D5" s="32" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E5" s="32" t="s">
         <v>1570</v>
-      </c>
-      <c r="E5" s="32" t="s">
-        <v>1571</v>
       </c>
       <c r="F5" s="32"/>
       <c r="G5" s="32"/>
@@ -59754,7 +59789,7 @@
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="E6" s="32" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
@@ -59766,7 +59801,7 @@
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="E7" s="32" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
@@ -59786,7 +59821,7 @@
         <v>556</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
@@ -59798,7 +59833,7 @@
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="E9" s="32" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
@@ -59810,7 +59845,7 @@
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="E10" s="32" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
@@ -59822,7 +59857,7 @@
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="E11" s="32" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
@@ -59834,7 +59869,7 @@
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="E12" s="32" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -59846,7 +59881,7 @@
       <c r="C13" s="32"/>
       <c r="D13" s="32"/>
       <c r="E13" s="32" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -59858,7 +59893,7 @@
       <c r="C14" s="32"/>
       <c r="D14" s="32"/>
       <c r="E14" s="32" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -59870,7 +59905,7 @@
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
       <c r="E15" s="32" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -59882,7 +59917,7 @@
       <c r="C16" s="32"/>
       <c r="D16" s="32"/>
       <c r="E16" s="32" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -59894,7 +59929,7 @@
       <c r="C17" s="32"/>
       <c r="D17" s="32"/>
       <c r="E17" s="32" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
@@ -59906,7 +59941,7 @@
       <c r="C18" s="32"/>
       <c r="D18" s="32"/>
       <c r="E18" s="32" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -59918,7 +59953,7 @@
       <c r="C19" s="32"/>
       <c r="D19" s="32"/>
       <c r="E19" s="32" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -59930,7 +59965,7 @@
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
       <c r="E20" s="32" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
@@ -59942,7 +59977,7 @@
       <c r="C21" s="32"/>
       <c r="D21" s="32"/>
       <c r="E21" s="32" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F21" s="32"/>
       <c r="G21" s="32"/>
@@ -59954,7 +59989,7 @@
       <c r="C22" s="32"/>
       <c r="D22" s="32"/>
       <c r="E22" s="32" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
@@ -59966,7 +60001,7 @@
       <c r="C23" s="32"/>
       <c r="D23" s="32"/>
       <c r="E23" s="32" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F23" s="32"/>
       <c r="G23" s="32"/>
@@ -59978,7 +60013,7 @@
       <c r="C24" s="32"/>
       <c r="D24" s="32"/>
       <c r="E24" s="32" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F24" s="32"/>
       <c r="G24" s="32"/>
@@ -59990,7 +60025,7 @@
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
       <c r="E25" s="32" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="F25" s="32"/>
       <c r="G25" s="32"/>
@@ -60002,7 +60037,7 @@
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
       <c r="E26" s="32" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
@@ -60014,7 +60049,7 @@
       <c r="C27" s="32"/>
       <c r="D27" s="32"/>
       <c r="E27" s="32" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="F27" s="32"/>
       <c r="G27" s="32"/>
@@ -60026,7 +60061,7 @@
       <c r="C28" s="32"/>
       <c r="D28" s="32"/>
       <c r="E28" s="32" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F28" s="32"/>
       <c r="G28" s="32"/>
@@ -60038,7 +60073,7 @@
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="E29" s="32" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F29" s="32"/>
       <c r="G29" s="32"/>
@@ -60050,7 +60085,7 @@
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="E30" s="32" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F30" s="32"/>
       <c r="G30" s="32"/>
@@ -60062,7 +60097,7 @@
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="E31" s="32" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F31" s="32"/>
       <c r="G31" s="32"/>
@@ -60074,7 +60109,7 @@
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="E32" s="32" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="F32" s="32"/>
       <c r="G32" s="32"/>
@@ -60086,7 +60121,7 @@
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
       <c r="E33" s="32" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F33" s="32"/>
       <c r="G33" s="32"/>
@@ -60098,7 +60133,7 @@
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
       <c r="E34" s="32" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="F34" s="32"/>
       <c r="G34" s="32"/>
@@ -60110,7 +60145,7 @@
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="E35" s="32" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="F35" s="32"/>
       <c r="G35" s="32"/>
@@ -60122,7 +60157,7 @@
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="E36" s="32" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="F36" s="32"/>
       <c r="G36" s="32"/>
@@ -60134,7 +60169,7 @@
       <c r="C37" s="32"/>
       <c r="D37" s="32"/>
       <c r="E37" s="32" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F37" s="32"/>
       <c r="G37" s="32"/>
@@ -60146,7 +60181,7 @@
       <c r="C38" s="32"/>
       <c r="D38" s="32"/>
       <c r="E38" s="32" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="F38" s="32"/>
       <c r="G38" s="32"/>
@@ -60158,7 +60193,7 @@
       <c r="C39" s="32"/>
       <c r="D39" s="32"/>
       <c r="E39" s="32" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="F39" s="32"/>
       <c r="G39" s="32"/>
@@ -60170,7 +60205,7 @@
       <c r="C40" s="32"/>
       <c r="D40" s="32"/>
       <c r="E40" s="32" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F40" s="32"/>
       <c r="G40" s="32"/>
@@ -60182,7 +60217,7 @@
       <c r="C41" s="32"/>
       <c r="D41" s="32"/>
       <c r="E41" s="32" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F41" s="32"/>
       <c r="G41" s="32"/>
@@ -60194,7 +60229,7 @@
       <c r="C42" s="32"/>
       <c r="D42" s="32"/>
       <c r="E42" s="32" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="F42" s="32"/>
       <c r="G42" s="32"/>
@@ -60206,7 +60241,7 @@
       <c r="C43" s="32"/>
       <c r="D43" s="32"/>
       <c r="E43" s="32" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="F43" s="32"/>
       <c r="G43" s="32"/>
@@ -60218,7 +60253,7 @@
       <c r="C44" s="32"/>
       <c r="D44" s="32"/>
       <c r="E44" s="32" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="F44" s="32"/>
       <c r="G44" s="32"/>
@@ -60230,7 +60265,7 @@
       <c r="C45" s="32"/>
       <c r="D45" s="32"/>
       <c r="E45" s="32" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="F45" s="32"/>
       <c r="G45" s="32"/>
@@ -60242,7 +60277,7 @@
       <c r="C46" s="32"/>
       <c r="D46" s="32"/>
       <c r="E46" s="32" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="F46" s="32"/>
       <c r="G46" s="32"/>
@@ -60254,7 +60289,7 @@
       <c r="C47" s="32"/>
       <c r="D47" s="32"/>
       <c r="E47" s="32" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="F47" s="32"/>
       <c r="G47" s="32"/>
@@ -60266,7 +60301,7 @@
       <c r="C48" s="32"/>
       <c r="D48" s="32"/>
       <c r="E48" s="32" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="F48" s="32"/>
       <c r="G48" s="32"/>
@@ -60278,7 +60313,7 @@
       <c r="C49" s="32"/>
       <c r="D49" s="32"/>
       <c r="E49" s="32" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="F49" s="32"/>
       <c r="G49" s="32"/>
@@ -60290,7 +60325,7 @@
       <c r="C50" s="32"/>
       <c r="D50" s="32"/>
       <c r="E50" s="32" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="F50" s="32"/>
       <c r="G50" s="32"/>
@@ -60310,7 +60345,7 @@
         <v>558</v>
       </c>
       <c r="E51" s="32" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F51" s="32"/>
       <c r="G51" s="32"/>
@@ -60322,7 +60357,7 @@
       <c r="C52" s="32"/>
       <c r="D52" s="32"/>
       <c r="E52" s="32" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="F52" s="32"/>
       <c r="G52" s="32"/>
@@ -60334,7 +60369,7 @@
       <c r="C53" s="32"/>
       <c r="D53" s="32"/>
       <c r="E53" s="32" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="F53" s="32"/>
       <c r="G53" s="32"/>
@@ -60346,7 +60381,7 @@
       <c r="C54" s="32"/>
       <c r="D54" s="32"/>
       <c r="E54" s="32" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F54" s="32"/>
       <c r="G54" s="32"/>
@@ -60358,7 +60393,7 @@
       <c r="C55" s="32"/>
       <c r="D55" s="32"/>
       <c r="E55" s="32" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F55" s="32"/>
       <c r="G55" s="32"/>
@@ -60370,7 +60405,7 @@
       <c r="C56" s="32"/>
       <c r="D56" s="32"/>
       <c r="E56" s="32" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="F56" s="32"/>
       <c r="G56" s="32"/>
@@ -60382,7 +60417,7 @@
       <c r="C57" s="32"/>
       <c r="D57" s="32"/>
       <c r="E57" s="32" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="F57" s="32"/>
       <c r="G57" s="32"/>
@@ -60394,7 +60429,7 @@
       <c r="C58" s="32"/>
       <c r="D58" s="32"/>
       <c r="E58" s="32" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="F58" s="32"/>
       <c r="G58" s="32"/>
@@ -60406,7 +60441,7 @@
       <c r="C59" s="32"/>
       <c r="D59" s="32"/>
       <c r="E59" s="32" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="F59" s="32"/>
       <c r="G59" s="32"/>
@@ -60418,7 +60453,7 @@
       <c r="C60" s="32"/>
       <c r="D60" s="32"/>
       <c r="E60" s="32" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="F60" s="32"/>
       <c r="G60" s="32"/>
@@ -60430,7 +60465,7 @@
       <c r="C61" s="32"/>
       <c r="D61" s="32"/>
       <c r="E61" s="32" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="F61" s="32"/>
       <c r="G61" s="32"/>
@@ -60442,7 +60477,7 @@
       <c r="C62" s="32"/>
       <c r="D62" s="32"/>
       <c r="E62" s="32" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="F62" s="32"/>
       <c r="G62" s="32"/>
@@ -60454,7 +60489,7 @@
       <c r="C63" s="32"/>
       <c r="D63" s="32"/>
       <c r="E63" s="32" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="F63" s="32"/>
       <c r="G63" s="32"/>
@@ -60466,7 +60501,7 @@
       <c r="C64" s="32"/>
       <c r="D64" s="32"/>
       <c r="E64" s="32" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="F64" s="32"/>
       <c r="G64" s="32"/>
@@ -60478,7 +60513,7 @@
       <c r="C65" s="32"/>
       <c r="D65" s="32"/>
       <c r="E65" s="32" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F65" s="32"/>
       <c r="G65" s="32"/>
@@ -60490,7 +60525,7 @@
       <c r="C66" s="32"/>
       <c r="D66" s="32"/>
       <c r="E66" s="32" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="F66" s="32"/>
       <c r="G66" s="32"/>
@@ -60502,7 +60537,7 @@
       <c r="C67" s="32"/>
       <c r="D67" s="32"/>
       <c r="E67" s="32" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="F67" s="32"/>
       <c r="G67" s="32"/>
@@ -60514,7 +60549,7 @@
       <c r="C68" s="32"/>
       <c r="D68" s="32"/>
       <c r="E68" s="32" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="F68" s="32"/>
       <c r="G68" s="32"/>
@@ -60526,7 +60561,7 @@
       <c r="C69" s="32"/>
       <c r="D69" s="32"/>
       <c r="E69" s="32" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="F69" s="32"/>
       <c r="G69" s="32"/>
@@ -60538,7 +60573,7 @@
       <c r="C70" s="32"/>
       <c r="D70" s="32"/>
       <c r="E70" s="32" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="F70" s="32"/>
       <c r="G70" s="32"/>
@@ -60550,7 +60585,7 @@
       <c r="C71" s="32"/>
       <c r="D71" s="32"/>
       <c r="E71" s="32" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="F71" s="32"/>
       <c r="G71" s="32"/>
@@ -60562,7 +60597,7 @@
       <c r="C72" s="32"/>
       <c r="D72" s="32"/>
       <c r="E72" s="32" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="F72" s="32"/>
       <c r="G72" s="32"/>
@@ -60574,7 +60609,7 @@
       <c r="C73" s="32"/>
       <c r="D73" s="32"/>
       <c r="E73" s="32" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="F73" s="32"/>
       <c r="G73" s="32"/>
@@ -60586,7 +60621,7 @@
       <c r="C74" s="32"/>
       <c r="D74" s="32"/>
       <c r="E74" s="32" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="F74" s="32"/>
       <c r="G74" s="32"/>
@@ -60598,7 +60633,7 @@
       <c r="C75" s="32"/>
       <c r="D75" s="32"/>
       <c r="E75" s="32" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="F75" s="32"/>
       <c r="G75" s="32"/>
@@ -60610,7 +60645,7 @@
       <c r="C76" s="32"/>
       <c r="D76" s="32"/>
       <c r="E76" s="32" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="F76" s="32"/>
       <c r="G76" s="32"/>
@@ -60622,7 +60657,7 @@
       <c r="C77" s="32"/>
       <c r="D77" s="32"/>
       <c r="E77" s="32" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="F77" s="32"/>
       <c r="G77" s="32"/>
@@ -60633,16 +60668,16 @@
         <v>5</v>
       </c>
       <c r="B78" s="32" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C78" s="32" t="s">
         <v>397</v>
       </c>
       <c r="D78" s="32" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E78" s="132" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="F78" s="32"/>
       <c r="G78" s="32"/>
@@ -60654,7 +60689,7 @@
       <c r="C79" s="32"/>
       <c r="D79" s="32"/>
       <c r="E79" s="32" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="F79" s="32"/>
       <c r="G79" s="32"/>
@@ -60666,7 +60701,7 @@
       <c r="C80" s="32"/>
       <c r="D80" s="32"/>
       <c r="E80" s="32" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="F80" s="32"/>
       <c r="G80" s="32"/>
@@ -60678,7 +60713,7 @@
       <c r="C81" s="32"/>
       <c r="D81" s="32"/>
       <c r="E81" s="32" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="F81" s="32"/>
       <c r="G81" s="32"/>
@@ -60695,10 +60730,10 @@
         <v>397</v>
       </c>
       <c r="D82" s="32" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E82" s="32" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="F82" s="32"/>
       <c r="G82" s="32"/>
@@ -60710,7 +60745,7 @@
       <c r="C83" s="32"/>
       <c r="D83" s="32"/>
       <c r="E83" s="32" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F83" s="32"/>
       <c r="G83" s="32"/>
@@ -60722,7 +60757,7 @@
       <c r="C84" s="32"/>
       <c r="D84" s="32"/>
       <c r="E84" s="32" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="F84" s="32"/>
       <c r="G84" s="32"/>
@@ -60734,7 +60769,7 @@
       <c r="C85" s="32"/>
       <c r="D85" s="32"/>
       <c r="E85" s="32" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="F85" s="32"/>
       <c r="G85" s="32"/>
@@ -60745,16 +60780,16 @@
         <v>5</v>
       </c>
       <c r="B86" s="32" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C86" s="32" t="s">
         <v>397</v>
       </c>
       <c r="D86" s="32" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E86" s="32" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="F86" s="32"/>
       <c r="G86" s="32"/>
@@ -60766,7 +60801,7 @@
       <c r="C87" s="32"/>
       <c r="D87" s="32"/>
       <c r="E87" s="32" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="F87" s="32"/>
       <c r="G87" s="32"/>
@@ -60778,7 +60813,7 @@
       <c r="C88" s="32"/>
       <c r="D88" s="32"/>
       <c r="E88" s="32" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F88" s="32"/>
       <c r="G88" s="32"/>
@@ -60790,7 +60825,7 @@
       <c r="C89" s="32"/>
       <c r="D89" s="32"/>
       <c r="E89" s="32" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="F89" s="32"/>
       <c r="G89" s="32"/>
@@ -60802,7 +60837,7 @@
       <c r="C90" s="32"/>
       <c r="D90" s="32"/>
       <c r="E90" s="32" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F90" s="32"/>
       <c r="G90" s="32"/>
@@ -60814,7 +60849,7 @@
       <c r="C91" s="32"/>
       <c r="D91" s="32"/>
       <c r="E91" s="32" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F91" s="32"/>
       <c r="G91" s="32"/>
@@ -60826,7 +60861,7 @@
       <c r="C92" s="32"/>
       <c r="D92" s="32"/>
       <c r="E92" s="32" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F92" s="32"/>
       <c r="G92" s="32"/>
@@ -60838,7 +60873,7 @@
       <c r="C93" s="32"/>
       <c r="D93" s="32"/>
       <c r="E93" s="32" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="F93" s="32"/>
       <c r="G93" s="32"/>
@@ -60850,7 +60885,7 @@
       <c r="C94" s="32"/>
       <c r="D94" s="32"/>
       <c r="E94" s="32" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F94" s="102"/>
       <c r="G94" s="32"/>
@@ -60867,10 +60902,10 @@
         <v>397</v>
       </c>
       <c r="D95" s="32" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E95" s="32" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="F95" s="32"/>
       <c r="G95" s="32"/>
@@ -60882,7 +60917,7 @@
       <c r="C96" s="32"/>
       <c r="D96" s="32"/>
       <c r="E96" s="32" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="F96" s="32"/>
       <c r="G96" s="32"/>
@@ -60894,7 +60929,7 @@
       <c r="C97" s="32"/>
       <c r="D97" s="32"/>
       <c r="E97" s="32" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="F97" s="32"/>
       <c r="G97" s="32"/>
@@ -60906,7 +60941,7 @@
       <c r="C98" s="32"/>
       <c r="D98" s="32"/>
       <c r="E98" s="29" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="F98" s="32"/>
       <c r="G98" s="32"/>
@@ -60918,7 +60953,7 @@
       <c r="C99" s="32"/>
       <c r="D99" s="32"/>
       <c r="E99" s="29" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="F99" s="32"/>
       <c r="G99" s="32"/>
@@ -60930,7 +60965,7 @@
       <c r="C100" s="32"/>
       <c r="D100" s="32"/>
       <c r="E100" s="29" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="F100" s="32"/>
       <c r="G100" s="32"/>
@@ -60942,7 +60977,7 @@
       <c r="C101" s="32"/>
       <c r="D101" s="32"/>
       <c r="E101" s="29" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="F101" s="32"/>
       <c r="G101" s="32"/>
@@ -60954,7 +60989,7 @@
       <c r="C102" s="32"/>
       <c r="D102" s="32"/>
       <c r="E102" s="29" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F102" s="32"/>
       <c r="G102" s="32"/>
@@ -60966,7 +61001,7 @@
       <c r="C103" s="32"/>
       <c r="D103" s="32"/>
       <c r="E103" s="29" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="F103" s="32"/>
       <c r="G103" s="32"/>
@@ -60978,7 +61013,7 @@
       <c r="C104" s="32"/>
       <c r="D104" s="32"/>
       <c r="E104" s="29" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="F104" s="32"/>
       <c r="G104" s="32"/>
@@ -60990,7 +61025,7 @@
       <c r="C105" s="32"/>
       <c r="D105" s="32"/>
       <c r="E105" s="29" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="F105" s="32"/>
       <c r="G105" s="32"/>
@@ -61002,7 +61037,7 @@
       <c r="C106" s="32"/>
       <c r="D106" s="32"/>
       <c r="E106" s="29" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="F106" s="32"/>
       <c r="G106" s="32"/>
@@ -61014,7 +61049,7 @@
       <c r="C107" s="32"/>
       <c r="D107" s="32"/>
       <c r="E107" s="29" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="F107" s="32"/>
       <c r="G107" s="32"/>
@@ -61026,7 +61061,7 @@
       <c r="C108" s="32"/>
       <c r="D108" s="32"/>
       <c r="E108" s="29" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="F108" s="32"/>
       <c r="G108" s="32"/>
@@ -61038,7 +61073,7 @@
       <c r="C109" s="32"/>
       <c r="D109" s="32"/>
       <c r="E109" s="29" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="F109" s="32"/>
       <c r="G109" s="32"/>
@@ -61050,7 +61085,7 @@
       <c r="C110" s="32"/>
       <c r="D110" s="32"/>
       <c r="E110" s="29" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="F110" s="32"/>
       <c r="G110" s="32"/>
@@ -61062,7 +61097,7 @@
       <c r="C111" s="32"/>
       <c r="D111" s="32"/>
       <c r="E111" s="29" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="F111" s="32"/>
       <c r="G111" s="32"/>
@@ -61074,7 +61109,7 @@
       <c r="C112" s="32"/>
       <c r="D112" s="32"/>
       <c r="E112" s="29" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="F112" s="32"/>
       <c r="G112" s="32"/>
@@ -61086,7 +61121,7 @@
       <c r="C113" s="32"/>
       <c r="D113" s="32"/>
       <c r="E113" s="29" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="F113" s="32"/>
       <c r="G113" s="32"/>
@@ -61098,7 +61133,7 @@
       <c r="C114" s="32"/>
       <c r="D114" s="32"/>
       <c r="E114" s="29" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F114" s="32"/>
       <c r="G114" s="32"/>
@@ -61110,7 +61145,7 @@
       <c r="C115" s="32"/>
       <c r="D115" s="32"/>
       <c r="E115" s="29" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="F115" s="32"/>
       <c r="G115" s="32"/>
@@ -61122,7 +61157,7 @@
       <c r="C116" s="32"/>
       <c r="D116" s="32"/>
       <c r="E116" s="29" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="F116" s="32"/>
       <c r="G116" s="32"/>
@@ -61134,7 +61169,7 @@
       <c r="C117" s="32"/>
       <c r="D117" s="32"/>
       <c r="E117" s="29" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="F117" s="32"/>
       <c r="G117" s="32"/>
@@ -61146,7 +61181,7 @@
       <c r="C118" s="32"/>
       <c r="D118" s="32"/>
       <c r="E118" s="29" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="F118" s="32"/>
       <c r="G118" s="32"/>
@@ -61158,7 +61193,7 @@
       <c r="C119" s="32"/>
       <c r="D119" s="32"/>
       <c r="E119" s="29" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="F119" s="32"/>
       <c r="G119" s="32"/>
@@ -61170,7 +61205,7 @@
       <c r="C120" s="32"/>
       <c r="D120" s="32"/>
       <c r="E120" s="29" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="F120" s="32"/>
       <c r="G120" s="32"/>
@@ -61182,7 +61217,7 @@
       <c r="C121" s="32"/>
       <c r="D121" s="32"/>
       <c r="E121" s="29" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="F121" s="32"/>
       <c r="G121" s="32"/>
@@ -61194,7 +61229,7 @@
       <c r="C122" s="32"/>
       <c r="D122" s="32"/>
       <c r="E122" s="29" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="F122" s="32"/>
       <c r="G122" s="32"/>
@@ -61206,7 +61241,7 @@
       <c r="C123" s="32"/>
       <c r="D123" s="32"/>
       <c r="E123" s="29" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="F123" s="32"/>
       <c r="G123" s="32"/>
@@ -61218,7 +61253,7 @@
       <c r="C124" s="32"/>
       <c r="D124" s="32"/>
       <c r="E124" s="29" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="F124" s="32"/>
       <c r="G124" s="32"/>
@@ -61230,7 +61265,7 @@
       <c r="C125" s="32"/>
       <c r="D125" s="32"/>
       <c r="E125" s="29" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="F125" s="32"/>
       <c r="G125" s="32"/>
@@ -61242,7 +61277,7 @@
       <c r="C126" s="32"/>
       <c r="D126" s="32"/>
       <c r="E126" s="29" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="F126" s="32"/>
       <c r="G126" s="32"/>
@@ -61254,7 +61289,7 @@
       <c r="C127" s="32"/>
       <c r="D127" s="32"/>
       <c r="E127" s="29" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="F127" s="32"/>
       <c r="G127" s="32"/>
@@ -61266,7 +61301,7 @@
       <c r="C128" s="32"/>
       <c r="D128" s="32"/>
       <c r="E128" s="29" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="F128" s="32"/>
       <c r="G128" s="32"/>
@@ -61278,7 +61313,7 @@
       <c r="C129" s="32"/>
       <c r="D129" s="32"/>
       <c r="E129" s="29" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="F129" s="32"/>
       <c r="G129" s="32"/>
@@ -61290,7 +61325,7 @@
       <c r="C130" s="32"/>
       <c r="D130" s="32"/>
       <c r="E130" s="29" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="F130" s="32"/>
       <c r="G130" s="32"/>
@@ -61302,7 +61337,7 @@
       <c r="C131" s="32"/>
       <c r="D131" s="32"/>
       <c r="E131" s="32" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="F131" s="32"/>
       <c r="G131" s="32"/>
@@ -61314,7 +61349,7 @@
       <c r="C132" s="32"/>
       <c r="D132" s="32"/>
       <c r="E132" s="32" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F132" s="32"/>
       <c r="G132" s="32"/>
@@ -61326,7 +61361,7 @@
       <c r="C133" s="32"/>
       <c r="D133" s="32"/>
       <c r="E133" s="32" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="F133" s="32"/>
       <c r="G133" s="32"/>
@@ -61338,7 +61373,7 @@
       <c r="C134" s="32"/>
       <c r="D134" s="32"/>
       <c r="E134" s="32" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="F134" s="32"/>
       <c r="G134" s="32"/>
@@ -61350,7 +61385,7 @@
       <c r="C135" s="32"/>
       <c r="D135" s="32"/>
       <c r="E135" s="32" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="F135" s="32"/>
       <c r="G135" s="32"/>
@@ -61362,7 +61397,7 @@
       <c r="C136" s="32"/>
       <c r="D136" s="32"/>
       <c r="E136" s="32" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="F136" s="32"/>
       <c r="G136" s="32"/>
@@ -61382,7 +61417,7 @@
         <v>561</v>
       </c>
       <c r="E137" s="76" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="F137" s="32"/>
       <c r="G137" s="32"/>
@@ -61394,7 +61429,7 @@
       <c r="C138" s="32"/>
       <c r="D138" s="32"/>
       <c r="E138" s="76" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F138" s="32"/>
       <c r="G138" s="32"/>
@@ -61406,7 +61441,7 @@
       <c r="C139" s="32"/>
       <c r="D139" s="32"/>
       <c r="E139" s="32" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="F139" s="32"/>
       <c r="G139" s="32"/>
@@ -61418,7 +61453,7 @@
       <c r="C140" s="32"/>
       <c r="D140" s="32"/>
       <c r="E140" s="32" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="F140" s="32"/>
       <c r="G140" s="32"/>
@@ -61430,7 +61465,7 @@
       <c r="C141" s="32"/>
       <c r="D141" s="32"/>
       <c r="E141" s="32" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="F141" s="32"/>
       <c r="G141" s="32"/>
@@ -61442,7 +61477,7 @@
       <c r="C142" s="32"/>
       <c r="D142" s="32"/>
       <c r="E142" s="32" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="F142" s="32"/>
       <c r="G142" s="32"/>
@@ -61454,7 +61489,7 @@
       <c r="C143" s="32"/>
       <c r="D143" s="32"/>
       <c r="E143" s="32" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="F143" s="32"/>
       <c r="G143" s="32"/>
@@ -61466,7 +61501,7 @@
       <c r="C144" s="32"/>
       <c r="D144" s="32"/>
       <c r="E144" s="32" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="F144" s="32"/>
       <c r="G144" s="32"/>
@@ -61478,7 +61513,7 @@
       <c r="C145" s="32"/>
       <c r="D145" s="32"/>
       <c r="E145" s="32" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="F145" s="32"/>
       <c r="G145" s="32"/>
@@ -61490,7 +61525,7 @@
       <c r="C146" s="32"/>
       <c r="D146" s="32"/>
       <c r="E146" s="32" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F146" s="32"/>
       <c r="G146" s="32"/>
@@ -61502,7 +61537,7 @@
       <c r="C147" s="32"/>
       <c r="D147" s="32"/>
       <c r="E147" s="32" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="F147" s="32"/>
       <c r="G147" s="32"/>
@@ -61514,7 +61549,7 @@
       <c r="C148" s="32"/>
       <c r="D148" s="32"/>
       <c r="E148" s="32" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="F148" s="32"/>
       <c r="G148" s="32"/>
@@ -61526,7 +61561,7 @@
       <c r="C149" s="32"/>
       <c r="D149" s="32"/>
       <c r="E149" s="32" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="F149" s="32"/>
       <c r="G149" s="32"/>
@@ -61538,7 +61573,7 @@
       <c r="C150" s="32"/>
       <c r="D150" s="32"/>
       <c r="E150" s="32" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="F150" s="32"/>
       <c r="G150" s="32"/>
@@ -61550,7 +61585,7 @@
       <c r="C151" s="32"/>
       <c r="D151" s="32"/>
       <c r="E151" s="32" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="F151" s="32"/>
       <c r="G151" s="32"/>
@@ -61562,7 +61597,7 @@
       <c r="C152" s="32"/>
       <c r="D152" s="32"/>
       <c r="E152" s="32" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="F152" s="32"/>
       <c r="G152" s="32"/>
@@ -61574,7 +61609,7 @@
       <c r="C153" s="32"/>
       <c r="D153" s="32"/>
       <c r="E153" s="32" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="F153" s="32"/>
       <c r="G153" s="32"/>
@@ -61586,7 +61621,7 @@
       <c r="C154" s="32"/>
       <c r="D154" s="32"/>
       <c r="E154" s="32" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="F154" s="32"/>
       <c r="G154" s="32"/>
@@ -61598,7 +61633,7 @@
       <c r="C155" s="32"/>
       <c r="D155" s="32"/>
       <c r="E155" s="32" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="F155" s="32"/>
       <c r="G155" s="32"/>
@@ -61610,7 +61645,7 @@
       <c r="C156" s="32"/>
       <c r="D156" s="32"/>
       <c r="E156" s="32" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="F156" s="32"/>
       <c r="G156" s="32"/>
@@ -61630,7 +61665,7 @@
         <v>563</v>
       </c>
       <c r="E157" s="32" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="F157" s="32"/>
       <c r="G157" s="32"/>
@@ -61642,7 +61677,7 @@
       <c r="C158" s="32"/>
       <c r="D158" s="32"/>
       <c r="E158" s="32" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="F158" s="32"/>
       <c r="G158" s="32"/>
@@ -61654,7 +61689,7 @@
       <c r="C159" s="32"/>
       <c r="D159" s="32"/>
       <c r="E159" s="32" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="F159" s="32"/>
       <c r="G159" s="32"/>
@@ -61666,7 +61701,7 @@
       <c r="C160" s="32"/>
       <c r="D160" s="32"/>
       <c r="E160" s="32" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="F160" s="32"/>
       <c r="G160" s="32"/>
@@ -61678,7 +61713,7 @@
       <c r="C161" s="32"/>
       <c r="D161" s="32"/>
       <c r="E161" s="32" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="F161" s="32"/>
       <c r="G161" s="32"/>
@@ -61690,7 +61725,7 @@
       <c r="C162" s="32"/>
       <c r="D162" s="32"/>
       <c r="E162" s="32" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="F162" s="32"/>
       <c r="G162" s="32"/>
@@ -61702,7 +61737,7 @@
       <c r="C163" s="32"/>
       <c r="D163" s="32"/>
       <c r="E163" s="32" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="F163" s="32"/>
       <c r="G163" s="32"/>
@@ -61714,7 +61749,7 @@
       <c r="C164" s="32"/>
       <c r="D164" s="32"/>
       <c r="E164" s="32" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="F164" s="32"/>
       <c r="G164" s="32"/>
@@ -61726,7 +61761,7 @@
       <c r="C165" s="32"/>
       <c r="D165" s="32"/>
       <c r="E165" s="32" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="F165" s="32"/>
       <c r="G165" s="32"/>
@@ -61738,7 +61773,7 @@
       <c r="C166" s="32"/>
       <c r="D166" s="32"/>
       <c r="E166" s="32" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="F166" s="32"/>
       <c r="G166" s="32"/>
@@ -61750,7 +61785,7 @@
       <c r="C167" s="32"/>
       <c r="D167" s="32"/>
       <c r="E167" s="32" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="F167" s="32"/>
       <c r="G167" s="32"/>
@@ -61762,7 +61797,7 @@
       <c r="C168" s="32"/>
       <c r="D168" s="32"/>
       <c r="E168" s="32" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="F168" s="32"/>
       <c r="G168" s="32"/>
@@ -61774,7 +61809,7 @@
       <c r="C169" s="32"/>
       <c r="D169" s="32"/>
       <c r="E169" s="32" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="F169" s="32"/>
       <c r="G169" s="32"/>
@@ -61786,7 +61821,7 @@
       <c r="C170" s="32"/>
       <c r="D170" s="32"/>
       <c r="E170" s="32" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="F170" s="32"/>
       <c r="G170" s="32"/>
@@ -61798,7 +61833,7 @@
       <c r="C171" s="32"/>
       <c r="D171" s="32"/>
       <c r="E171" s="32" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="F171" s="32"/>
       <c r="G171" s="32"/>
@@ -61810,7 +61845,7 @@
       <c r="C172" s="32"/>
       <c r="D172" s="32"/>
       <c r="E172" s="32" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="F172" s="32"/>
       <c r="G172" s="32"/>
@@ -61822,7 +61857,7 @@
       <c r="C173" s="32"/>
       <c r="D173" s="32"/>
       <c r="E173" s="32" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="F173" s="32"/>
       <c r="G173" s="32"/>
@@ -61834,7 +61869,7 @@
       <c r="C174" s="32"/>
       <c r="D174" s="32"/>
       <c r="E174" s="32" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="F174" s="32"/>
       <c r="G174" s="32"/>
@@ -61846,7 +61881,7 @@
       <c r="C175" s="32"/>
       <c r="D175" s="32"/>
       <c r="E175" s="32" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="F175" s="32"/>
       <c r="G175" s="32"/>
@@ -61858,7 +61893,7 @@
       <c r="C176" s="32"/>
       <c r="D176" s="32"/>
       <c r="E176" s="32" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="F176" s="32"/>
       <c r="G176" s="32"/>
@@ -61870,7 +61905,7 @@
       <c r="C177" s="32"/>
       <c r="D177" s="32"/>
       <c r="E177" s="32" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="F177" s="32"/>
       <c r="G177" s="32"/>
@@ -61882,7 +61917,7 @@
       <c r="C178" s="32"/>
       <c r="D178" s="32"/>
       <c r="E178" s="32" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="F178" s="32"/>
       <c r="G178" s="32"/>
@@ -61894,7 +61929,7 @@
       <c r="C179" s="32"/>
       <c r="D179" s="32"/>
       <c r="E179" s="32" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="F179" s="32"/>
       <c r="G179" s="32"/>
@@ -61906,7 +61941,7 @@
       <c r="C180" s="32"/>
       <c r="D180" s="32"/>
       <c r="E180" s="32" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="F180" s="32"/>
       <c r="G180" s="32"/>
@@ -61918,7 +61953,7 @@
       <c r="C181" s="32"/>
       <c r="D181" s="32"/>
       <c r="E181" s="32" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="F181" s="32"/>
       <c r="G181" s="32"/>
@@ -61930,7 +61965,7 @@
       <c r="C182" s="32"/>
       <c r="D182" s="32"/>
       <c r="E182" s="32" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="F182" s="32"/>
       <c r="G182" s="32"/>
@@ -61942,7 +61977,7 @@
       <c r="C183" s="32"/>
       <c r="D183" s="32"/>
       <c r="E183" s="32" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="F183" s="32"/>
       <c r="G183" s="32"/>
@@ -61954,7 +61989,7 @@
       <c r="C184" s="32"/>
       <c r="D184" s="32"/>
       <c r="E184" s="32" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="F184" s="32"/>
       <c r="G184" s="32"/>
@@ -61966,7 +62001,7 @@
       <c r="C185" s="32"/>
       <c r="D185" s="32"/>
       <c r="E185" s="32" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F185" s="32"/>
       <c r="G185" s="32"/>
@@ -61978,7 +62013,7 @@
       <c r="C186" s="32"/>
       <c r="D186" s="32"/>
       <c r="E186" s="32" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="F186" s="32"/>
       <c r="G186" s="32"/>
@@ -61990,7 +62025,7 @@
       <c r="C187" s="32"/>
       <c r="D187" s="32"/>
       <c r="E187" s="32" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="F187" s="32"/>
       <c r="G187" s="32"/>
@@ -62002,7 +62037,7 @@
       <c r="C188" s="32"/>
       <c r="D188" s="32"/>
       <c r="E188" s="32" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="F188" s="32"/>
       <c r="G188" s="32"/>
@@ -62013,16 +62048,16 @@
         <v>5</v>
       </c>
       <c r="B189" s="32" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C189" s="32" t="s">
         <v>397</v>
       </c>
       <c r="D189" s="32" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E189" s="97" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F189" s="32"/>
       <c r="G189" s="32"/>
@@ -62034,7 +62069,7 @@
       <c r="C190" s="32"/>
       <c r="D190" s="32"/>
       <c r="E190" s="32" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F190" s="32"/>
       <c r="G190" s="32"/>
@@ -62046,7 +62081,7 @@
       <c r="C191" s="32"/>
       <c r="D191" s="32"/>
       <c r="E191" s="32" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="F191" s="32"/>
       <c r="G191" s="32"/>
@@ -62058,7 +62093,7 @@
       <c r="C192" s="32"/>
       <c r="D192" s="32"/>
       <c r="E192" s="32" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="F192" s="32"/>
       <c r="G192" s="32"/>
@@ -62078,7 +62113,7 @@
         <v>565</v>
       </c>
       <c r="E193" s="32" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="F193" s="32"/>
       <c r="G193" s="32"/>
@@ -62090,7 +62125,7 @@
       <c r="C194" s="32"/>
       <c r="D194" s="32"/>
       <c r="E194" s="32" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="F194" s="32"/>
       <c r="G194" s="32"/>
@@ -62102,7 +62137,7 @@
       <c r="C195" s="32"/>
       <c r="D195" s="32"/>
       <c r="E195" s="32" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="F195" s="32"/>
       <c r="G195" s="32"/>
@@ -62114,7 +62149,7 @@
       <c r="C196" s="32"/>
       <c r="D196" s="32"/>
       <c r="E196" s="32" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="F196" s="32"/>
       <c r="G196" s="32"/>
@@ -62126,7 +62161,7 @@
       <c r="C197" s="32"/>
       <c r="D197" s="32"/>
       <c r="E197" s="32" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F197" s="32"/>
       <c r="G197" s="32"/>
@@ -62138,7 +62173,7 @@
       <c r="C198" s="32"/>
       <c r="D198" s="32"/>
       <c r="E198" s="32" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F198" s="32"/>
       <c r="G198" s="32"/>
@@ -62150,7 +62185,7 @@
       <c r="C199" s="32"/>
       <c r="D199" s="32"/>
       <c r="E199" s="32" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="F199" s="32"/>
       <c r="G199" s="32"/>
@@ -62162,7 +62197,7 @@
       <c r="C200" s="32"/>
       <c r="D200" s="32"/>
       <c r="E200" s="32" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="F200" s="32"/>
       <c r="G200" s="32"/>
@@ -62174,7 +62209,7 @@
       <c r="C201" s="32"/>
       <c r="D201" s="32"/>
       <c r="E201" s="32" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="F201" s="32"/>
       <c r="G201" s="32"/>
@@ -62186,7 +62221,7 @@
       <c r="C202" s="32"/>
       <c r="D202" s="32"/>
       <c r="E202" s="32" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="F202" s="32"/>
       <c r="G202" s="32"/>
@@ -62198,7 +62233,7 @@
       <c r="C203" s="32"/>
       <c r="D203" s="32"/>
       <c r="E203" s="32" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="F203" s="32"/>
       <c r="G203" s="32"/>
@@ -62210,7 +62245,7 @@
       <c r="C204" s="32"/>
       <c r="D204" s="32"/>
       <c r="E204" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="F204" s="32"/>
       <c r="G204" s="32"/>
@@ -62222,7 +62257,7 @@
       <c r="C205" s="32"/>
       <c r="D205" s="32"/>
       <c r="E205" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="F205" s="32"/>
       <c r="G205" s="32"/>
@@ -62234,7 +62269,7 @@
       <c r="C206" s="32"/>
       <c r="D206" s="32"/>
       <c r="E206" s="32" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="F206" s="32"/>
       <c r="G206" s="32"/>
@@ -62246,7 +62281,7 @@
       <c r="C207" s="32"/>
       <c r="D207" s="32"/>
       <c r="E207" s="32" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="F207" s="32"/>
       <c r="G207" s="32"/>
@@ -62258,7 +62293,7 @@
       <c r="C208" s="32"/>
       <c r="D208" s="32"/>
       <c r="E208" s="32" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="F208" s="32"/>
       <c r="G208" s="32"/>
@@ -62270,7 +62305,7 @@
       <c r="C209" s="32"/>
       <c r="D209" s="32"/>
       <c r="E209" s="32" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="F209" s="32"/>
       <c r="G209" s="32"/>
@@ -62282,7 +62317,7 @@
       <c r="C210" s="32"/>
       <c r="D210" s="32"/>
       <c r="E210" s="32" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="F210" s="32"/>
       <c r="G210" s="32"/>
@@ -62294,7 +62329,7 @@
       <c r="C211" s="32"/>
       <c r="D211" s="32"/>
       <c r="E211" s="32" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="F211" s="32"/>
       <c r="G211" s="32"/>
@@ -62306,7 +62341,7 @@
       <c r="C212" s="32"/>
       <c r="D212" s="32"/>
       <c r="E212" s="32" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="F212" s="32"/>
       <c r="G212" s="32"/>
@@ -62318,7 +62353,7 @@
       <c r="C213" s="32"/>
       <c r="D213" s="32"/>
       <c r="E213" s="32" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="F213" s="32"/>
       <c r="G213" s="32"/>
@@ -62330,7 +62365,7 @@
       <c r="C214" s="32"/>
       <c r="D214" s="32"/>
       <c r="E214" s="32" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="F214" s="32"/>
       <c r="G214" s="32"/>
@@ -62342,7 +62377,7 @@
       <c r="C215" s="32"/>
       <c r="D215" s="32"/>
       <c r="E215" s="32" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="F215" s="32"/>
       <c r="G215" s="32"/>
@@ -62354,7 +62389,7 @@
       <c r="C216" s="32"/>
       <c r="D216" s="32"/>
       <c r="E216" s="32" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="F216" s="32"/>
       <c r="G216" s="32"/>
@@ -62366,7 +62401,7 @@
       <c r="C217" s="32"/>
       <c r="D217" s="32"/>
       <c r="E217" s="32" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="F217" s="32"/>
       <c r="G217" s="32"/>
@@ -62378,7 +62413,7 @@
       <c r="C218" s="32"/>
       <c r="D218" s="32"/>
       <c r="E218" s="32" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="F218" s="32"/>
       <c r="G218" s="32"/>
@@ -62390,7 +62425,7 @@
       <c r="C219" s="32"/>
       <c r="D219" s="32"/>
       <c r="E219" s="32" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="F219" s="32"/>
       <c r="G219" s="32"/>
@@ -62402,7 +62437,7 @@
       <c r="C220" s="32"/>
       <c r="D220" s="32"/>
       <c r="E220" s="32" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="F220" s="32"/>
       <c r="G220" s="32"/>
@@ -62414,7 +62449,7 @@
       <c r="C221" s="32"/>
       <c r="D221" s="32"/>
       <c r="E221" s="32" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="F221" s="32"/>
       <c r="G221" s="32"/>
@@ -62426,7 +62461,7 @@
       <c r="C222" s="32"/>
       <c r="D222" s="32"/>
       <c r="E222" s="32" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="F222" s="32"/>
       <c r="G222" s="32"/>
@@ -62438,7 +62473,7 @@
       <c r="C223" s="32"/>
       <c r="D223" s="32"/>
       <c r="E223" s="32" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F223" s="32"/>
       <c r="G223" s="32"/>
@@ -62450,7 +62485,7 @@
       <c r="C224" s="32"/>
       <c r="D224" s="32"/>
       <c r="E224" s="32" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="F224" s="32"/>
       <c r="G224" s="32"/>
@@ -62462,7 +62497,7 @@
       <c r="C225" s="32"/>
       <c r="D225" s="32"/>
       <c r="E225" s="32" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="F225" s="32"/>
       <c r="G225" s="32"/>
@@ -62474,7 +62509,7 @@
       <c r="C226" s="32"/>
       <c r="D226" s="32"/>
       <c r="E226" s="32" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="F226" s="32"/>
       <c r="G226" s="32"/>
@@ -62486,7 +62521,7 @@
       <c r="C227" s="32"/>
       <c r="D227" s="32"/>
       <c r="E227" s="32" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="F227" s="32"/>
       <c r="G227" s="32"/>
@@ -62498,7 +62533,7 @@
       <c r="C228" s="32"/>
       <c r="D228" s="32"/>
       <c r="E228" s="32" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="F228" s="32"/>
       <c r="G228" s="32"/>
@@ -62510,7 +62545,7 @@
       <c r="C229" s="32"/>
       <c r="D229" s="32"/>
       <c r="E229" s="32" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="F229" s="32"/>
       <c r="G229" s="32"/>
@@ -62522,7 +62557,7 @@
       <c r="C230" s="32"/>
       <c r="D230" s="32"/>
       <c r="E230" s="32" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="F230" s="32"/>
       <c r="G230" s="32"/>
@@ -62534,7 +62569,7 @@
       <c r="C231" s="32"/>
       <c r="D231" s="32"/>
       <c r="E231" s="32" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="F231" s="32"/>
       <c r="G231" s="32"/>
@@ -62546,7 +62581,7 @@
       <c r="C232" s="32"/>
       <c r="D232" s="32"/>
       <c r="E232" s="32" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="F232" s="32"/>
       <c r="G232" s="32"/>
@@ -62558,7 +62593,7 @@
       <c r="C233" s="32"/>
       <c r="D233" s="32"/>
       <c r="E233" s="32" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="F233" s="32"/>
       <c r="G233" s="32"/>
@@ -62570,7 +62605,7 @@
       <c r="C234" s="32"/>
       <c r="D234" s="32"/>
       <c r="E234" s="32" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="F234" s="32"/>
       <c r="G234" s="32"/>
@@ -62582,7 +62617,7 @@
       <c r="C235" s="32"/>
       <c r="D235" s="32"/>
       <c r="E235" s="32" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="F235" s="32"/>
       <c r="G235" s="32"/>
@@ -62594,7 +62629,7 @@
       <c r="C236" s="32"/>
       <c r="D236" s="32"/>
       <c r="E236" s="32" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="F236" s="32"/>
       <c r="G236" s="32"/>
@@ -62606,7 +62641,7 @@
       <c r="C237" s="32"/>
       <c r="D237" s="32"/>
       <c r="E237" s="32" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="F237" s="32"/>
       <c r="G237" s="32"/>
@@ -62618,7 +62653,7 @@
       <c r="C238" s="32"/>
       <c r="D238" s="32"/>
       <c r="E238" s="32" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="F238" s="32"/>
       <c r="G238" s="32"/>
@@ -62630,7 +62665,7 @@
       <c r="C239" s="32"/>
       <c r="D239" s="32"/>
       <c r="E239" s="32" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="F239" s="32"/>
       <c r="G239" s="32"/>
@@ -62642,7 +62677,7 @@
       <c r="C240" s="32"/>
       <c r="D240" s="32"/>
       <c r="E240" s="32" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="F240" s="32"/>
       <c r="G240" s="32"/>
@@ -62650,7 +62685,7 @@
     </row>
     <row r="241" spans="1:9" s="33" customFormat="1" ht="16">
       <c r="E241" s="32" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="I241" s="75"/>
     </row>
@@ -62660,7 +62695,7 @@
       <c r="C242" s="33"/>
       <c r="D242" s="33"/>
       <c r="E242" s="32" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="F242" s="33"/>
       <c r="G242" s="33"/>
@@ -62672,7 +62707,7 @@
       <c r="C243" s="33"/>
       <c r="D243" s="33"/>
       <c r="E243" s="32" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="F243" s="33"/>
       <c r="G243" s="33"/>
@@ -62684,7 +62719,7 @@
       <c r="C244" s="33"/>
       <c r="D244" s="33"/>
       <c r="E244" s="32" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="F244" s="33"/>
       <c r="G244" s="33"/>
@@ -62695,16 +62730,16 @@
         <v>5</v>
       </c>
       <c r="B245" s="32" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C245" s="32" t="s">
         <v>397</v>
       </c>
       <c r="D245" s="32" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E245" s="32" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="F245" s="33"/>
       <c r="G245" s="33"/>
@@ -62716,7 +62751,7 @@
       <c r="C246" s="33"/>
       <c r="D246" s="33"/>
       <c r="E246" s="32" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="F246" s="33"/>
       <c r="G246" s="33"/>
@@ -62728,7 +62763,7 @@
       <c r="C247" s="33"/>
       <c r="D247" s="33"/>
       <c r="E247" s="32" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="F247" s="33"/>
       <c r="G247" s="33"/>
@@ -62740,7 +62775,7 @@
       <c r="C248" s="33"/>
       <c r="D248" s="33"/>
       <c r="E248" s="32" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="F248" s="33"/>
       <c r="G248" s="33"/>
@@ -62752,7 +62787,7 @@
       <c r="C249" s="33"/>
       <c r="D249" s="33"/>
       <c r="E249" s="32" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="F249" s="33"/>
       <c r="G249" s="33"/>
@@ -62764,7 +62799,7 @@
       <c r="C250" s="33"/>
       <c r="D250" s="33"/>
       <c r="E250" s="32" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="F250" s="33"/>
       <c r="G250" s="33"/>
@@ -62776,7 +62811,7 @@
       <c r="C251" s="33"/>
       <c r="D251" s="33"/>
       <c r="E251" s="32" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="F251" s="33"/>
       <c r="G251" s="33"/>
@@ -62788,7 +62823,7 @@
       <c r="C252" s="33"/>
       <c r="D252" s="33"/>
       <c r="E252" s="32" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="F252" s="33"/>
       <c r="G252" s="33"/>
@@ -62800,7 +62835,7 @@
       <c r="C253" s="33"/>
       <c r="D253" s="33"/>
       <c r="E253" s="32" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="F253" s="33"/>
       <c r="G253" s="33"/>
@@ -62812,7 +62847,7 @@
       <c r="C254" s="33"/>
       <c r="D254" s="33"/>
       <c r="E254" s="32" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="F254" s="33"/>
       <c r="G254" s="33"/>
@@ -62824,7 +62859,7 @@
       <c r="C255" s="33"/>
       <c r="D255" s="33"/>
       <c r="E255" s="32" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="F255" s="33"/>
       <c r="G255" s="33"/>
@@ -62836,7 +62871,7 @@
       <c r="C256" s="33"/>
       <c r="D256" s="33"/>
       <c r="E256" s="32" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="F256" s="33"/>
       <c r="G256" s="33"/>
@@ -62848,7 +62883,7 @@
       <c r="C257" s="33"/>
       <c r="D257" s="33"/>
       <c r="E257" s="32" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="F257" s="33"/>
       <c r="G257" s="33"/>
@@ -62860,7 +62895,7 @@
       <c r="C258" s="33"/>
       <c r="D258" s="33"/>
       <c r="E258" s="32" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="F258" s="33"/>
       <c r="G258" s="33"/>
@@ -62872,7 +62907,7 @@
       <c r="C259" s="33"/>
       <c r="D259" s="33"/>
       <c r="E259" s="32" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="F259" s="33"/>
       <c r="G259" s="33"/>
@@ -62884,7 +62919,7 @@
       <c r="C260" s="33"/>
       <c r="D260" s="33"/>
       <c r="E260" s="32" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="F260" s="33"/>
       <c r="G260" s="33"/>
@@ -62896,7 +62931,7 @@
       <c r="C261" s="33"/>
       <c r="D261" s="33"/>
       <c r="E261" s="32" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="F261" s="33"/>
       <c r="G261" s="33"/>
@@ -62908,7 +62943,7 @@
       <c r="C262" s="33"/>
       <c r="D262" s="33"/>
       <c r="E262" s="32" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="F262" s="33"/>
       <c r="G262" s="33"/>
@@ -62920,7 +62955,7 @@
       <c r="C263" s="33"/>
       <c r="D263" s="33"/>
       <c r="E263" s="32" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="F263" s="33"/>
       <c r="G263" s="33"/>
@@ -62932,7 +62967,7 @@
       <c r="C264" s="33"/>
       <c r="D264" s="33"/>
       <c r="E264" s="32" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="F264" s="33"/>
       <c r="G264" s="33"/>
@@ -62944,7 +62979,7 @@
       <c r="C265" s="33"/>
       <c r="D265" s="33"/>
       <c r="E265" s="32" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="F265" s="33"/>
       <c r="G265" s="33"/>
@@ -62956,7 +62991,7 @@
       <c r="C266" s="33"/>
       <c r="D266" s="33"/>
       <c r="E266" s="32" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="F266" s="33"/>
       <c r="G266" s="33"/>
@@ -62968,7 +63003,7 @@
       <c r="C267" s="33"/>
       <c r="D267" s="33"/>
       <c r="E267" s="32" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="F267" s="33"/>
       <c r="G267" s="33"/>
@@ -62980,7 +63015,7 @@
       <c r="C268" s="33"/>
       <c r="D268" s="33"/>
       <c r="E268" s="32" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="F268" s="33"/>
       <c r="G268" s="33"/>
@@ -62992,7 +63027,7 @@
       <c r="C269" s="33"/>
       <c r="D269" s="33"/>
       <c r="E269" s="32" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="F269" s="33"/>
       <c r="G269" s="33"/>
@@ -63004,7 +63039,7 @@
       <c r="C270" s="33"/>
       <c r="D270" s="33"/>
       <c r="E270" s="32" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="F270" s="33"/>
       <c r="G270" s="33"/>
@@ -63016,7 +63051,7 @@
       <c r="C271" s="33"/>
       <c r="D271" s="33"/>
       <c r="E271" s="32" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F271" s="33"/>
       <c r="G271" s="33"/>
@@ -63028,7 +63063,7 @@
       <c r="C272" s="33"/>
       <c r="D272" s="33"/>
       <c r="E272" s="32" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="F272" s="33"/>
       <c r="G272" s="33"/>
@@ -63039,16 +63074,16 @@
         <v>5</v>
       </c>
       <c r="B273" s="32" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C273" s="33" t="s">
         <v>397</v>
       </c>
       <c r="D273" s="32" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E273" s="32" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="F273" s="33"/>
       <c r="G273" s="33"/>
@@ -63060,7 +63095,7 @@
       <c r="C274" s="33"/>
       <c r="D274" s="32"/>
       <c r="E274" s="32" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="F274" s="33"/>
       <c r="G274" s="33"/>
@@ -63072,7 +63107,7 @@
       <c r="C275" s="33"/>
       <c r="D275" s="32"/>
       <c r="E275" s="32" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="F275" s="33"/>
       <c r="G275" s="33"/>
@@ -63084,7 +63119,7 @@
       <c r="C276" s="33"/>
       <c r="D276" s="32"/>
       <c r="E276" s="32" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="F276" s="33"/>
       <c r="G276" s="33"/>
@@ -63107,16 +63142,16 @@
         <v>5</v>
       </c>
       <c r="B278" s="32" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C278" s="32" t="s">
         <v>397</v>
       </c>
       <c r="D278" s="32" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E278" s="32" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="F278" s="32"/>
       <c r="G278" s="32"/>
@@ -63128,7 +63163,7 @@
       <c r="C279" s="32"/>
       <c r="D279" s="32"/>
       <c r="E279" s="32" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="F279" s="32"/>
       <c r="G279" s="32"/>
@@ -63140,7 +63175,7 @@
       <c r="C280" s="32"/>
       <c r="D280" s="32"/>
       <c r="E280" s="32" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="F280" s="32"/>
       <c r="G280" s="32"/>
@@ -63151,16 +63186,16 @@
         <v>5</v>
       </c>
       <c r="B281" s="32" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C281" s="32" t="s">
         <v>397</v>
       </c>
       <c r="D281" s="32" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E281" s="32" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="F281" s="32"/>
       <c r="G281" s="32"/>
@@ -63172,7 +63207,7 @@
       <c r="C282" s="32"/>
       <c r="D282" s="32"/>
       <c r="E282" s="32" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="F282" s="32"/>
       <c r="G282" s="32"/>
@@ -63184,7 +63219,7 @@
       <c r="C283" s="32"/>
       <c r="D283" s="32"/>
       <c r="E283" s="32" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="F283" s="32"/>
       <c r="G283" s="32"/>
@@ -63326,7 +63361,7 @@
       <c r="E1" s="141"/>
       <c r="F1" s="142"/>
       <c r="G1" s="143" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H1" s="144"/>
       <c r="I1" s="145"/>
@@ -63357,7 +63392,7 @@
         <v>295</v>
       </c>
       <c r="I2" s="37" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="28.75" customHeight="1">
@@ -63390,7 +63425,7 @@
         <v>298</v>
       </c>
       <c r="F4" s="53" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="G4" s="53" t="b">
         <v>0</v>
@@ -63399,7 +63434,7 @@
         <v>299</v>
       </c>
       <c r="I4" s="53" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="32">
@@ -63419,7 +63454,7 @@
         <v>300</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="G5" s="53" t="b">
         <v>0</v>
@@ -63440,13 +63475,13 @@
         <v>301</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E6" s="53" t="s">
         <v>302</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="G6" s="53" t="b">
         <v>0</v>
@@ -63471,7 +63506,7 @@
         <v>303</v>
       </c>
       <c r="F7" s="53" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="G7" s="53" t="b">
         <v>0</v>
@@ -63496,7 +63531,7 @@
         <v>304</v>
       </c>
       <c r="F8" s="53" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="G8" s="53" t="b">
         <v>0</v>
@@ -63515,7 +63550,7 @@
         <v>305</v>
       </c>
       <c r="D9" s="53" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="E9" s="53" t="s">
         <v>306</v>
@@ -63528,7 +63563,7 @@
       </c>
       <c r="H9" s="53"/>
       <c r="I9" s="53" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -63542,13 +63577,13 @@
         <v>305</v>
       </c>
       <c r="D10" s="53" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="E10" s="53" t="s">
         <v>308</v>
       </c>
       <c r="F10" s="53" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="G10" s="53" t="b">
         <v>0</v>
@@ -63567,13 +63602,13 @@
         <v>305</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="E11" s="53" t="s">
         <v>309</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="G11" s="53" t="b">
         <v>0</v>
@@ -63592,13 +63627,13 @@
         <v>305</v>
       </c>
       <c r="D12" s="53" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="E12" s="53" t="s">
         <v>310</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="G12" s="53" t="b">
         <v>0</v>
@@ -63616,10 +63651,10 @@
         <v>397</v>
       </c>
       <c r="C13" s="53" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D13" s="53" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E13" s="53" t="s">
         <v>594</v>
@@ -63632,7 +63667,7 @@
       </c>
       <c r="H13" s="53"/>
       <c r="I13" s="53" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -63643,10 +63678,10 @@
         <v>397</v>
       </c>
       <c r="C14" s="53" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D14" s="53" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E14" s="53" t="s">
         <v>596</v>
@@ -63659,7 +63694,7 @@
       </c>
       <c r="H14" s="53"/>
       <c r="I14" s="53" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
   </sheetData>
@@ -63695,7 +63730,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="40" customFormat="1" ht="92" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B1" s="136"/>
       <c r="C1" s="136"/>
@@ -63713,7 +63748,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="105" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>421</v>
@@ -63724,13 +63759,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="63" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C3" s="63" t="s">
         <v>1023</v>
       </c>
-      <c r="C3" s="63" t="s">
+      <c r="D3" s="32" t="s">
         <v>1024</v>
-      </c>
-      <c r="D3" s="32" t="s">
-        <v>1025</v>
       </c>
       <c r="E3" s="33"/>
     </row>
@@ -63785,7 +63820,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="40" customFormat="1" ht="207" customHeight="1">
       <c r="A1" s="136" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1" s="138"/>
       <c r="C1" s="138"/>
@@ -63812,34 +63847,34 @@
         <v>2</v>
       </c>
       <c r="D2" s="105" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E2" s="106" t="s">
         <v>1026</v>
       </c>
-      <c r="E2" s="106" t="s">
+      <c r="F2" s="106" t="s">
         <v>1027</v>
       </c>
-      <c r="F2" s="106" t="s">
+      <c r="G2" s="106" t="s">
         <v>1028</v>
       </c>
-      <c r="G2" s="106" t="s">
+      <c r="H2" s="107" t="s">
         <v>1029</v>
       </c>
-      <c r="H2" s="107" t="s">
+      <c r="I2" s="108" t="s">
         <v>1030</v>
       </c>
-      <c r="I2" s="108" t="s">
+      <c r="J2" s="108" t="s">
         <v>1031</v>
       </c>
-      <c r="J2" s="108" t="s">
+      <c r="K2" s="106" t="s">
         <v>1032</v>
       </c>
-      <c r="K2" s="106" t="s">
+      <c r="L2" s="106" t="s">
         <v>1033</v>
       </c>
-      <c r="L2" s="106" t="s">
+      <c r="M2" s="106" t="s">
         <v>1034</v>
-      </c>
-      <c r="M2" s="106" t="s">
-        <v>1035</v>
       </c>
       <c r="N2" s="109" t="s">
         <v>421</v>
@@ -63850,29 +63885,29 @@
         <v>5</v>
       </c>
       <c r="B3" s="32" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C3" s="32" t="s">
         <v>1036</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="D3" s="32" t="s">
         <v>1037</v>
-      </c>
-      <c r="D3" s="32" t="s">
-        <v>1038</v>
       </c>
       <c r="E3" s="32" t="s">
         <v>397</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="G3" s="32">
         <v>10</v>
       </c>
       <c r="H3" s="110"/>
       <c r="I3" s="111" t="s">
+        <v>1039</v>
+      </c>
+      <c r="J3" s="111" t="s">
         <v>1040</v>
-      </c>
-      <c r="J3" s="111" t="s">
-        <v>1041</v>
       </c>
       <c r="K3" s="32"/>
       <c r="L3" s="32"/>
@@ -63884,19 +63919,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="32" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>1042</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="D4" s="32" t="s">
         <v>1043</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="E4" s="32" t="s">
         <v>1044</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="F4" s="32" t="s">
         <v>1045</v>
-      </c>
-      <c r="F4" s="32" t="s">
-        <v>1046</v>
       </c>
       <c r="G4" s="32">
         <v>100</v>
@@ -63907,7 +63942,7 @@
       <c r="I4" s="111"/>
       <c r="J4" s="111"/>
       <c r="K4" s="32" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="L4" s="112"/>
       <c r="M4" s="32"/>
@@ -63925,13 +63960,13 @@
       <c r="I5" s="111"/>
       <c r="J5" s="111"/>
       <c r="K5" s="32" t="s">
+        <v>1047</v>
+      </c>
+      <c r="L5" s="33" t="s">
         <v>1048</v>
       </c>
-      <c r="L5" s="33" t="s">
+      <c r="M5" s="32" t="s">
         <v>1049</v>
-      </c>
-      <c r="M5" s="32" t="s">
-        <v>1050</v>
       </c>
       <c r="N5" s="113"/>
     </row>
@@ -63947,10 +63982,10 @@
       <c r="I6" s="111"/>
       <c r="J6" s="111"/>
       <c r="K6" s="32" t="s">
+        <v>1050</v>
+      </c>
+      <c r="L6" s="33" t="s">
         <v>1051</v>
-      </c>
-      <c r="L6" s="33" t="s">
-        <v>1052</v>
       </c>
       <c r="M6" s="32"/>
       <c r="N6" s="113"/>
